--- a/indicadores/GR-EPRIV-FOR_out.xlsx
+++ b/indicadores/GR-EPRIV-FOR_out.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">log</t>
   </si>
   <si>
-    <t xml:space="preserve">(1 0 1)</t>
+    <t xml:space="preserve">(0 1 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Regresores</t>
   </si>
   <si>
-    <t xml:space="preserve">const | easter[1]</t>
+    <t xml:space="preserve">easter[1]</t>
   </si>
   <si>
     <t xml:space="preserve">Resumen del correlograma</t>
@@ -106,7 +106,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">16/11/2025</t>
+    <t xml:space="preserve">09/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
@@ -1060,7 +1060,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.470965011511414</v>
+        <v>0.49620024218763</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1076,7 +1076,7 @@
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -1118,7 +1118,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.221808042067946</v>
+        <v>0.21925200112787</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1188,7 +1188,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.624729263321151</v>
+        <v>0.793468451407221</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1218,7 +1218,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.369515201517608</v>
+        <v>0.173834291500104</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1478,40 +1478,40 @@
         <v>187.428</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.993344020632718</v>
+        <v>0.993331631911461</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>187.476672424254</v>
+        <v>187.479153666739</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>191.004504060418</v>
+        <v>190.999394823529</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>184.438892127197</v>
+        <v>184.434725737315</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>188.683875985498</v>
+        <v>188.686229229742</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>188.683875985498</v>
+        <v>188.686229229742</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>189.893019136992</v>
+        <v>189.894833401763</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>189.893019136992</v>
+        <v>189.894833401763</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>1.01288878600997</v>
+        <v>1.01288505781991</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.994180844431429</v>
+        <v>0.994216937583567</v>
       </c>
     </row>
     <row r="3">
@@ -1531,44 +1531,44 @@
         <v>193.778</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.00762666842006</v>
+        <v>1.00762281051611</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>194.340804351531</v>
+        <v>194.341279635961</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>196.840321403324</v>
+        <v>196.835563599233</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>190.9422414936</v>
+        <v>190.937791867447</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>192.31130543998</v>
+        <v>192.312041745805</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>192.31130543998</v>
+        <v>192.312041745805</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>193.955403076506</v>
+        <v>193.955965060532</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>193.955403076506</v>
+        <v>193.955965060532</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.0211673951771505</v>
+        <v>0.0211607385680659</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.0213930135924767</v>
+        <v>0.0213862146010926</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>0.998016879284252</v>
+        <v>0.998017330254537</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.985343864985333</v>
+        <v>0.9853705372848</v>
       </c>
     </row>
     <row r="4">
@@ -1588,44 +1588,44 @@
         <v>202.718</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1.00100177485011</v>
+        <v>1.00100957433084</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>199.052074958097</v>
+        <v>199.052087305517</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>202.674688353683</v>
+        <v>202.67028664644</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>197.466815779295</v>
+        <v>197.462115515041</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>202.515125440567</v>
+        <v>202.513547520776</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>202.515125440567</v>
+        <v>202.513547520776</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>198.559789415938</v>
+        <v>198.558942996997</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>198.559789415938</v>
+        <v>198.558942996997</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.0234620093117239</v>
+        <v>0.0234548490245913</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0237394074431381</v>
+        <v>0.0237320772012752</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.997526850487427</v>
+        <v>0.997522536361232</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.979697025952422</v>
+        <v>0.979714127228647</v>
       </c>
     </row>
     <row r="5">
@@ -1645,44 +1645,44 @@
         <v>196.406</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.997503263933716</v>
+        <v>0.997508158531354</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>198.33118716151</v>
+        <v>198.326514685869</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>208.503323883972</v>
+        <v>208.499291035497</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>204.040685223304</v>
+        <v>204.035825446951</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>196.897601342637</v>
+        <v>196.89663520063</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>196.897601342637</v>
+        <v>196.89663520063</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>199.133694013835</v>
+        <v>199.128950714108</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>199.133694013835</v>
+        <v>199.128950714108</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.00288616746410492</v>
+        <v>0.00286661030652121</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.00289033645525771</v>
+        <v>0.00287072296270119</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>1.00404629682205</v>
+        <v>1.00404603504231</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.955062443631109</v>
+        <v>0.955058166985355</v>
       </c>
     </row>
     <row r="6">
@@ -1702,46 +1702,46 @@
         <v>206.403</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.03085813013542</v>
+        <v>1.03093774771214</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>202.74617270667</v>
+        <v>202.733742849207</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>214.321847239845</v>
+        <v>214.318205874795</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>210.717161612958</v>
+        <v>210.71230759006</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>200.224447929499</v>
+        <v>200.208984934396</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>200.224447929499</v>
+        <v>200.208984934396</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>202.994220648372</v>
+        <v>202.978815824707</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>202.994220648372</v>
+        <v>202.978815824707</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.0192010805605435</v>
+        <v>0.0191490096474891</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>0.0689925389091246</v>
+        <v>0.0689012027792308</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.0193866068404742</v>
+        <v>0.0193335278310489</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>1.00122344080971</v>
+        <v>1.00120884156754</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.947146654728127</v>
+        <v>0.947090868907735</v>
       </c>
     </row>
     <row r="7">
@@ -1761,46 +1761,46 @@
         <v>221.58</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.972036395026227</v>
+        <v>0.971950046334791</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.0453735305965774</v>
+        <v>0.0439947273789287</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>213.997091790049</v>
+        <v>213.985194671946</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>220.118624090371</v>
+        <v>220.11540861283</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>217.513841316184</v>
+        <v>217.509251920019</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>227.954427564434</v>
+        <v>227.974679188066</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>214.630385391855</v>
+        <v>214.600658229404</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>212.454886762193</v>
+        <v>212.435826772185</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>212.454886762193</v>
+        <v>212.435826772185</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0455521593124033</v>
+        <v>0.0455383330424504</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.0953800894032821</v>
+        <v>0.0952786458817358</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0466055934183893</v>
+        <v>0.0465911228669575</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.992793336512401</v>
+        <v>0.992759462157481</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.965183603341846</v>
+        <v>0.965111111988744</v>
       </c>
     </row>
     <row r="8">
@@ -1820,46 +1820,46 @@
         <v>220.366</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1.00014374366752</v>
+        <v>1.00014974744415</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>222.714238956926</v>
+        <v>222.710821152538</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>225.873209230045</v>
+        <v>225.870458435008</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>224.395857132489</v>
+        <v>224.3918317992</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>220.334328335564</v>
+        <v>220.333005695535</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>220.334328335564</v>
+        <v>220.333005695535</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>221.287717162365</v>
+        <v>221.279536560669</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>221.287717162365</v>
+        <v>221.279536560669</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.0407340741729259</v>
+        <v>0.0407868224616896</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.114463899328666</v>
+        <v>0.114427450210671</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0415750869974492</v>
+        <v>0.0416300297499625</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.993594833445574</v>
+        <v>0.993573349581929</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.979698822700967</v>
+        <v>0.979674535987802</v>
       </c>
     </row>
     <row r="9">
@@ -1879,46 +1879,46 @@
         <v>229.158</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.996981417999679</v>
+        <v>0.996982935970688</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>228.965795485863</v>
+        <v>228.96605351843</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>231.561727304182</v>
+        <v>231.559467807749</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>231.313924581763</v>
+        <v>231.310677621522</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>229.851826586475</v>
+        <v>229.851476622201</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>229.851826586475</v>
+        <v>229.851476622201</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>228.937994908781</v>
+        <v>228.937496167864</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>228.937994908781</v>
+        <v>228.937496167864</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0339874598910196</v>
+        <v>0.0340222502430531</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.149669803709239</v>
+        <v>0.149694684508996</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0345716330057462</v>
+        <v>0.0346076267431761</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.999878581964513</v>
+        <v>0.999875276923686</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.988669403938442</v>
+        <v>0.988676897279528</v>
       </c>
     </row>
     <row r="10">
@@ -1938,46 +1938,46 @@
         <v>234.538</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.995010910951588</v>
+        <v>0.995010794424017</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>235.26379962757</v>
+        <v>235.264244986483</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>237.156841157532</v>
+        <v>237.155088289506</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>238.198451539907</v>
+        <v>238.196125650388</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>235.713998126611</v>
+        <v>235.714025731517</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>235.713998126611</v>
+        <v>235.714025731517</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>235.172940617372</v>
+        <v>235.173183350339</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>235.172940617372</v>
+        <v>235.173183350339</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.0268699587099563</v>
+        <v>0.026873169356262</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.158520374945748</v>
+        <v>0.158609495256076</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0272342112154655</v>
+        <v>0.0272375093064854</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>0.999613799444106</v>
+        <v>0.999612938905574</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.991634647642985</v>
+        <v>0.991643000563633</v>
       </c>
     </row>
     <row r="11">
@@ -1997,46 +1997,46 @@
         <v>241.824</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1.01007493767411</v>
+        <v>1.01006959779305</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>239.734149489712</v>
+        <v>239.734567269002</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>242.6301449469</v>
+        <v>242.628903944246</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>244.972535392848</v>
+        <v>244.971216144202</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>239.411939629792</v>
+        <v>239.413205316122</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>239.411939629792</v>
+        <v>239.413205316122</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>240.776474988123</v>
+        <v>240.776897354293</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>240.776474988123</v>
+        <v>240.776897354293</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0235478524197586</v>
+        <v>0.0235485744557919</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.133306362859195</v>
+        <v>0.133410032633058</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.0238272921877865</v>
+        <v>0.0238280314282502</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.00434783905685</v>
+        <v>1.00434785061314</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.992360100352815</v>
+        <v>0.992366916884814</v>
       </c>
     </row>
     <row r="12">
@@ -2056,46 +2056,46 @@
         <v>247.933</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.997445276509256</v>
+        <v>0.997448765673096</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>250.112540702826</v>
+        <v>250.112864316663</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>247.952331052195</v>
+        <v>247.951598171833</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>251.546851259445</v>
+        <v>251.546578861774</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>248.568022566298</v>
+        <v>248.567153053411</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>248.568022566298</v>
+        <v>248.567153053411</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>250.741102935807</v>
+        <v>250.741218576126</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>250.741102935807</v>
+        <v>250.741218576126</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>0.0405519309710811</v>
+        <v>0.0405506379829162</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0.13309995760782</v>
+        <v>0.133142370385342</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>0.0413853884528164</v>
+        <v>0.0413840419547045</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>1.00251311761983</v>
+        <v>1.00251228284951</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.01124720978334</v>
+        <v>1.01125066514941</v>
       </c>
     </row>
     <row r="13">
@@ -2115,46 +2115,46 @@
         <v>265.114</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.995111311282123</v>
+        <v>0.995107815543756</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>265.649745111206</v>
+        <v>265.649147288424</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>253.092080475004</v>
+        <v>253.091844560491</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>257.804271279745</v>
+        <v>257.805053507774</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>266.416426980838</v>
+        <v>266.417362881563</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>266.416426980838</v>
+        <v>266.417362881563</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>264.13933584906</v>
+        <v>264.13902306394</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>264.13933584906</v>
+        <v>264.13902306394</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.0520558068214175</v>
+        <v>0.0520541614595812</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.153759278595519</v>
+        <v>0.15376042581625</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.0534345297056606</v>
+        <v>0.0534327964261143</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0.994314283036433</v>
+        <v>0.99431534322659</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.04364915470023</v>
+        <v>1.04364889166078</v>
       </c>
     </row>
     <row r="14">
@@ -2174,46 +2174,46 @@
         <v>274.574</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.99788314308984</v>
+        <v>0.997891315448259</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>272.05843661795</v>
+        <v>272.05795542196</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>258.018459024109</v>
+        <v>258.018701420246</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>263.612773450325</v>
+        <v>263.61458265783</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>275.156466868265</v>
+        <v>275.154213439226</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>275.156466868265</v>
+        <v>275.154213439226</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>271.039573457996</v>
+        <v>271.039059467428</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>271.039573457996</v>
+        <v>271.039059467428</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.0257880865163736</v>
+        <v>0.025787374315168</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.152511733477787</v>
+        <v>0.15250835833463</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.026123476031148</v>
+        <v>0.0261227452250314</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>0.9962549841401</v>
+        <v>0.996254856973576</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.0504658251318</v>
+        <v>1.05046284620267</v>
       </c>
     </row>
     <row r="15">
@@ -2233,46 +2233,46 @@
         <v>270.671</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.01212309695748</v>
+        <v>1.0121173632741</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>271.578400683523</v>
+        <v>271.578412661917</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>262.708860224859</v>
+        <v>262.70955551007</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>268.88339654627</v>
+        <v>268.88617043444</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>267.428933114616</v>
+        <v>267.430448109699</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>267.428933114616</v>
+        <v>267.430448109699</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>272.020292801928</v>
+        <v>272.020501328227</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>272.020292801928</v>
+        <v>272.020501328227</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.0036118316635566</v>
+        <v>0.00361449461591371</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.129762751179683</v>
+        <v>0.12976163542784</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.00361836218755696</v>
+        <v>0.00362103477899867</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>1.0016271254168</v>
+        <v>1.00162784906936</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.03544392286236</v>
+        <v>1.0354419762162</v>
       </c>
     </row>
     <row r="16">
@@ -2292,46 +2292,46 @@
         <v>276.7245</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.995172606272153</v>
+        <v>0.995172400327895</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>276.769311667382</v>
+        <v>276.768065414446</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>267.151388857506</v>
+        <v>267.152503283952</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>273.584897809754</v>
+        <v>273.588519114007</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>278.066838110215</v>
+        <v>278.066895654284</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>278.066838110215</v>
+        <v>278.066895654284</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>277.238501791449</v>
+        <v>277.239324373446</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>277.238501791449</v>
+        <v>277.239324373446</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0190014836196697</v>
+        <v>0.0190036840873615</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.105676327277007</v>
+        <v>0.105679097947251</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0191831606964705</v>
+        <v>0.0191854033785552</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1.00169523897444</v>
+        <v>1.00170272158493</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.03775804040204</v>
+        <v>1.037756790468</v>
       </c>
     </row>
     <row r="17">
@@ -2351,46 +2351,46 @@
         <v>282.778</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.99084275892472</v>
+        <v>0.990836994798855</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>283.811542112202</v>
+        <v>283.821138785627</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>271.337099747856</v>
+        <v>271.338591753752</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>277.678762165794</v>
+        <v>277.683052361311</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>285.391397830747</v>
+        <v>285.393058075517</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>285.391397830747</v>
+        <v>285.393058075517</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>283.322935911223</v>
+        <v>283.331614740176</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>283.322935911223</v>
+        <v>283.331614740176</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.0217092103367617</v>
+        <v>0.0217368751017106</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.072626820236745</v>
+        <v>0.0726609474571656</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.0219465697601817</v>
+        <v>0.021974842062896</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.998278413212716</v>
+        <v>0.998275237540286</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.04417323017938</v>
+        <v>1.04419947383418</v>
       </c>
     </row>
     <row r="18">
@@ -2410,46 +2410,46 @@
         <v>292.243</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.03994363585755</v>
+        <v>1.04004431984656</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.521596525429919</v>
+        <v>0.516686719710223</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>288.175243204648</v>
+        <v>288.196458108905</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>275.263869877502</v>
+        <v>275.265689426565</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>281.148884240906</v>
+        <v>281.153585723835</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>281.018114754857</v>
+        <v>280.990910121133</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>284.442109873181</v>
+        <v>284.473447155389</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>286.924728337009</v>
+        <v>286.944882879299</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>286.924728337009</v>
+        <v>286.944882879299</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.0126325473989258</v>
+        <v>0.012672156424804</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0586082492543269</v>
+        <v>0.0586846170552855</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.0127126750758881</v>
+        <v>0.0127527884328626</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.995660574955251</v>
+        <v>0.995657215089254</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.04236247374091</v>
+        <v>1.04242880206779</v>
       </c>
     </row>
     <row r="19">
@@ -2469,46 +2469,46 @@
         <v>306.237</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.977944911207743</v>
+        <v>0.977858269253417</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>293.423295770926</v>
+        <v>293.439579130903</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>278.938360164335</v>
+        <v>278.940448850933</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>284.017721839934</v>
+        <v>284.022484777631</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>313.143405615561</v>
+        <v>313.171151309901</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>293.423295770926</v>
+        <v>293.439579130903</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>292.018013193259</v>
+        <v>292.035055908265</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>292.018013193259</v>
+        <v>292.035055908265</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.0175955786256857</v>
+        <v>0.0175836979429241</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0735155461577703</v>
+        <v>0.0735773755371751</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0177512927720447</v>
+        <v>0.0177392012636328</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.995210732760753</v>
+        <v>0.995213586296715</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.04689083646013</v>
+        <v>1.04694409545576</v>
       </c>
     </row>
     <row r="20">
@@ -2528,46 +2528,46 @@
         <v>280.597</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.992274602287356</v>
+        <v>0.992271258575254</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>296.783351358001</v>
+        <v>296.787618215864</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>282.372967926244</v>
+        <v>282.375277423982</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>286.324198895882</v>
+        <v>286.328714405909</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>282.781600328354</v>
+        <v>282.78255323337</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>296.783351358001</v>
+        <v>296.787618215864</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>295.385453954293</v>
+        <v>295.392231771356</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>295.385453954293</v>
+        <v>295.392231771356</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.0114656376403673</v>
+        <v>0.0114302228877506</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0654561038441024</v>
+        <v>0.0654773901174914</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.0115316199990916</v>
+        <v>0.0114957974913317</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.995289838876367</v>
+        <v>0.995298367051508</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.04608261946465</v>
+        <v>1.04609806660882</v>
       </c>
     </row>
     <row r="21">
@@ -2587,46 +2587,46 @@
         <v>290.531</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.986349371846734</v>
+        <v>0.986341689470931</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>292.53459723468</v>
+        <v>292.535160381584</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>285.589143565873</v>
+        <v>285.591644499261</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>288.15426721141</v>
+        <v>288.158324963647</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>294.551817330244</v>
+        <v>294.554111522792</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>294.551817330244</v>
+        <v>294.554111522792</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>292.844610458544</v>
+        <v>292.8457140431</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>292.844610458544</v>
+        <v>292.8457140431</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0086389984186915</v>
+        <v>-0.0086581753334755</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0336071434410949</v>
+        <v>0.0335793776901601</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.00860178949821488</v>
+        <v>-0.00862080127492049</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.0010597489213</v>
+        <v>1.00106159430925</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.02540526156589</v>
+        <v>1.02540014627024</v>
       </c>
     </row>
     <row r="22">
@@ -2646,46 +2646,46 @@
         <v>288.02</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.00885681211401</v>
+        <v>1.0088725054267</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>288.573243498534</v>
+        <v>288.57124831052</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>288.617343975511</v>
+        <v>288.620027143316</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>289.646174351488</v>
+        <v>289.64966132487</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>285.491455815685</v>
+        <v>285.48701491095</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>285.491455815685</v>
+        <v>285.48701491095</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>288.625962924301</v>
+        <v>288.62456493328</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>288.625962924301</v>
+        <v>288.62456493328</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0145105246891461</v>
+        <v>-0.0145191368005445</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>0.00592920170092115</v>
+        <v>0.00585367488392374</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0144057543952637</v>
+        <v>-0.0144142424061505</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>1.00018268993039</v>
+        <v>1.00018476068934</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.00002986289275</v>
+        <v>1.00001572236691</v>
       </c>
     </row>
     <row r="23">
@@ -2705,46 +2705,46 @@
         <v>293.355</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.0151776675061</v>
+        <v>1.01517416968933</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>286.75540566455</v>
+        <v>286.754833044661</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>291.493627718549</v>
+        <v>291.496503964579</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>290.970155631678</v>
+        <v>290.973047296402</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>288.96912273559</v>
+        <v>288.970118388428</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>288.96912273559</v>
+        <v>288.970118388428</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>286.746718352028</v>
+        <v>286.746537650574</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>286.746718352028</v>
+        <v>286.746537650574</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.00653229225451648</v>
+        <v>-0.00652807881292354</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0180512660283809</v>
+        <v>-0.0181091898068287</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.00651100321410147</v>
+        <v>-0.00650681719742152</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.999969704799454</v>
+        <v>0.99997107147594</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.983715220796851</v>
+        <v>0.983704894400441</v>
       </c>
     </row>
     <row r="24">
@@ -2764,46 +2764,46 @@
         <v>280.514</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.989267871101687</v>
+        <v>0.989261846741027</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>282.832395849626</v>
+        <v>282.835031588636</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>294.252099678279</v>
+        <v>294.255195438841</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>292.275672774867</v>
+        <v>292.277993452995</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>283.557172121246</v>
+        <v>283.558898914489</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>283.557172121246</v>
+        <v>283.558898914489</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>283.515035796902</v>
+        <v>283.516706563085</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>283.515035796902</v>
+        <v>283.516706563085</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.0113341535795428</v>
+        <v>-0.0113276303761769</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0401861973854272</v>
+        <v>-0.0402025643567446</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.0112701640447673</v>
+        <v>-0.0112637143379372</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.0024135847141</v>
+        <v>1.00241015043512</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.963510663498692</v>
+        <v>0.963506204674686</v>
       </c>
     </row>
     <row r="25">
@@ -2823,46 +2823,46 @@
         <v>273.279</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.983100466292418</v>
+        <v>0.983092566143439</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>281.474979918335</v>
+        <v>281.474969589252</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>296.925286922377</v>
+        <v>296.928643050905</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>293.702182339459</v>
+        <v>293.703995724862</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>277.976676209524</v>
+        <v>277.978910034935</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>277.976676209524</v>
+        <v>277.978910034935</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>282.582498583486</v>
+        <v>282.582701965151</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>282.582498583486</v>
+        <v>282.582701965151</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.00329461974412656</v>
+        <v>-0.00329979304470757</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.0350428572306264</v>
+        <v>-0.0350457991556549</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.00328919843984365</v>
+        <v>-0.00329435471107498</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.00393469666637</v>
+        <v>1.00393545606387</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.951695631963336</v>
+        <v>0.951685560078168</v>
       </c>
     </row>
     <row r="26">
@@ -2882,46 +2882,46 @@
         <v>294.75</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.01351536129661</v>
+        <v>1.01353411431669</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>287.48944085276</v>
+        <v>287.487244398286</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>299.539032188797</v>
+        <v>299.542703100247</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>295.34554838059</v>
+        <v>295.346954569523</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>290.81946979365</v>
+        <v>290.814088876245</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>290.81946979365</v>
+        <v>290.814088876245</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>288.162359666875</v>
+        <v>288.160614700763</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>288.162359666875</v>
+        <v>288.160614700763</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0195535317946358</v>
+        <v>0.0195467565553114</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>-0.00160624239319462</v>
+        <v>-0.00160745234081106</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.019745954230568</v>
+        <v>0.0197390452310831</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.00234067314653</v>
+        <v>1.00234226149367</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.962019398811601</v>
+        <v>0.96200178378014</v>
       </c>
     </row>
     <row r="27">
@@ -2941,46 +2941,46 @@
         <v>298.139</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.01742180161768</v>
+        <v>1.0174164264426</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>295.547270053171</v>
+        <v>295.546904537807</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>302.107335333798</v>
+        <v>302.111388303209</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>297.223007422747</v>
+        <v>297.22414501605</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>293.033822870677</v>
+        <v>293.035371015626</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>293.033822870677</v>
+        <v>293.035371015626</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>294.451735922864</v>
+        <v>294.451744076066</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>294.451735922864</v>
+        <v>294.451744076066</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.0215910347164702</v>
+        <v>0.0215971179205733</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0268704646913414</v>
+        <v>0.0268711402363344</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0218258077261002</v>
+        <v>0.021832023719953</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.996293201659044</v>
+        <v>0.996294461403838</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.974659339527537</v>
+        <v>0.974646290991666</v>
       </c>
     </row>
     <row r="28">
@@ -3000,46 +3000,46 @@
         <v>296.237</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.984438286486002</v>
+        <v>0.984430705853872</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>297.573410708112</v>
+        <v>297.576737587639</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>304.638746487142</v>
+        <v>304.643255992242</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>299.329165597482</v>
+        <v>299.330177765045</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>300.919828156452</v>
+        <v>300.922145396766</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>300.919828156452</v>
+        <v>300.922145396766</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>297.855075171018</v>
+        <v>297.857192034275</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>297.855075171018</v>
+        <v>297.857192034275</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>0.0114919384325616</v>
+        <v>0.0114990177421704</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0505794669189581</v>
+        <v>0.0505807422956868</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.0115582244318844</v>
+        <v>0.0115653855910904</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00094653773748</v>
+        <v>1.00094246092255</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.977732079735926</v>
+        <v>0.977724555444811</v>
       </c>
     </row>
     <row r="29">
@@ -3059,46 +3059,46 @@
         <v>291.018</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.981355991365825</v>
+        <v>0.981348430293958</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>300.428278903666</v>
+        <v>300.42791673821</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>307.136144833299</v>
+        <v>307.141190988993</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>301.637683113587</v>
+        <v>301.638719647113</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>296.546821500492</v>
+        <v>296.54910632794</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>296.546821500492</v>
+        <v>296.54910632794</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>300.393157122976</v>
+        <v>300.393143606928</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>300.393157122976</v>
+        <v>300.393143606928</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.00848509713112826</v>
+        <v>0.00847794513755669</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0630281727593545</v>
+        <v>0.0630273598416284</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.00852119760088277</v>
+        <v>0.00851398468955411</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.999883094291863</v>
+        <v>0.999884254660288</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.978045606732538</v>
+        <v>0.978029493991554</v>
       </c>
     </row>
     <row r="30">
@@ -3118,46 +3118,46 @@
         <v>313.284</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.01861379357112</v>
+        <v>1.01863678204791</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>305.138365387835</v>
+        <v>305.135374798896</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>309.600085232786</v>
+        <v>309.605752420985</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>304.130173492649</v>
+        <v>304.131397331013</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>307.559157334469</v>
+        <v>307.552216375066</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>307.559157334469</v>
+        <v>307.552216375066</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>305.101143263589</v>
+        <v>305.098818374853</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>305.101143263589</v>
+        <v>305.098818374853</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0155511984794893</v>
+        <v>0.0155436233859091</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0587820824909095</v>
+        <v>0.058780425949881</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0156727476274872</v>
+        <v>0.0156650538405176</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.999878015587457</v>
+        <v>0.99988019604719</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.985468537691732</v>
+        <v>0.985442989960974</v>
       </c>
     </row>
     <row r="31">
@@ -3177,46 +3177,46 @@
         <v>314.394</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1.01831500106409</v>
+        <v>1.01830742315824</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>308.550123867793</v>
+        <v>308.550193537259</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>312.024504219034</v>
+        <v>312.030879362831</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>306.762795948188</v>
+        <v>306.76438941891</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>308.739436884926</v>
+        <v>308.74173442134</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>308.739436884926</v>
+        <v>308.74173442134</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>308.219293319939</v>
+        <v>308.219671270315</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>308.219293319939</v>
+        <v>308.219671270315</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.0101681820342879</v>
+        <v>0.0101770283601846</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.0467565842460556</v>
+        <v>0.0467578388351884</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0102200536615358</v>
+        <v>0.0102289904368866</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.998927789936665</v>
+        <v>0.998928789306028</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.987804769024089</v>
+        <v>0.987785798314902</v>
       </c>
     </row>
     <row r="32">
@@ -3236,46 +3236,46 @@
         <v>301.481</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.979345894318369</v>
+        <v>0.97933362179314</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>309.990321998035</v>
+        <v>309.994903706861</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>314.40206274554</v>
+        <v>314.409227429112</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>309.508854612935</v>
+        <v>309.51097860819</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>307.839142175434</v>
+        <v>307.842999863514</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>307.839142175434</v>
+        <v>307.842999863514</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>309.901434865151</v>
+        <v>309.904422667002</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>309.901434865151</v>
+        <v>309.904422667002</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.00544277394730321</v>
+        <v>0.005451188798946</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.0404436945961575</v>
+        <v>0.040446331177864</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.00545761275062628</v>
+        <v>0.00546607356286888</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.999713258361385</v>
+        <v>0.999708120879481</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.985685119744167</v>
+        <v>0.985672161090991</v>
       </c>
     </row>
     <row r="33">
@@ -3295,46 +3295,46 @@
         <v>309.323</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.981392001327204</v>
+        <v>0.981385966150626</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>312.721291501804</v>
+        <v>312.720460545564</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>316.723368598715</v>
+        <v>316.731396518823</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>312.351536824304</v>
+        <v>312.354334321249</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>315.188018224808</v>
+        <v>315.189956519639</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>315.188018224808</v>
+        <v>315.189956519639</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>312.508492058945</v>
+        <v>312.508145049101</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>312.508492058945</v>
+        <v>312.508145049101</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.0083773485220349</v>
+        <v>0.00836659703066343</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.04033159427466</v>
+        <v>0.0403304858982592</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.00841253669873576</v>
+        <v>0.00840169481833186</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.999319523650476</v>
+        <v>0.999321069379047</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.98669224642811</v>
+        <v>0.986666141986115</v>
       </c>
     </row>
     <row r="34">
@@ -3354,46 +3354,46 @@
         <v>319.058</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.0232160813603</v>
+        <v>1.02324601661424</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>312.445894208368</v>
+        <v>312.441422960406</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>318.974927739615</v>
+        <v>318.983882638728</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>315.265681357521</v>
+        <v>315.269286086763</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>311.818789610727</v>
+        <v>311.809667293612</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>311.818789610727</v>
+        <v>311.809667293612</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>312.796061765227</v>
+        <v>312.792667365545</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>312.796061765227</v>
+        <v>312.792667365545</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>0.00091977493142298</v>
+        <v>0.000910033476466561</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0.0252208773108085</v>
+        <v>0.0252175640393297</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>0.000920198054101151</v>
+        <v>0.000910447682568316</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.00112073022354</v>
+        <v>1.00112419282248</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.98062899169482</v>
+        <v>0.980590821009614</v>
       </c>
     </row>
     <row r="35">
@@ -3413,46 +3413,46 @@
         <v>317.946</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1.01788761217993</v>
+        <v>1.01787872007125</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>313.415855222227</v>
+        <v>313.415887002719</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>321.142286535313</v>
+        <v>321.152218395595</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>318.240309394815</v>
+        <v>318.244841544397</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>312.358649614647</v>
+        <v>312.361378355316</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>312.358649614647</v>
+        <v>312.361378355316</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>314.857578245159</v>
+        <v>314.858212342303</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>314.857578245159</v>
+        <v>314.858212342303</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.00656898570056079</v>
+        <v>0.00658185147279335</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.0215375385937631</v>
+        <v>0.021538343236263</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.00659060880849349</v>
+        <v>0.00660355945730773</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.00460003219017</v>
+        <v>1.00460195350458</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.980430144040023</v>
+        <v>0.980401797986215</v>
       </c>
     </row>
     <row r="36">
@@ -3472,46 +3472,46 @@
         <v>314.546</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.97414563805582</v>
+        <v>0.974126929825112</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>324.017934727877</v>
+        <v>324.023106998321</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>323.206518766549</v>
+        <v>323.217452511599</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>321.247207659681</v>
+        <v>321.252710239851</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>322.894224140617</v>
+        <v>322.900425364969</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>322.894224140617</v>
+        <v>322.900425364969</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>323.315275868948</v>
+        <v>323.320742396091</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>323.315275868948</v>
+        <v>323.320742396091</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.026507529413936</v>
+        <v>0.0265224230849036</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0.0432842171564471</v>
+        <v>0.0432917982054919</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.026861978901469</v>
+        <v>0.0268772727598026</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>0.99783141985792</v>
+        <v>0.997832362609146</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>1.00033649414874</v>
+        <v>1.00031956778228</v>
       </c>
     </row>
     <row r="37">
@@ -3531,46 +3531,46 @@
         <v>329.818</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.984196406322234</v>
+        <v>0.984176626933885</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>331.248875512879</v>
+        <v>331.261162973048</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>325.143208440989</v>
+        <v>325.155139433889</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>324.228754576712</v>
+        <v>324.235184402879</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>335.114005579914</v>
+        <v>335.12074049911</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>335.114005579914</v>
+        <v>335.12074049911</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>329.732317868202</v>
+        <v>329.750992031251</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>329.732317868202</v>
+        <v>329.750992031251</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0196532338769587</v>
+        <v>0.0196929589992414</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.0551147448691056</v>
+        <v>0.0551756722354877</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0198476300942085</v>
+        <v>0.0198881444707377</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>0.995421697228923</v>
+        <v>0.995441147014507</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>1.01411411743526</v>
+        <v>1.01413433785904</v>
       </c>
     </row>
     <row r="38">
@@ -3590,46 +3590,46 @@
         <v>340.482</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.06460687416704</v>
+        <v>1.06476658330554</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0.28474542085429</v>
+        <v>0.277844632718093</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>328.19071014273</v>
+        <v>328.205368933383</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>326.927744382159</v>
+        <v>326.94063546765</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>327.135563652909</v>
+        <v>327.142794838863</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>319.8194641251</v>
+        <v>319.771492962319</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>325.807036172365</v>
+        <v>325.862061761813</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>327.023234539354</v>
+        <v>327.054537534975</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>327.023234539354</v>
+        <v>327.054537534975</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>-0.00824994530850186</v>
+        <v>-0.00821086158402366</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.045483861573697</v>
+        <v>0.0455952829378936</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>-0.00821600790108368</v>
+        <v>-0.00817724453129109</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>0.996442691498282</v>
+        <v>0.996493563154839</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.0002920833696</v>
+        <v>1.00034838761221</v>
       </c>
     </row>
     <row r="39">
@@ -3649,46 +3649,46 @@
         <v>329.749</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.977964806245198</v>
+        <v>0.97785181496953</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>321.364860232774</v>
+        <v>321.373286117165</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>328.541747161795</v>
+        <v>328.55552541873</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>329.972674650284</v>
+        <v>329.980500133663</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>337.178800192248</v>
+        <v>337.217761374483</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>321.364860232774</v>
+        <v>321.373286117165</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>321.71199961904</v>
+        <v>321.731723051898</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>321.71199961904</v>
+        <v>321.731723051898</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>-0.0163744878111046</v>
+        <v>-0.0164088983920216</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.0217699107389568</v>
+        <v>0.0218304952520092</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>-0.0162411546317048</v>
+        <v>-0.0162750057626343</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00108020331163</v>
+        <v>1.00111532896546</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.979211933942169</v>
+        <v>0.979230900596983</v>
       </c>
     </row>
     <row r="40">
@@ -3708,46 +3708,46 @@
         <v>309.118</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.97111870198125</v>
+        <v>0.971097296576256</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>318.531011068444</v>
+        <v>318.53922070791</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>329.966136909002</v>
+        <v>329.980719984413</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>332.738484693452</v>
+        <v>332.746855207757</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>318.311241838249</v>
+        <v>318.318258211448</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>318.311241838249</v>
+        <v>318.318258211448</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>320.088174827473</v>
+        <v>320.096461271903</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>320.088174827473</v>
+        <v>320.096461271903</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>-0.00506023002542093</v>
+        <v>-0.00509564820716026</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>-0.00998128230347839</v>
+        <v>-0.00997239181220966</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>-0.00504744862948836</v>
+        <v>-0.00508268741572426</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.00488857820721</v>
+        <v>1.00488869333118</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.970063709645899</v>
+        <v>0.970045950827136</v>
       </c>
     </row>
     <row r="41">
@@ -3767,46 +3767,46 @@
         <v>319.451</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.990959464620508</v>
+        <v>0.990926613142733</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>324.516986656674</v>
+        <v>324.513408581025</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>331.177348198556</v>
+        <v>331.192640962418</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>335.388351834935</v>
+        <v>335.397378911537</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>322.365355400622</v>
+        <v>322.376042547549</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>322.365355400622</v>
+        <v>322.376042547549</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>326.344141527457</v>
+        <v>326.342571500786</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>326.344141527457</v>
+        <v>326.342571500786</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0193559692448031</v>
+        <v>0.0193252706087662</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>-0.010275536115629</v>
+        <v>-0.010336346554923</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0195445105191905</v>
+        <v>0.0195132123737463</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>1.00563038283329</v>
+        <v>1.00563663279049</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.985405986558594</v>
+        <v>0.985355745080752</v>
       </c>
     </row>
     <row r="42">
@@ -3826,46 +3826,46 @@
         <v>351.422</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.02654533363583</v>
+        <v>1.02664931005112</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>341.929207045726</v>
+        <v>341.917367642725</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>332.144531295812</v>
+        <v>332.160421111858</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>337.805497912983</v>
+        <v>337.815447110417</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>342.334613470337</v>
+        <v>342.299942696598</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>342.334613470337</v>
+        <v>342.299942696598</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>340.834656357123</v>
+        <v>340.824582759282</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>340.834656357123</v>
+        <v>340.824582759282</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0434450075551946</v>
+        <v>0.0434202624104853</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.0422337631062328</v>
+        <v>0.0421032080095638</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0444025584827203</v>
+        <v>0.0443767149100287</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.996798896771471</v>
+        <v>0.996803950349241</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.02616368551187</v>
+        <v>1.02608426861461</v>
       </c>
     </row>
     <row r="43">
@@ -3885,46 +3885,46 @@
         <v>358.827</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1.00708091014332</v>
+        <v>1.00702901889371</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>353.618867909348</v>
+        <v>353.618628542323</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>332.831328970627</v>
+        <v>332.847682817834</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>339.808029783673</v>
+        <v>339.819328987987</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>356.304043087198</v>
+        <v>356.322403096383</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>356.304043087198</v>
+        <v>356.322403096383</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>350.7056550844</v>
+        <v>350.707731237655</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>350.7056550844</v>
+        <v>350.707731237655</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0285498011761521</v>
+        <v>0.0285852771998991</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.0901230153046606</v>
+        <v>0.0900626394901185</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0289612530391685</v>
+        <v>0.0289977571405224</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.991761715538056</v>
+        <v>0.991768258033615</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.05370385705292</v>
+        <v>1.0536583228359</v>
       </c>
     </row>
     <row r="44">
@@ -3944,46 +3944,46 @@
         <v>338.369</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.972660334422507</v>
+        <v>0.972642844941382</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>347.369520718661</v>
+        <v>347.389522846085</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>333.207752794217</v>
+        <v>333.22438566644</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>341.236699880868</v>
+        <v>341.249716205773</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>347.879920692868</v>
+        <v>347.886176061258</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>347.879920692868</v>
+        <v>347.886176061258</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>347.325483953641</v>
+        <v>347.337900881847</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>347.325483953641</v>
+        <v>347.337900881847</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.00968494774185564</v>
+        <v>-0.00965511817291523</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0850931439152609</v>
+        <v>0.0851038449525507</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.00963819967472712</v>
+        <v>-0.00960865716851045</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>0.999873227895962</v>
+        <v>0.999851400342142</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.04236915570252</v>
+        <v>1.04235438888178</v>
       </c>
     </row>
     <row r="45">
@@ -4003,46 +4003,46 @@
         <v>336.904</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.999009449436976</v>
+        <v>0.998953769774407</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>341.226655636411</v>
+        <v>341.224341355698</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>333.258484784121</v>
+        <v>333.275160943942</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>342.014740704949</v>
+        <v>342.029815795838</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>337.23805134163</v>
+        <v>337.256848308489</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>337.23805134163</v>
+        <v>337.256848308489</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>343.465356254343</v>
+        <v>343.465955755292</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>343.465356254343</v>
+        <v>343.465955755292</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.0111760829865724</v>
+        <v>-0.0112100870223569</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0524636803551897</v>
+        <v>0.0524705807635177</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.0111138625803032</v>
+        <v>-0.0111474881282014</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.006560743661</v>
+        <v>1.00656932735422</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.03062749168062</v>
+        <v>1.03057772077129</v>
       </c>
     </row>
     <row r="46">
@@ -4062,46 +4062,46 @@
         <v>359.582</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.02297716712473</v>
+        <v>1.02309781600402</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>351.418105713276</v>
+        <v>351.404715017016</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>332.977377062815</v>
+        <v>332.993803555603</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>342.098600860358</v>
+        <v>342.116017089525</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>351.505401641244</v>
+        <v>351.463950342933</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>351.505401641244</v>
+        <v>351.463950342933</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>350.934200249855</v>
+        <v>350.922071231404</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>350.934200249855</v>
+        <v>350.922071231404</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0215124907952977</v>
+        <v>0.0214761826641925</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.0296317985989925</v>
+        <v>0.0296266436838959</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0217455526722208</v>
+        <v>0.0217084556742035</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.9986229922262</v>
+        <v>0.998626530137511</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.05392805765195</v>
+        <v>1.05383964351399</v>
       </c>
     </row>
     <row r="47">
@@ -4121,46 +4121,46 @@
         <v>362.479</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.997224264558529</v>
+        <v>0.997181496656875</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>358.521013274079</v>
+        <v>358.512887985223</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>332.360768981871</v>
+        <v>332.37659696129</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>341.42084550472</v>
+        <v>341.44084458074</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>363.487946375301</v>
+        <v>363.50353593126</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>363.487946375301</v>
+        <v>363.50353593126</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>356.415460529794</v>
+        <v>356.412352442498</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>356.415460529794</v>
+        <v>356.412352442498</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.0154983321522802</v>
+        <v>0.01552417439343</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.016280904977193</v>
+        <v>0.0162660263710495</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0156190541589745</v>
+        <v>0.0156453003706174</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.994127114823599</v>
+        <v>0.994140976201638</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.07237524338871</v>
+        <v>1.0723148251139</v>
       </c>
     </row>
     <row r="48">
@@ -4180,46 +4180,46 @@
         <v>340.80650444183</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.981640551790063</v>
+        <v>0.981646659610903</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>351.105788256621</v>
+        <v>351.105260215624</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>331.416579908226</v>
+        <v>331.431368462612</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>339.961073799564</v>
+        <v>339.983562429656</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>347.180547727327</v>
+        <v>347.17838756454</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>347.180547727327</v>
+        <v>347.17838756454</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>350.518002034241</v>
+        <v>350.52986770529</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>350.518002034241</v>
+        <v>350.52986770529</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.0166850082026214</v>
+        <v>-0.0166424365157913</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.00919171851215528</v>
+        <v>0.00918980282698545</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.0165465843899885</v>
+        <v>-0.0165047162279743</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.998325899936601</v>
+        <v>0.998361196554046</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.05763568657701</v>
+        <v>1.05762429588747</v>
       </c>
     </row>
     <row r="49">
@@ -4239,46 +4239,46 @@
         <v>345.764859332108</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.00447934384403</v>
+        <v>1.00437373858791</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>345.149317140619</v>
+        <v>345.243528334748</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>330.172183694686</v>
+        <v>330.185399698032</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>337.809220410771</v>
+        <v>337.833748253199</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>344.222966307007</v>
+        <v>344.25915976082</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>344.222966307007</v>
+        <v>344.25915976082</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>344.263985919549</v>
+        <v>344.378852440894</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>344.263985919549</v>
+        <v>344.378852440894</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.0180033021656045</v>
+        <v>-0.0177035508039987</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.00232521170086963</v>
+        <v>0.00265789569622732</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.0178422108947235</v>
+        <v>-0.0175477636318482</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.997434932717223</v>
+        <v>0.997495460963384</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.04268016180883</v>
+        <v>1.04298631240461</v>
       </c>
     </row>
     <row r="50">
@@ -4298,46 +4298,46 @@
         <v>374.704344280682</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.05318521070022</v>
+        <v>1.05336295567031</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.21630116425633</v>
+        <v>0.23310225507827</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>337.468157031726</v>
+        <v>337.592738173428</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>328.664806673945</v>
+        <v>328.675814192956</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>335.091317373863</v>
+        <v>335.116953793968</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>355.782003463148</v>
+        <v>355.721968637333</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>341.429463336854</v>
+        <v>341.818702677398</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>336.042319037731</v>
+        <v>336.230622674401</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>336.042319037731</v>
+        <v>336.230622674401</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0241716624514943</v>
+        <v>-0.0239450650844428</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.0424349670152434</v>
+        <v>-0.0418652736929593</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0238818674566174</v>
+        <v>-0.023660656595899</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.995774896196026</v>
+        <v>0.995965210903537</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>1.02244691921367</v>
+        <v>1.02298559296185</v>
       </c>
     </row>
     <row r="51">
@@ -4357,46 +4357,46 @@
         <v>298.598</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.954700577624946</v>
+        <v>0.95465148042799</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0.575362235882236</v>
+        <v>0.58293419514245</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>322.942465060398</v>
+        <v>322.957380027263</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>326.940456917829</v>
+        <v>326.948531572826</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>331.965465453841</v>
+        <v>331.990857852102</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>312.766124791541</v>
+        <v>312.78221018013</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>317.08738317021</v>
+        <v>317.025925581987</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>323.744816281688</v>
+        <v>323.805530576949</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>323.744816281688</v>
+        <v>323.805530576949</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>-0.0372815001488576</v>
+        <v>-0.0376541801984223</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.0916644979416494</v>
+        <v>-0.0914862283590731</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.0365951014481073</v>
+        <v>-0.0369540763379058</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00248450206491</v>
+        <v>1.00262619962304</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.990225618859572</v>
+        <v>0.990386863092009</v>
       </c>
     </row>
     <row r="52">
@@ -4416,46 +4416,46 @@
         <v>316.88</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.992187756798313</v>
+        <v>0.992260665954157</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>321.781975576812</v>
+        <v>321.742621226203</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>325.053120408578</v>
+        <v>325.057685768386</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>328.621456145523</v>
+        <v>328.646647972156</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>319.375035449479</v>
+        <v>319.351568466426</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>319.375035449479</v>
+        <v>319.351568466426</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>322.139343265685</v>
+        <v>322.12679435753</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>322.139343265685</v>
+        <v>322.12679435753</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>-0.00497140640116124</v>
+        <v>-0.00519788198944505</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>-0.0809620578796499</v>
+        <v>-0.081028967755865</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.00495906941288615</v>
+        <v>-0.00518439637651591</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00111058951712</v>
+        <v>1.00119403866937</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.991035997011104</v>
+        <v>0.99098347296749</v>
       </c>
     </row>
     <row r="53">
@@ -4475,46 +4475,46 @@
         <v>335.545</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.00849086828036</v>
+        <v>1.00831450435201</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>326.597743929248</v>
+        <v>326.653862573589</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>323.05062495734</v>
+        <v>323.051209081639</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>325.174690532308</v>
+        <v>325.200687037333</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>332.719918993574</v>
+        <v>332.778114915283</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>332.719918993574</v>
+        <v>332.778114915283</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>324.434925600605</v>
+        <v>324.471545004176</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>324.434925600605</v>
+        <v>324.471545004176</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.00710078359420155</v>
+        <v>0.00725260422669096</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.0575984161281899</v>
+        <v>-0.0578064166705324</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.00712605393569277</v>
+        <v>0.00727896805766348</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.993377730346137</v>
+        <v>0.993319174148994</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.004285088888</v>
+        <v>1.0043966277872</v>
       </c>
     </row>
     <row r="54">
@@ -4534,46 +4534,46 @@
         <v>315.165</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.00715881523882</v>
+        <v>1.00698648343784</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>313.730055460354</v>
+        <v>313.743474297087</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>320.977249572164</v>
+        <v>320.973467491271</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>321.694337594114</v>
+        <v>321.722862533311</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>312.924828965795</v>
+        <v>312.978381719713</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>312.924828965795</v>
+        <v>312.978381719713</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>314.089895905874</v>
+        <v>314.099653741208</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>314.089895905874</v>
+        <v>314.099653741208</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0324057409652828</v>
+        <v>-0.0324875394001422</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.0653263648302352</v>
+        <v>-0.0658208010833802</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0318863010065269</v>
+        <v>-0.0319654879531421</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.00114697472957</v>
+        <v>1.0011352569003</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.97854254880846</v>
+        <v>0.978584479883059</v>
       </c>
     </row>
     <row r="55">
@@ -4593,46 +4593,46 @@
         <v>293.215</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.984636802460036</v>
+        <v>0.985054489133324</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>302.517392668691</v>
+        <v>302.443308257692</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>318.88331656987</v>
+        <v>318.874906292117</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>318.287292453167</v>
+        <v>318.320949085155</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>297.790006698334</v>
+        <v>297.663736610122</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>297.790006698334</v>
+        <v>297.663736610122</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>305.663529478081</v>
+        <v>305.607892503161</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>305.663529478081</v>
+        <v>305.607892503161</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.0271943175229897</v>
+        <v>-0.0274074209473925</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0558504287768278</v>
+        <v>-0.0561992812209365</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0268278812455612</v>
+        <v>-0.0270352454608042</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>1.010399854308</v>
+        <v>1.01046339647486</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.958543497245353</v>
+        <v>0.958394299685649</v>
       </c>
     </row>
     <row r="56">
@@ -4652,46 +4652,46 @@
         <v>315.244</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>1.00348472696053</v>
+        <v>1.00355999166466</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>312.545021874654</v>
+        <v>312.514744131066</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>316.814115504403</v>
+        <v>316.800973850403</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>315.016602688548</v>
+        <v>315.058998913862</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>314.14927554986</v>
+        <v>314.125715072686</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>314.14927554986</v>
+        <v>314.125715072686</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>312.635630508297</v>
+        <v>312.619451370543</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>312.635630508297</v>
+        <v>312.619451370543</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.0225534725394035</v>
+        <v>0.0226837573127472</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0295018691633385</v>
+        <v>-0.0295142880180137</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0228097249355246</v>
+        <v>0.0229429901497371</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00028990586092</v>
+        <v>1.00033504735838</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.986810925424036</v>
+        <v>0.986800790322588</v>
       </c>
     </row>
     <row r="57">
@@ -4711,46 +4711,46 @@
         <v>327.515</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.00943442245214</v>
+        <v>1.0090964298445</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>320.325056028325</v>
+        <v>320.438863242232</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>314.801752611033</v>
+        <v>314.783861551303</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>311.842829450569</v>
+        <v>311.897778178056</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>324.453964235134</v>
+        <v>324.562638726677</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>324.453964235134</v>
+        <v>324.562638726677</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>319.01525317118</v>
+        <v>319.090927921055</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>319.01525317118</v>
+        <v>319.090927921055</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0202005245807517</v>
+        <v>0.0204894621479735</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.0167049599219078</v>
+        <v>-0.0165827086102482</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0204059359853208</v>
+        <v>0.0207008121923986</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>0.995911019658015</v>
+        <v>0.995793471155345</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.01338461595337</v>
+        <v>1.01368261494896</v>
       </c>
     </row>
     <row r="58">
@@ -4770,46 +4770,46 @@
         <v>324.057</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.03531328063568</v>
+        <v>1.03495316597564</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>317.708625774384</v>
+        <v>317.730168326777</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>312.876668600063</v>
+        <v>312.854088743256</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>308.722197253844</v>
+        <v>308.793386617152</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>313.003808664591</v>
+        <v>313.11271915818</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>313.003808664591</v>
+        <v>313.11271915818</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>317.697980949052</v>
+        <v>317.716034922309</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>317.697980949052</v>
+        <v>317.716034922309</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>-0.00413773118237594</v>
+        <v>-0.00431809077259593</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.0114874279313317</v>
+        <v>0.0115134835012607</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>-0.00412918256739514</v>
+        <v>-0.00430878122328249</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.999966495006845</v>
+        <v>0.999955517587321</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.01540962568594</v>
+        <v>1.01554061894663</v>
       </c>
     </row>
     <row r="59">
@@ -4829,46 +4829,46 @@
         <v>304.316</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.950006789490143</v>
+        <v>0.950761508011865</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>321.253344204704</v>
+        <v>321.117719385175</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>311.075336814057</v>
+        <v>311.048286510437</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>305.673986286911</v>
+        <v>305.765248273311</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>320.330342231894</v>
+        <v>320.076062646199</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>320.330342231894</v>
+        <v>320.076062646199</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>319.138615800475</v>
+        <v>319.033089953666</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>319.138615800475</v>
+        <v>319.033089953666</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.00452435464994482</v>
+        <v>0.00413681576671295</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.0440847043329096</v>
+        <v>0.0439294853956256</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.00453460499534653</v>
+        <v>0.00414538420032629</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.993417256372961</v>
+        <v>0.993508208031933</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.02592066304259</v>
+        <v>1.02567062346753</v>
       </c>
     </row>
     <row r="60">
@@ -4888,46 +4888,46 @@
         <v>326.08</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1.00987961913388</v>
+        <v>1.00994985398977</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>314.189569651447</v>
+        <v>314.122630069422</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>309.434310058123</v>
+        <v>309.403247581028</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>302.738884795365</v>
+        <v>302.854383851398</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>322.889970073524</v>
+        <v>322.867515364087</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>322.889970073524</v>
+        <v>322.867515364087</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>312.669742971183</v>
+        <v>312.631661032187</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>312.669742971183</v>
+        <v>312.631661032187</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>-0.020478041476182</v>
+        <v>-0.0202691319164252</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.000109112524476984</v>
+        <v>0.0000390559883305386</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.0202697903325378</v>
+        <v>-0.0200650939449841</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.995162708036585</v>
+        <v>0.995253544652593</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.01045596046687</v>
+        <v>1.0104343230926</v>
       </c>
     </row>
     <row r="61">
@@ -4947,46 +4947,46 @@
         <v>287.232</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.00935911290463</v>
+        <v>1.00883846786365</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>293.170911664231</v>
+        <v>293.353571500036</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>307.995925515754</v>
+        <v>307.961407043297</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>300.03086280452</v>
+        <v>300.173368128141</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>284.568689505793</v>
+        <v>284.715550754376</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>284.568689505793</v>
+        <v>284.715550754376</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>294.942753645792</v>
+        <v>295.061067095897</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>294.942753645792</v>
+        <v>295.061067095897</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0583662171461062</v>
+        <v>-0.0578433537295417</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>-0.0754587728520656</v>
+        <v>-0.075307251703197</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0566955700827935</v>
+        <v>-0.0562022217400461</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1.00604371685957</v>
+        <v>1.00582060612772</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.957619011199243</v>
+        <v>0.958110530565327</v>
       </c>
     </row>
     <row r="62">
@@ -5006,46 +5006,46 @@
         <v>285.117</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.99087150887054</v>
+        <v>0.990176439561045</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>286.991556617464</v>
+        <v>287.035695654253</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>306.81093015795</v>
+        <v>306.773615152875</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>297.764645766087</v>
+        <v>297.934841537834</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>287.743665498057</v>
+        <v>287.94565151075</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>287.743665498057</v>
+        <v>287.94565151075</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>289.423502579045</v>
+        <v>289.462134558327</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>289.423502579045</v>
+        <v>289.462134558327</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.0188902597711126</v>
+        <v>-0.0191578495619073</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0889979794191428</v>
+        <v>-0.088928153629046</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0187129570010546</v>
+        <v>-0.0189755042665496</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.00847392860698</v>
+        <v>1.00845343955755</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.943328526236162</v>
+        <v>0.94356919976341</v>
       </c>
     </row>
     <row r="63">
@@ -5065,46 +5065,46 @@
         <v>294.649</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.989957633378256</v>
+        <v>0.991277520640611</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>293.83682372037</v>
+        <v>293.633560542913</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>305.915428933209</v>
+        <v>305.876193505215</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>296.077648265278</v>
+        <v>296.2741554279</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>297.637989814274</v>
+        <v>297.24168445743</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>297.637989814274</v>
+        <v>297.24168445743</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>293.184351501129</v>
+        <v>293.027317246278</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>293.184351501129</v>
+        <v>293.027317246278</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.0129105748736947</v>
+        <v>0.0122413451339646</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.0813259913227585</v>
+        <v>-0.081514342951588</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.0129942761682122</v>
+        <v>0.0123165770659144</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.997779474298081</v>
+        <v>0.997935374636626</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.958383670034308</v>
+        <v>0.95799321250963</v>
       </c>
     </row>
     <row r="64">
@@ -5124,46 +5124,46 @@
         <v>293.701</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.01374868806807</v>
+        <v>1.01387996406552</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>293.052272336192</v>
+        <v>292.962147455923</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>305.333609749614</v>
+        <v>305.293696218493</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>295.057179985969</v>
+        <v>295.276715195628</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>289.71776087791</v>
+        <v>289.680248559503</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>289.71776087791</v>
+        <v>289.680248559503</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>292.072712680828</v>
+        <v>292.019833941432</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>292.072712680828</v>
+        <v>292.019833941432</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.00379880987404571</v>
+        <v>-0.0034441131751216</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0658747152654733</v>
+        <v>-0.0659300693432757</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.00379160352388885</v>
+        <v>-0.00343818902044468</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.996657389319813</v>
+        <v>0.996783497381234</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.956569153721201</v>
+        <v>0.956521007667446</v>
       </c>
     </row>
     <row r="65">
@@ -5183,46 +5183,46 @@
         <v>292.276</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00363529469042</v>
+        <v>1.00274068069908</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>289.443240678551</v>
+        <v>289.47863915054</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>305.084487115799</v>
+        <v>305.045280842727</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>294.798352319778</v>
+        <v>295.032763883455</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>291.217339153218</v>
+        <v>291.477154189291</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>291.217339153218</v>
+        <v>291.477154189291</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>289.027663488048</v>
+        <v>289.19660782649</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>289.027663488048</v>
+        <v>289.19660782649</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>-0.0104803823558088</v>
+        <v>-0.0097149637099555</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>-0.0200550448676137</v>
+        <v>-0.0198754085963544</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>-0.0104256545051087</v>
+        <v>-0.0096679258968001</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.998564218706476</v>
+        <v>0.999025726648165</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.947369255711594</v>
+        <v>0.948044851005552</v>
       </c>
     </row>
     <row r="66">
@@ -5242,46 +5242,46 @@
         <v>280.81</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.988913105505967</v>
+        <v>0.98823912608245</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>283.012474645628</v>
+        <v>283.861814476793</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>305.177315634853</v>
+        <v>305.140346523153</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>295.369579562784</v>
+        <v>295.604562200635</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>283.958214767845</v>
+        <v>284.151874367876</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>283.958214767845</v>
+        <v>284.151874367876</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>283.898157780291</v>
+        <v>284.49244495056</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>283.898157780291</v>
+        <v>284.49244495056</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.017906830459455</v>
+        <v>-0.0164000630288025</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>-0.0190908642508928</v>
+        <v>-0.0171687036556605</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.0177474558865853</v>
+        <v>-0.0162663141566058</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.00312948443623</v>
+        <v>1.00222161080358</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.930272806121596</v>
+        <v>0.932333099153028</v>
       </c>
     </row>
     <row r="67">
@@ -5301,46 +5301,46 @@
         <v>256.914</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.997981275562973</v>
+        <v>0.999498898262362</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>276.458862432255</v>
+        <v>278.188876877196</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>305.612682942389</v>
+        <v>305.579812325844</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>296.821370945234</v>
+        <v>297.036592807954</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>257.433687676226</v>
+        <v>257.04280459603</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>276.458862432255</v>
+        <v>278.188876877196</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>278.742142814642</v>
+        <v>280.008591390031</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>278.742142814642</v>
+        <v>280.008591390031</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>-0.018328439318892</v>
+        <v>-0.015886411445375</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.0492598210393628</v>
+        <v>-0.0444283692680615</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>-0.0181614949739813</v>
+        <v>-0.0157608879958401</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00825902400921</v>
+        <v>1.00654129141777</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.912076488877875</v>
+        <v>0.916319010928164</v>
       </c>
     </row>
     <row r="68">
@@ -5360,46 +5360,46 @@
         <v>306.755</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1.00930777377204</v>
+        <v>1.00963239554368</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>278.092631626211</v>
+        <v>279.504737437857</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>306.377914735978</v>
+        <v>306.351479521779</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>299.147178873399</v>
+        <v>299.316074927033</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>303.926124390758</v>
+        <v>303.828404629206</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>278.092631626211</v>
+        <v>279.504737437857</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>279.773208228275</v>
+        <v>281.005480420285</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>279.773208228275</v>
+        <v>281.005480420285</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.00369216918749962</v>
+        <v>0.00355388618424828</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.0421111042509261</v>
+        <v>-0.0377178268081483</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.00369899364058113</v>
+        <v>0.00356020872539875</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00604322592884</v>
+        <v>1.00536929354466</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.91316375878258</v>
+        <v>0.91726496917508</v>
       </c>
     </row>
     <row r="69">
@@ -5419,46 +5419,46 @@
         <v>287.002</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.00193155967409</v>
+        <v>1.00062208999008</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>288.132754540035</v>
+        <v>288.570867925533</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>307.442115575372</v>
+        <v>307.426030047281</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>302.238643210985</v>
+        <v>302.335989199839</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>286.448707228422</v>
+        <v>286.823569928229</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>286.448707228422</v>
+        <v>286.823569928229</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>288.578542481714</v>
+        <v>289.172005542355</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>288.578542481714</v>
+        <v>289.172005542355</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0309879888479205</v>
+        <v>0.0286475135345528</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.00155390318322346</v>
+        <v>-0.0000850711366221502</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0314731146316725</v>
+        <v>0.0290618001821752</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00154716162829</v>
+        <v>1.00208315420452</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.938643496977129</v>
+        <v>0.940623035394504</v>
       </c>
     </row>
     <row r="70">
@@ -5478,46 +5478,46 @@
         <v>300.125</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>0.989453117664166</v>
+        <v>0.988761981290533</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>302.608410369953</v>
+        <v>302.614508525676</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>308.75671171838</v>
+        <v>308.75736662487</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>305.882131085463</v>
+        <v>305.890259580892</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>303.324123843801</v>
+        <v>303.536144875106</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>303.324123843801</v>
+        <v>303.536144875106</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>302.686693948455</v>
+        <v>302.749658691107</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>302.686693948455</v>
+        <v>302.749658691107</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0477309639768707</v>
+        <v>0.0458845691172645</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.066180549796679</v>
+        <v>0.0641746874639169</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0488884285900595</v>
+        <v>0.0469535532088832</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00025869597744</v>
+        <v>1.000446608347</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.980340450783589</v>
+        <v>0.980542300903022</v>
       </c>
     </row>
     <row r="71">
@@ -5537,46 +5537,46 @@
         <v>318.876</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1.0038601599674</v>
+        <v>1.00559195646752</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>316.079610208957</v>
+        <v>315.703405108225</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>310.260008542592</v>
+        <v>310.286515439491</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>309.785059944391</v>
+        <v>309.695247928357</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>317.649820877796</v>
+        <v>317.102775085989</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>317.649820877796</v>
+        <v>317.102775085989</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>316.211111532124</v>
+        <v>315.936884834576</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>316.211111532124</v>
+        <v>315.936884834576</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0437118078159501</v>
+        <v>0.04263620703135</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.13442161396599</v>
+        <v>0.12831139668318</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0446812425324927</v>
+        <v>0.043558186656532</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>1.0004160386147</v>
+        <v>1.00073955403259</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.01918101858337</v>
+        <v>1.01821016742246</v>
       </c>
     </row>
     <row r="72">
@@ -5596,46 +5596,46 @@
         <v>327.007</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1.00241039124074</v>
+        <v>1.00307097472733</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>330.824698269629</v>
+        <v>330.65845435057</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>311.88691605818</v>
+        <v>311.951239412498</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>313.642057199119</v>
+        <v>313.455545526867</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>326.220680529104</v>
+        <v>326.00584429122</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>326.220680529104</v>
+        <v>326.00584429122</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>329.326885200818</v>
+        <v>329.22507156335</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>329.326885200818</v>
+        <v>329.22507156335</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0406407645450843</v>
+        <v>0.0411991628636232</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.177120880467265</v>
+        <v>0.171596621784549</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0414779025479053</v>
+        <v>0.0420596244586364</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.995472487161192</v>
+        <v>0.995665065361672</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.05591760424918</v>
+        <v>1.05537350062588</v>
       </c>
     </row>
     <row r="73">
@@ -5655,46 +5655,46 @@
         <v>348.079</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.00248444841581</v>
+        <v>1.00084298265194</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>340.463475667878</v>
+        <v>340.982825597814</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>313.576962908022</v>
+        <v>313.693561627521</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>317.187074065662</v>
+        <v>316.912781296846</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>347.216358867269</v>
+        <v>347.78582258497</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>347.216358867269</v>
+        <v>347.78582258497</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>339.191893344584</v>
+        <v>339.549137892855</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>339.191893344584</v>
+        <v>339.549137892855</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0295151747559138</v>
+        <v>0.030877047621541</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.175388476314301</v>
+        <v>0.174211650453559</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0299550646700153</v>
+        <v>0.0313586880867858</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.996265143211618</v>
+        <v>0.995795425466236</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.08168626355398</v>
+        <v>1.08242303772888</v>
       </c>
     </row>
     <row r="74">
@@ -5714,46 +5714,46 @@
         <v>333.69</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.992787643919317</v>
+        <v>0.991298585136873</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>341.690322729695</v>
+        <v>341.862815384477</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>315.278636337793</v>
+        <v>315.464289296242</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>320.216954876687</v>
+        <v>319.871335652536</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>336.114175114692</v>
+        <v>336.619062110258</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>336.114175114692</v>
+        <v>336.619062110258</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>339.950998862202</v>
+        <v>340.089050433978</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>339.950998862202</v>
+        <v>340.089050433978</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.00223548193600414</v>
+        <v>0.00158882377116101</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.123111803917266</v>
+        <v>0.123334215814815</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.00223798248871354</v>
+        <v>0.0015900866203753</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.994909648439565</v>
+        <v>0.994811471529876</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.07825573851434</v>
+        <v>1.07805879135376</v>
       </c>
     </row>
     <row r="75">
@@ -5773,46 +5773,46 @@
         <v>342.148</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1.00525536901612</v>
+        <v>1.00829789985674</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>338.538396167047</v>
+        <v>338.082808090575</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>316.961448215641</v>
+        <v>317.235537293437</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>322.678690388869</v>
+        <v>322.289954214624</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>340.359286352156</v>
+        <v>339.332254930426</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>340.359286352156</v>
+        <v>339.332254930426</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>337.071944394972</v>
+        <v>336.655184883951</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>337.071944394972</v>
+        <v>336.655184883951</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.00850509381099415</v>
+        <v>-0.0101482800775512</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0659712201818958</v>
+        <v>0.0655773385251397</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.00846902782126402</v>
+        <v>-0.0100969600333941</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.995668285226496</v>
+        <v>0.995777297240617</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.06344776720495</v>
+        <v>1.06121523381711</v>
       </c>
     </row>
     <row r="76">
@@ -5832,46 +5832,46 @@
         <v>329.742</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.994831788305887</v>
+        <v>0.995185666683821</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>326.519448610868</v>
+        <v>325.855104336792</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>318.60793262145</v>
+        <v>318.992642226897</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>324.598757460072</v>
+        <v>324.211121236082</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>331.455029760883</v>
+        <v>331.337167564695</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>331.455029760883</v>
+        <v>331.337167564695</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>327.295198131455</v>
+        <v>326.779729310392</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>327.295198131455</v>
+        <v>326.779729310392</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0294338821732627</v>
+        <v>-0.0297728830324682</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>-0.00616921108072988</v>
+        <v>-0.00742756996405403</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0290049243969724</v>
+        <v>-0.0293340367740451</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00237581413263</v>
+        <v>1.00283753411039</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.02726631894733</v>
+        <v>1.02441149435026</v>
       </c>
     </row>
     <row r="77">
@@ -5891,46 +5891,46 @@
         <v>305.407</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.00816563376691</v>
+        <v>1.00638839188027</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>0.763355862631742</v>
+        <v>0.864448057580595</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>315.518031907724</v>
+        <v>315.596530575838</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>320.215247283938</v>
+        <v>320.73475115293</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>326.092035927977</v>
+        <v>325.762532473463</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>302.933357149735</v>
+        <v>303.468325414006</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>305.911446651899</v>
+        <v>305.112327181753</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>317.479892239147</v>
+        <v>317.289156117427</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>317.479892239147</v>
+        <v>317.289156117427</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0304480254490249</v>
+        <v>-0.029472810731639</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.0640109670409472</v>
+        <v>-0.0655574680989232</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0299891533647433</v>
+        <v>-0.0290427230997269</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00621790241135</v>
+        <v>1.00536325775984</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.991457761402706</v>
+        <v>0.989257182069864</v>
       </c>
     </row>
     <row r="78">
@@ -5950,46 +5950,46 @@
         <v>324.625</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.993407833957254</v>
+        <v>0.990934524850621</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0.980875203289263</v>
+        <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>319.587642695332</v>
+        <v>319.495517531184</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>321.788579367538</v>
+        <v>322.468726456185</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>327.307686991769</v>
+        <v>327.107513914963</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>326.779182631218</v>
+        <v>327.594802541506</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>326.641645891907</v>
+        <v>327.594802541506</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>320.817397729792</v>
+        <v>320.713521130043</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>320.817397729792</v>
+        <v>320.713521130043</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.0104576220496535</v>
+        <v>0.0107347445974525</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.0562834090690997</v>
+        <v>-0.0569719292026902</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0105124940893295</v>
+        <v>0.0107925686919756</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.00384794300583</v>
+        <v>1.00381227132159</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>0.996981926332953</v>
+        <v>0.994556975042415</v>
       </c>
     </row>
     <row r="79">
@@ -6009,46 +6009,46 @@
         <v>325.422</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1.0041569023521</v>
+        <v>1.00889731389025</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>325.228676106742</v>
+        <v>324.696407277653</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>323.324176161285</v>
+        <v>324.191666506325</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>328.293968904253</v>
+        <v>328.306140522318</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>324.074852483455</v>
+        <v>322.552152255408</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>324.074852483455</v>
+        <v>322.552152255408</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>324.635181170563</v>
+        <v>324.138412915706</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>324.635181170563</v>
+        <v>324.138412915706</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0118299255110581</v>
+        <v>0.010622357811473</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>-0.0368964650758234</v>
+        <v>-0.037179798589943</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0119001758252102</v>
+        <v>0.0106789753472034</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.998175145736582</v>
+        <v>0.998281488955712</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.00405476950361</v>
+        <v>0.999835734239583</v>
       </c>
     </row>
     <row r="80">
@@ -6068,46 +6068,46 @@
         <v>321.243</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.992258289818959</v>
+        <v>0.991936056930613</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>327.076502794267</v>
+        <v>326.705821841906</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>324.821318120794</v>
+        <v>325.90387347057</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>329.095809712733</v>
+        <v>329.420923700399</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>323.749373823434</v>
+        <v>323.854544610501</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>323.749373823434</v>
+        <v>323.854544610501</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>326.80095433483</v>
+        <v>326.620290688741</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>326.80095433483</v>
+        <v>326.620290688741</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>0.00664925086511656</v>
+        <v>0.00762768071348227</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.00151008569464683</v>
+        <v>-0.000487908543127302</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>0.00667140621191487</v>
+        <v>0.00765684557627733</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.999157541256915</v>
+        <v>0.999738201319209</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>1.00609453906994</v>
+        <v>1.00219824701849</v>
       </c>
     </row>
     <row r="81">
@@ -6127,46 +6127,46 @@
         <v>338.9</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.00974221814172</v>
+        <v>1.00797120739085</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>329.78546481294</v>
+        <v>330.761107764557</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>326.279754874381</v>
+        <v>327.60462481973</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>329.737041882412</v>
+        <v>330.485604912739</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>335.630217208997</v>
+        <v>336.219921278553</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>335.630217208997</v>
+        <v>336.219921278553</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>329.849169773813</v>
+        <v>330.457232677339</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>329.849169773813</v>
+        <v>330.457232677339</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>0.00928420546189618</v>
+        <v>0.0116789433957613</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.0389608218883619</v>
+        <v>0.041501817210035</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>0.00932743738520214</v>
+        <v>0.0117474085290499</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>1.00019317091767</v>
+        <v>0.999081285314129</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>1.01093973759054</v>
+        <v>1.00870747126717</v>
       </c>
     </row>
     <row r="82">
@@ -6186,46 +6186,46 @@
         <v>335.07</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.03293329695514</v>
+        <v>1.02929168853944</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>330.345680317976</v>
+        <v>330.449526493662</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>327.698566085174</v>
+        <v>329.29191719408</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>330.214765699044</v>
+        <v>331.506093727426</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>324.386870853822</v>
+        <v>325.534543541746</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>324.386870853822</v>
+        <v>325.534543541746</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>329.673185772919</v>
+        <v>329.829380558735</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>329.673185772919</v>
+        <v>329.829380558735</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.000533671083597672</v>
+        <v>-0.00190175688934399</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>0.0276038273042334</v>
+        <v>0.028423682907325</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.000533528706513575</v>
+        <v>-0.00189994969550689</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.99796427020202</v>
+        <v>0.99812332630188</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>1.00602571964636</v>
+        <v>1.00163217903809</v>
       </c>
     </row>
     <row r="83">
@@ -6245,46 +6245,46 @@
         <v>322.848</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.965775746251054</v>
+        <v>0.972350224485813</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>329.109046432799</v>
+        <v>328.257920254098</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>329.082675455263</v>
+        <v>330.96913179418</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>330.555547325016</v>
+        <v>332.516971294374</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>334.288784175033</v>
+        <v>332.028513872895</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>334.288784175033</v>
+        <v>332.028513872895</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>330.354133987123</v>
+        <v>329.646529790851</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>330.354133987123</v>
+        <v>329.646529790851</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>0.00206339475781742</v>
+        <v>-0.000554533591599671</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>0.0176165528207353</v>
+        <v>0.0169931012668274</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.00206552502172053</v>
+        <v>-0.000554379866264165</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00378320671467</v>
+        <v>1.00423023924504</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>1.00386364469081</v>
+        <v>0.996003850884343</v>
       </c>
     </row>
     <row r="84">
@@ -6304,46 +6304,46 @@
         <v>325.352</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.990561495038912</v>
+        <v>0.988928242430197</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>333.655546523348</v>
+        <v>333.264805505063</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>330.434936877216</v>
+        <v>332.637301462058</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>330.756813448491</v>
+        <v>333.522961012568</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>328.452096744604</v>
+        <v>328.994547875869</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>328.452096744604</v>
+        <v>328.994547875869</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>332.932255191103</v>
+        <v>332.773716206409</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>332.932255191103</v>
+        <v>332.773716206409</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.00777381906067923</v>
+        <v>0.00944176952932836</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0.0187615757388224</v>
+        <v>0.0188396915105677</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.00780411364272537</v>
+        <v>0.0094864836512667</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.997832221463776</v>
+        <v>0.998526429162209</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>1.00755767031624</v>
+        <v>1.00041010056224</v>
       </c>
     </row>
     <row r="85">
@@ -6363,46 +6363,46 @@
         <v>344.852</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1.01267400907269</v>
+        <v>1.01106712553076</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>337.019440241972</v>
+        <v>336.869839318612</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>331.761458061553</v>
+        <v>334.298121153541</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>330.83465694188</v>
+        <v>334.526343993889</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>340.53604310017</v>
+        <v>341.077255201003</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>340.53604310017</v>
+        <v>341.077255201003</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>335.714502601069</v>
+        <v>336.478365444727</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>335.714502601069</v>
+        <v>336.478365444727</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.00832207270882169</v>
+        <v>0.0110711260514993</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.0177818632415483</v>
+        <v>0.0182206112379681</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.00835679741624662</v>
+        <v>0.0111326377592289</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.996128004841601</v>
+        <v>0.998837907618335</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>1.01191532181771</v>
+        <v>1.00652185625113</v>
       </c>
     </row>
     <row r="86">
@@ -6422,46 +6422,46 @@
         <v>332.281</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>0.996841522304065</v>
+        <v>0.992581638086184</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>331.804755147165</v>
+        <v>336.423556496238</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>333.06710744371</v>
+        <v>335.951009103465</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>330.793647094075</v>
+        <v>335.506759284531</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>333.333827459331</v>
+        <v>334.764403501033</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>333.333827459331</v>
+        <v>334.764403501033</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>331.183783460399</v>
+        <v>336.431187763475</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>331.183783460399</v>
+        <v>336.431187763475</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>-0.0135876457979288</v>
+        <v>-0.000140219977870711</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.00458210662155767</v>
+        <v>0.020015825132242</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>-0.0134957504235496</v>
+        <v>-0.00014021014750909</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>0.998128502750086</v>
+        <v>1.00002268351038</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.994345511936721</v>
+        <v>1.00142931155733</v>
       </c>
     </row>
     <row r="87">
@@ -6481,80 +6481,106 @@
         <v>317.285</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.999223901022196</v>
+        <v>1.00750944292085</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>322.668518037177</v>
+        <v>335.118688850828</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>334.362237574772</v>
+        <v>337.599620505446</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>330.686860124761</v>
+        <v>336.476600486725</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>317.531435822763</v>
+        <v>314.920125294474</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>317.531435822763</v>
+        <v>335.118688850828</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>322.798899701619</v>
+        <v>335.516969399917</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>322.798899701619</v>
+        <v>335.516969399917</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>-0.0256439305476353</v>
+        <v>-0.00272109959053658</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>-0.022870106677093</v>
+        <v>0.0178082857805004</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>-0.0253179176563836</v>
+        <v>-0.00271740075477322</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00040407308787</v>
+        <v>1.00118847609023</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.965416734984712</v>
+        <v>0.993831002823964</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
         <v>138</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88" s="2" t="n">
+        <v>355.915</v>
+      </c>
       <c r="C88" s="3" t="n">
-        <v>321.383742218219</v>
+        <v>355.915</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>355.791017282577</v>
+        <v>355.915</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>290.303871500369</v>
+        <v>355.915</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.989971577762586</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="11"/>
-      <c r="L88" s="12"/>
-      <c r="M88" s="13"/>
+        <v>0.987629225089268</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>337.066096396978</v>
+      </c>
+      <c r="I88" s="9" t="n">
+        <v>339.246868924596</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>337.444549423785</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>360.373094435141</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>337.066096396978</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>336.416960548261</v>
+      </c>
       <c r="N88" s="14" t="n">
-        <v>324.639362823498</v>
-      </c>
-      <c r="O88" s="15"/>
-      <c r="P88" s="16"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="18"/>
-      <c r="S88" s="19"/>
+        <v>336.416960548261</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>0.00267881006279969</v>
+      </c>
+      <c r="P88" s="16" t="n">
+        <v>0.0109481132806557</v>
+      </c>
+      <c r="Q88" s="17" t="n">
+        <v>0.00268240128049002</v>
+      </c>
+      <c r="R88" s="18" t="n">
+        <v>0.998074158582974</v>
+      </c>
+      <c r="S88" s="19" t="n">
+        <v>0.991658262358306</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
@@ -6562,16 +6588,16 @@
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3" t="n">
-        <v>320.77813521558</v>
+        <v>339.945234078288</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>359.042239318231</v>
+        <v>378.003507086034</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>286.591940346001</v>
+        <v>305.718756588784</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1.01445956228052</v>
+        <v>1.01292930858347</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="8"/>
@@ -6581,7 +6607,7 @@
       <c r="L89" s="12"/>
       <c r="M89" s="13"/>
       <c r="N89" s="14" t="n">
-        <v>316.205935793504</v>
+        <v>335.606079513766</v>
       </c>
       <c r="O89" s="15"/>
       <c r="P89" s="16"/>
@@ -6595,16 +6621,16 @@
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3" t="n">
-        <v>317.193261404224</v>
+        <v>336.679700552532</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>357.906133162785</v>
+        <v>379.177450186792</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>281.111598147684</v>
+        <v>298.945047255057</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>0.996891074649685</v>
+        <v>0.992364505303043</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -6614,7 +6640,7 @@
       <c r="L90" s="12"/>
       <c r="M90" s="13"/>
       <c r="N90" s="14" t="n">
-        <v>318.182466941725</v>
+        <v>339.270196337503</v>
       </c>
       <c r="O90" s="15"/>
       <c r="P90" s="16"/>
@@ -6628,16 +6654,16 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
-        <v>322.918460078139</v>
+        <v>343.242440761618</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>366.29021054451</v>
+        <v>390.849556552598</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>284.682278852674</v>
+        <v>301.43407140885</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0.997842287784937</v>
+        <v>1.0073298729474</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -6647,7 +6673,7 @@
       <c r="L91" s="12"/>
       <c r="M91" s="13"/>
       <c r="N91" s="14" t="n">
-        <v>323.616731853458</v>
+        <v>340.744824490618</v>
       </c>
       <c r="O91" s="15"/>
       <c r="P91" s="16"/>
@@ -6660,10 +6686,18 @@
         <v>142</v>
       </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
+      <c r="C92" s="3" t="n">
+        <v>339.945234078288</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>391.000874925807</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>295.556275147645</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>0.986443389410891</v>
+      </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
       <c r="I92" s="9"/>
@@ -6671,7 +6705,9 @@
       <c r="K92" s="11"/>
       <c r="L92" s="12"/>
       <c r="M92" s="13"/>
-      <c r="N92" s="14"/>
+      <c r="N92" s="14" t="n">
+        <v>344.617073546719</v>
+      </c>
       <c r="O92" s="15"/>
       <c r="P92" s="16"/>
       <c r="Q92" s="17"/>
@@ -7109,7 +7145,7 @@
         <v>162</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.176684721752862</v>
+        <v>0.18166587788623</v>
       </c>
     </row>
     <row r="6">
@@ -7117,7 +7153,7 @@
         <v>163</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0954410356808009</v>
+        <v>0.104693170072222</v>
       </c>
     </row>
     <row r="7">
@@ -7125,7 +7161,7 @@
         <v>164</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.165275036803515</v>
+        <v>0.181158701800193</v>
       </c>
     </row>
     <row r="8">
@@ -7133,7 +7169,7 @@
         <v>165</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.329922323785511</v>
+        <v>0.328873486551596</v>
       </c>
     </row>
     <row r="9">
@@ -7141,7 +7177,7 @@
         <v>166</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.470965011511414</v>
+        <v>0.468243527587803</v>
       </c>
     </row>
     <row r="10">
@@ -7149,7 +7185,7 @@
         <v>167</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.463788920706522</v>
+        <v>0.49620024218763</v>
       </c>
     </row>
     <row r="11">
@@ -7157,7 +7193,7 @@
         <v>168</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.360681642095544</v>
+        <v>0.389986909824501</v>
       </c>
     </row>
     <row r="12">
@@ -7165,7 +7201,7 @@
         <v>169</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.25223472552379</v>
+        <v>0.273040971195524</v>
       </c>
     </row>
     <row r="13">
@@ -7173,7 +7209,7 @@
         <v>170</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.171664445629389</v>
+        <v>0.168171626210785</v>
       </c>
     </row>
     <row r="14">
@@ -7231,237 +7267,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CD7ED26-BB90-4636-8127-5ADF66727A68}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5732F33-DF65-409F-94C3-26AF294D4650}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8A84C4-09D9-49F2-868E-ECAE0287FE40}"/>
 </file>
--- a/indicadores/GR-EPRIV-FOR_out.xlsx
+++ b/indicadores/GR-EPRIV-FOR_out.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correlograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlograma" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -55,10 +56,10 @@
     <t xml:space="preserve">Modelo</t>
   </si>
   <si>
-    <t xml:space="preserve">log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0 1 1)</t>
+    <t xml:space="preserve">niv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3 0 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -70,7 +71,7 @@
     <t xml:space="preserve">Regresores</t>
   </si>
   <si>
-    <t xml:space="preserve">easter[1]</t>
+    <t xml:space="preserve">const</t>
   </si>
   <si>
     <t xml:space="preserve">Resumen del correlograma</t>
@@ -106,13 +107,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">09/03/2026</t>
+    <t xml:space="preserve">07/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">vcorvalan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -494,6 +495,63 @@
   </si>
   <si>
     <t xml:space="preserve">2030T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de las series incluidas en la hoja Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original | serie de datos brutos transformados, se importa directo desde base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_normal | serie original con 4 forecasts obtenidos del mejor modelo ARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_optimista | serie original con 4 forecasts, intervalo y límite optimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_pesimista | serie original con 4 forecasts, intervalo y límite pesimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_d16 | salida D16 del X13-ARIMA-SEATS con los factores estacionales de la serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_c17 | salida C17 del X13-ARIMA-SEATS con pesos del irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_d12 | salida D12 del X13-ARIMA-SEATS con el componente tendencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_1600 | tendencia HP de largo plazo con un lambda de 1.600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_200 | suavizado con filtro HP usando lambda de 200, sirve para determinar PG automáticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_ajustada | serie ajustada por estacionalidad usando el mejor modelo (LOG o NIV según el caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_filtrada | serie ajustada por estacionalidad y corregida por irregularidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final | serie f_filtrada con o sin suavizado 2x2 según el caso (es la vieja española)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final_fct_normal | a_original_fct ajustada por D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_tctl | tasas de cambio trimestral logarítmicas de la serie g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_var_interanual | variaciones interanuales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_var_trimestral | variaciones trimestrales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_irregular | g_final/d_d12 componente irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_dt | g_final/d_hp_1600 desvíos respecto de la tendencia</t>
   </si>
   <si>
     <t xml:space="preserve">Coeficientes de correlación de TCTL del ICA-SFE y serie específica</t>
@@ -1060,7 +1118,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.49620024218763</v>
+        <v>0.510384249257591</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1076,7 +1134,7 @@
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -1118,7 +1176,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.21925200112787</v>
+        <v>0.260492081890234</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1188,7 +1246,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.793468451407221</v>
+        <v>0.317906197644644</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1218,7 +1276,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.173834291500104</v>
+        <v>0.307296559920668</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1478,40 +1536,40 @@
         <v>187.428</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.993331631911461</v>
+        <v>1.66220156240624</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>187.479153666739</v>
+        <v>185.763616817716</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>190.999394823529</v>
+        <v>189.989588472999</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>184.434725737315</v>
+        <v>182.652459219421</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>188.686229229742</v>
+        <v>185.765798437594</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>188.686229229742</v>
+        <v>185.765798437594</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>189.894833401763</v>
+        <v>187.510579325657</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>189.894833401763</v>
+        <v>187.510579325657</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>1.01288505781991</v>
+        <v>1.00940422316204</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.994216937583567</v>
+        <v>0.986951868429916</v>
       </c>
     </row>
     <row r="3">
@@ -1531,44 +1589,44 @@
         <v>193.778</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.00762281051611</v>
+        <v>2.77785889821579</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>194.341279635961</v>
+        <v>191.187053591071</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>196.835563599233</v>
+        <v>195.947833238304</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>190.937791867447</v>
+        <v>189.551624022892</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>192.312041745805</v>
+        <v>191.000141101784</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>192.312041745805</v>
+        <v>191.000141101784</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>193.955965060532</v>
+        <v>190.671485998139</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>193.955965060532</v>
+        <v>190.671485998139</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.0211607385680659</v>
+        <v>0.0167167117173488</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.0213862146010926</v>
+        <v>0.0168572177839197</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>0.998017330254537</v>
+        <v>0.997303334178501</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.9853705372848</v>
+        <v>0.97307269413003</v>
       </c>
     </row>
     <row r="4">
@@ -1588,44 +1646,44 @@
         <v>202.718</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1.00100957433084</v>
+        <v>-4.48183521396759</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>199.052087305517</v>
+        <v>194.919863351393</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>202.67028664644</v>
+        <v>201.903438134838</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>197.462115515041</v>
+        <v>196.466355522453</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>202.513547520776</v>
+        <v>207.199835213968</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>202.513547520776</v>
+        <v>194.919863351393</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>198.558942996997</v>
+        <v>194.328165278306</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>198.558942996997</v>
+        <v>194.328165278306</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.0234548490245913</v>
+        <v>0.0189963249573456</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0237320772012752</v>
+        <v>0.0191779030882593</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.997522536361232</v>
+        <v>0.996964403407052</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.979714127228647</v>
+        <v>0.96248071391695</v>
       </c>
     </row>
     <row r="5">
@@ -1645,44 +1703,44 @@
         <v>196.406</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.997508158531354</v>
+        <v>-0.0667933086518215</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>198.326514685869</v>
+        <v>197.623552074322</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>208.499291035497</v>
+        <v>207.850670986242</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>204.035825446951</v>
+        <v>203.41946299959</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>196.89663520063</v>
+        <v>196.472793308652</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>196.89663520063</v>
+        <v>196.472793308652</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>199.128950714108</v>
+        <v>198.144736388585</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>199.128950714108</v>
+        <v>198.144736388585</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.00286661030652121</v>
+        <v>0.0194494519480447</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.00287072296270119</v>
+        <v>0.0196398247511556</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>1.00404603504231</v>
+        <v>1.00263725810407</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.955058166985355</v>
+        <v>0.95330332804988</v>
       </c>
     </row>
     <row r="6">
@@ -1702,46 +1760,46 @@
         <v>206.403</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.03093774771214</v>
+        <v>1.68950441435661</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>202.733742849207</v>
+        <v>205.393981656429</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>214.318205874795</v>
+        <v>213.779434881919</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>210.71230759006</v>
+        <v>210.426023274934</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>200.208984934396</v>
+        <v>204.713495585643</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>200.208984934396</v>
+        <v>204.713495585643</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>202.978815824707</v>
+        <v>206.057529375965</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>202.978815824707</v>
+        <v>206.057529375965</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.0191490096474891</v>
+        <v>0.0391576431050139</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>0.0689012027792308</v>
+        <v>0.0989114860452578</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.0193335278310489</v>
+        <v>0.0399344092182305</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>1.00120884156754</v>
+        <v>1.00323060935956</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.947090868907735</v>
+        <v>0.963879100390461</v>
       </c>
     </row>
     <row r="7">
@@ -1761,46 +1819,46 @@
         <v>221.58</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.971950046334791</v>
+        <v>3.24966697607774</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.0439947273789287</v>
+        <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>213.985194671946</v>
+        <v>217.217005977974</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>220.11540861283</v>
+        <v>219.672521737724</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>217.509251920019</v>
+        <v>217.466379820659</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>227.974679188066</v>
+        <v>218.330333023922</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>214.600658229404</v>
+        <v>218.330333023922</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>212.435826772185</v>
+        <v>216.697937183028</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>212.435826772185</v>
+        <v>216.697937183028</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0455383330424504</v>
+        <v>0.0503489906511149</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.0952786458817358</v>
+        <v>0.136498916178495</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0465911228669575</v>
+        <v>0.0516380441874</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.992759462157481</v>
+        <v>0.997610367601702</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.965111111988744</v>
+        <v>0.986459004835173</v>
       </c>
     </row>
     <row r="8">
@@ -1820,46 +1878,46 @@
         <v>220.366</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1.00014974744415</v>
+        <v>-5.05158709862313</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>222.710821152538</v>
+        <v>225.431290800054</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>225.870458435008</v>
+        <v>225.50705725745</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>224.3918317992</v>
+        <v>224.492313470494</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>220.333005695535</v>
+        <v>225.417587098623</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>220.333005695535</v>
+        <v>225.417587098623</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>221.279536560669</v>
+        <v>224.599375140099</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>221.279536560669</v>
+        <v>224.599375140099</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.0407868224616896</v>
+        <v>0.0358138709316139</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.114427450210671</v>
+        <v>0.155773661622547</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0416300297499625</v>
+        <v>0.0364629126598335</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.993573349581929</v>
+        <v>0.996309670866884</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.979674535987802</v>
+        <v>0.995974928109165</v>
       </c>
     </row>
     <row r="9">
@@ -1879,46 +1937,46 @@
         <v>229.158</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.996982935970688</v>
+        <v>-0.0739933392257658</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>228.96605351843</v>
+        <v>229.346096096511</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>231.559467807749</v>
+        <v>231.259328276947</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>231.310677621522</v>
+        <v>231.459924824185</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>229.851476622201</v>
+        <v>229.231993339226</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>229.851476622201</v>
+        <v>229.231993339226</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>228.937496167864</v>
+        <v>229.181307422484</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>228.937496167864</v>
+        <v>229.181307422484</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0340222502430531</v>
+        <v>0.0201951655670093</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.149694684508996</v>
+        <v>0.156635859218749</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0346076267431761</v>
+        <v>0.0204004676305396</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.999875276923686</v>
+        <v>0.999281484721859</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.988676897279528</v>
+        <v>0.991014326341141</v>
       </c>
     </row>
     <row r="10">
@@ -1938,46 +1996,46 @@
         <v>234.538</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.995010794424017</v>
+        <v>1.69434408714024</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>235.264244986483</v>
+        <v>232.250964936114</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>237.155088289506</v>
+        <v>236.905565713213</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>238.196125650388</v>
+        <v>238.329940849618</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>235.714025731517</v>
+        <v>232.84365591286</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>235.714025731517</v>
+        <v>232.84365591286</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>235.173183350339</v>
+        <v>233.172003316667</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>235.173183350339</v>
+        <v>233.172003316667</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.026873169356262</v>
+        <v>0.0172629671146029</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.158609495256076</v>
+        <v>0.131586911785345</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0272375093064854</v>
+        <v>0.0174128332675332</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>0.999612938905574</v>
+        <v>1.00396570313844</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.991643000563633</v>
+        <v>0.984240292602218</v>
       </c>
     </row>
     <row r="11">
@@ -1997,46 +2055,46 @@
         <v>241.824</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1.01006959779305</v>
+        <v>4.05529189827914</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>239.734567269002</v>
+        <v>239.543029279208</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>242.628903944246</v>
+        <v>242.42073339891</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>244.971216144202</v>
+        <v>245.051948857253</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>239.413205316122</v>
+        <v>237.768708101721</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>239.413205316122</v>
+        <v>237.768708101721</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>240.776897354293</v>
+        <v>240.494060484996</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>240.776897354293</v>
+        <v>240.494060484996</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0235485744557919</v>
+        <v>0.0309189998317598</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.133410032633058</v>
+        <v>0.109812412666715</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.0238280314282502</v>
+        <v>0.0314019567708814</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.00434785061314</v>
+        <v>1.00397018944216</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.992366916884814</v>
+        <v>0.992052359190154</v>
       </c>
     </row>
     <row r="12">
@@ -2056,46 +2114,46 @@
         <v>247.933</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.997448765673096</v>
+        <v>-5.66216982368374</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>250.112864316663</v>
+        <v>252.649315478455</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>247.951598171833</v>
+        <v>247.777256473077</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>251.546578861774</v>
+        <v>251.548104732868</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>248.567153053411</v>
+        <v>253.595169823684</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>248.567153053411</v>
+        <v>253.595169823684</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>250.741218576126</v>
+        <v>252.676386034507</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>250.741218576126</v>
+        <v>252.676386034507</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>0.0405506379829162</v>
+        <v>0.04941417067669</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0.133142370385342</v>
+        <v>0.125009301013836</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>0.0413840419547045</v>
+        <v>0.0506554113018123</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>1.00251228284951</v>
+        <v>1.00010714676191</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.01125066514941</v>
+        <v>1.01977231337196</v>
       </c>
     </row>
     <row r="13">
@@ -2115,46 +2173,46 @@
         <v>265.114</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.995107815543756</v>
+        <v>-0.632496388938652</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>265.649147288424</v>
+        <v>266.220590618631</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>253.091844560491</v>
+        <v>252.94465255894</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>257.805053507774</v>
+        <v>257.704148158463</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>266.417362881563</v>
+        <v>265.746496388939</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>266.417362881563</v>
+        <v>265.746496388939</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>264.13902306394</v>
+        <v>264.403985269398</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>264.13902306394</v>
+        <v>264.403985269398</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.0520541614595812</v>
+        <v>0.0453686173541965</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.15376042581625</v>
+        <v>0.153689139149482</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.0534327964261143</v>
+        <v>0.0464135150060663</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0.99431534322659</v>
+        <v>0.993176315381873</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.04364889166078</v>
+        <v>1.0453037160285</v>
       </c>
     </row>
     <row r="14">
@@ -2174,46 +2232,46 @@
         <v>274.574</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.997891315448259</v>
+        <v>2.04622152396949</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>272.05795542196</v>
+        <v>270.117247426982</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>258.018701420246</v>
+        <v>257.89607547557</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>263.61458265783</v>
+        <v>263.41605414149</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>275.154213439226</v>
+        <v>272.527778476031</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>275.154213439226</v>
+        <v>272.527778476031</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>271.039059467428</v>
+        <v>269.147362053601</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>271.039059467428</v>
+        <v>269.147362053601</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.025787374315168</v>
+        <v>0.0177808631883466</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.15250835833463</v>
+        <v>0.154286784970822</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.0261227452250314</v>
+        <v>0.0179398838461913</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>0.996254856973576</v>
+        <v>0.996409391171353</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.05046284620267</v>
+        <v>1.04362721129929</v>
       </c>
     </row>
     <row r="15">
@@ -2233,46 +2291,46 @@
         <v>270.671</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.0121173632741</v>
+        <v>4.88360512659586</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>271.578412661917</v>
+        <v>267.676103274893</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>262.70955551007</v>
+        <v>262.612680194431</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>268.88617043444</v>
+        <v>268.620009430557</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>267.430448109699</v>
+        <v>265.787394873404</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>267.430448109699</v>
+        <v>265.787394873404</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>272.020501328227</v>
+        <v>268.576357434132</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>272.020501328227</v>
+        <v>268.576357434132</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.00361449461591371</v>
+        <v>-0.00212378518335524</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.12976163542784</v>
+        <v>0.116769191274426</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.00362103477899867</v>
+        <v>-0.00212153154729799</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>1.00162784906936</v>
+        <v>1.00336322199937</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.0354419762162</v>
+        <v>1.02270902241006</v>
       </c>
     </row>
     <row r="16">
@@ -2280,58 +2338,58 @@
         <v>66</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>276.7245</v>
+        <v>264.265</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>276.7245</v>
+        <v>264.265</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>276.7245</v>
+        <v>264.265</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>276.7245</v>
+        <v>264.265</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.995172400327895</v>
+        <v>-5.93786151369005</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>276.768065414446</v>
+        <v>271.60354860161</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>267.152503283952</v>
+        <v>267.084766501364</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>273.588519114007</v>
+        <v>273.297759395941</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>278.066895654284</v>
+        <v>270.20286151369</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>278.066895654284</v>
+        <v>270.20286151369</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>277.239324373446</v>
+        <v>272.730600642982</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>277.239324373446</v>
+        <v>272.730600642982</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0190036840873615</v>
+        <v>0.0153492383863812</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.105679097947251</v>
+        <v>0.0793671894837715</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0191854033785552</v>
+        <v>0.0154676429769833</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1.00170272158493</v>
+        <v>1.00414962192937</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.037756790468</v>
+        <v>1.0211387351498</v>
       </c>
     </row>
     <row r="17">
@@ -2351,46 +2409,46 @@
         <v>282.778</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.990836994798855</v>
+        <v>-1.95128467114375</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>283.821138785627</v>
+        <v>282.005527549452</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>271.338591753752</v>
+        <v>271.304618378883</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>277.683052361311</v>
+        <v>277.416886335137</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>285.393058075517</v>
+        <v>284.729284671144</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>285.393058075517</v>
+        <v>284.729284671144</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>283.331614740176</v>
+        <v>282.226794331557</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>283.331614740176</v>
+        <v>282.226794331557</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.0217368751017106</v>
+        <v>0.0342264857975161</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.0726609474571656</v>
+        <v>0.0674074902615396</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.021974842062896</v>
+        <v>0.034818951984805</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.998275237540286</v>
+        <v>1.0007846185996</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.04419947383418</v>
+        <v>1.04025798019192</v>
       </c>
     </row>
     <row r="18">
@@ -2410,46 +2468,46 @@
         <v>292.243</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.04004431984656</v>
+        <v>2.9972535297494</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.516686719710223</v>
+        <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>288.196458108905</v>
+        <v>292.540135013894</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>275.265689426565</v>
+        <v>275.266468618885</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>281.153585723835</v>
+        <v>280.929498056225</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>280.990910121133</v>
+        <v>289.245746470251</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>284.473447155389</v>
+        <v>289.245746470251</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>286.944882879299</v>
+        <v>290.986771147545</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>286.944882879299</v>
+        <v>290.986771147545</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.012672156424804</v>
+        <v>0.030566823231538</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0586846170552855</v>
+        <v>0.0811429431346025</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.0127527884328626</v>
+        <v>0.0310387850903213</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.995657215089254</v>
+        <v>0.994690082896572</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.04242880206779</v>
+        <v>1.0571093987856</v>
       </c>
     </row>
     <row r="19">
@@ -2469,46 +2527,46 @@
         <v>306.237</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.977858269253417</v>
+        <v>5.51069302146658</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>293.439579130903</v>
+        <v>296.25316002415</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>278.940448850933</v>
+        <v>278.972940429699</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>284.022484777631</v>
+        <v>283.824264358967</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>313.171151309901</v>
+        <v>300.726306978533</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>293.439579130903</v>
+        <v>300.726306978533</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>292.035055908265</v>
+        <v>295.678991885777</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>292.035055908265</v>
+        <v>295.678991885777</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.0175836979429241</v>
+        <v>0.0159965728062094</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0735773755371751</v>
+        <v>0.100912212491719</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0177392012636328</v>
+        <v>0.0161252029421413</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.995213586296715</v>
+        <v>0.998061900374915</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.04694409545576</v>
+        <v>1.05988412865544</v>
       </c>
     </row>
     <row r="20">
@@ -2528,46 +2586,46 @@
         <v>280.597</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.992271258575254</v>
+        <v>-6.16061833467602</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>0.400192782926635</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>296.787618215864</v>
+        <v>295.527083975286</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>282.375277423982</v>
+        <v>282.435394068312</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>286.328714405909</v>
+        <v>286.131436285195</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>282.78255323337</v>
+        <v>286.757618334676</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>296.787618215864</v>
+        <v>292.017607115791</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>295.392231771356</v>
+        <v>294.672937293866</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>295.392231771356</v>
+        <v>294.672937293866</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.0114302228877506</v>
+        <v>-0.00340832481813555</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0654773901174914</v>
+        <v>0.0804542526550132</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.0114957974913317</v>
+        <v>-0.00340252307238564</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.995298367051508</v>
+        <v>0.997109751600664</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.04609806660882</v>
+        <v>1.04332864606408</v>
       </c>
     </row>
     <row r="21">
@@ -2587,46 +2645,46 @@
         <v>290.531</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.986341689470931</v>
+        <v>-3.3992279653489</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>292.535160381584</v>
+        <v>290.169536376359</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>285.591644499261</v>
+        <v>285.678785645805</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>288.158324963647</v>
+        <v>287.96577508984</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>294.554111522792</v>
+        <v>293.930227965349</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>294.554111522792</v>
+        <v>293.930227965349</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>292.8457140431</v>
+        <v>290.931622099677</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>292.8457140431</v>
+        <v>290.931622099677</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0086581753334755</v>
+        <v>-0.0127777901942392</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0335793776901601</v>
+        <v>0.0308433782438604</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.00862080127492049</v>
+        <v>-0.0126965008342705</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.00106159430925</v>
+        <v>1.00262634642091</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.02540014627024</v>
+        <v>1.01838721220408</v>
       </c>
     </row>
     <row r="22">
@@ -2646,46 +2704,46 @@
         <v>288.02</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.0088725054267</v>
+        <v>4.1715746477788</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>288.57124831052</v>
+        <v>287.079906873757</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>288.620027143316</v>
+        <v>288.734060156412</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>289.64966132487</v>
+        <v>289.471472881983</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>285.48701491095</v>
+        <v>283.848425352221</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>285.48701491095</v>
+        <v>283.848425352221</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>288.62456493328</v>
+        <v>287.261127596749</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>288.62456493328</v>
+        <v>287.261127596749</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0145191368005445</v>
+        <v>-0.0126966096094819</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>0.00585367488392374</v>
+        <v>-0.0128034808458938</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0144142424061505</v>
+        <v>-0.0126163477054805</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>1.00018476068934</v>
+        <v>1.00063125533572</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.00001572236691</v>
+        <v>0.994898653249065</v>
       </c>
     </row>
     <row r="23">
@@ -2705,46 +2763,46 @@
         <v>293.355</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.01517416968933</v>
+        <v>5.93756828279724</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>286.754833044661</v>
+        <v>286.462316524264</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>291.496503964579</v>
+        <v>291.637319745816</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>290.973047296402</v>
+        <v>290.822544035086</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>288.970118388428</v>
+        <v>287.417431717203</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>288.970118388428</v>
+        <v>287.417431717203</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>286.746537650574</v>
+        <v>286.423770717413</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>286.746537650574</v>
+        <v>286.423770717413</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.00652807881292354</v>
+        <v>-0.00291922439112635</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0181091898068287</v>
+        <v>-0.0313015852405906</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.00650681719742152</v>
+        <v>-0.00291496759878829</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.99997107147594</v>
+        <v>0.99986544196347</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.983704894400441</v>
+        <v>0.982123176029229</v>
       </c>
     </row>
     <row r="24">
@@ -2764,46 +2822,46 @@
         <v>280.514</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.989261846741027</v>
+        <v>-6.49779408302356</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>282.835031588636</v>
+        <v>284.552908889156</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>294.255195438841</v>
+        <v>294.42161303795</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>292.277993452995</v>
+        <v>292.164887684958</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>283.558898914489</v>
+        <v>287.011794083024</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>283.558898914489</v>
+        <v>287.011794083024</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>283.516706563085</v>
+        <v>284.854624940801</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>283.516706563085</v>
+        <v>284.854624940801</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.0113276303761769</v>
+        <v>-0.00549346775477592</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0402025643567446</v>
+        <v>-0.0333193554970864</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.0112637143379372</v>
+        <v>-0.00547840625336815</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.00241015043512</v>
+        <v>1.00106031617397</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.963506204674686</v>
+        <v>0.967505822692725</v>
       </c>
     </row>
     <row r="25">
@@ -2823,46 +2881,46 @@
         <v>273.279</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.983092566143439</v>
+        <v>-4.55980255150752</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1</v>
+        <v>0.968569708328098</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>281.474969589252</v>
+        <v>282.251021499218</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>296.928643050905</v>
+        <v>297.117351226727</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>293.703995724862</v>
+        <v>293.627377405823</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>277.978910034935</v>
+        <v>277.838802551508</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>277.978910034935</v>
+        <v>277.977479879954</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>282.582701965151</v>
+        <v>283.065060118325</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>282.582701965151</v>
+        <v>283.065060118325</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.00329979304470757</v>
+        <v>-0.00630219656992552</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.0350457991556549</v>
+        <v>-0.0270392125977208</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.00329435471107498</v>
+        <v>-0.00628237938158249</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.00393545606387</v>
+        <v>1.00288409450135</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.951685560078168</v>
+        <v>0.952704575985267</v>
       </c>
     </row>
     <row r="26">
@@ -2882,46 +2940,46 @@
         <v>294.75</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.01353411431669</v>
+        <v>5.45651336963402</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>287.487244398286</v>
+        <v>285.985302508958</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>299.542703100247</v>
+        <v>299.750314369214</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>295.346954569523</v>
+        <v>295.313121303893</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>290.814088876245</v>
+        <v>289.293486630366</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>290.814088876245</v>
+        <v>289.293486630366</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>288.160614700763</v>
+        <v>287.144641472812</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>288.160614700763</v>
+        <v>287.144641472812</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0195467565553114</v>
+        <v>0.014309300430313</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>-0.00160745234081106</v>
+        <v>-0.000405506045704995</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0197390452310831</v>
+        <v>0.0144121685409784</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.00234226149367</v>
+        <v>1.00405384106695</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.96200178378014</v>
+        <v>0.957946089488084</v>
       </c>
     </row>
     <row r="27">
@@ -2941,46 +2999,46 @@
         <v>298.139</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.0174164264426</v>
+        <v>6.12488724943837</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>295.546904537807</v>
+        <v>294.963641100303</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>302.111388303209</v>
+        <v>302.334320102886</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>297.22414501605</v>
+        <v>297.24697799775</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>293.035371015626</v>
+        <v>292.014112750562</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>293.035371015626</v>
+        <v>292.014112750562</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>294.451744076066</v>
+        <v>293.958617013178</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>294.451744076066</v>
+        <v>293.958617013178</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.0215971179205733</v>
+        <v>0.0234529329097797</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0268711402363344</v>
+        <v>0.026306637458519</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.021832023719953</v>
+        <v>0.0237301156149583</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.996294461403838</v>
+        <v>0.996592718738566</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.974646290991666</v>
+        <v>0.972296552085593</v>
       </c>
     </row>
     <row r="28">
@@ -3000,46 +3058,46 @@
         <v>296.237</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.984430705853872</v>
+        <v>-7.05790466586625</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>1</v>
+        <v>0.843907981255756</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>297.576737587639</v>
+        <v>298.284086361782</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>304.643255992242</v>
+        <v>304.876650547881</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>299.330177765045</v>
+        <v>299.423707932611</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>300.922145396766</v>
+        <v>303.294904665866</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>300.922145396766</v>
+        <v>302.512755921221</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>297.857192034275</v>
+        <v>298.379656484801</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>297.857192034275</v>
+        <v>298.379656484801</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>0.0114990177421704</v>
+        <v>0.0149276917138305</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0505807422956868</v>
+        <v>0.0474804702462195</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.0115653855910904</v>
+        <v>0.0150396661834378</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00094246092255</v>
+        <v>1.00032039967061</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.977724555444811</v>
+        <v>0.978689761740018</v>
       </c>
     </row>
     <row r="29">
@@ -3059,46 +3117,46 @@
         <v>291.018</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.981348430293958</v>
+        <v>-5.46100134619909</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>300.42791673821</v>
+        <v>300.545158234486</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>307.141190988993</v>
+        <v>307.378137694744</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>301.638719647113</v>
+        <v>301.811907227455</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>296.54910632794</v>
+        <v>296.479001346199</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>296.54910632794</v>
+        <v>296.479001346199</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>300.393143606928</v>
+        <v>300.438431929212</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>300.393143606928</v>
+        <v>300.438431929212</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.00847794513755669</v>
+        <v>0.006876156869931</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0630273598416284</v>
+        <v>0.0613758964233364</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.00851398468955411</v>
+        <v>0.00689985191573017</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.999884254660288</v>
+        <v>0.999644890951161</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.978029493991554</v>
+        <v>0.977422903861747</v>
       </c>
     </row>
     <row r="30">
@@ -3118,46 +3176,46 @@
         <v>313.284</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.01863678204791</v>
+        <v>7.00103089677007</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>305.135374798896</v>
+        <v>304.10203021989</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>309.605752420985</v>
+        <v>309.838136099874</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>304.131397331013</v>
+        <v>304.395617241203</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>307.552216375066</v>
+        <v>306.28296910323</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>307.552216375066</v>
+        <v>306.28296910323</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>305.098818374853</v>
+        <v>304.371206998354</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>305.098818374853</v>
+        <v>304.371206998354</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0155436233859091</v>
+        <v>0.0130051845956948</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.058780425949881</v>
+        <v>0.0599926414687173</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0156650538405176</v>
+        <v>0.0130901198088669</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.99988019604719</v>
+        <v>1.00088515284909</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.985442989960974</v>
+        <v>0.982355531922777</v>
       </c>
     </row>
     <row r="31">
@@ -3177,46 +3235,46 @@
         <v>314.394</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1.01830742315824</v>
+        <v>5.95411155924372</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>308.550193537259</v>
+        <v>308.433867081344</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>312.030879362831</v>
+        <v>312.249188359457</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>306.76438941891</v>
+        <v>307.132214803373</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>308.74173442134</v>
+        <v>308.439888440756</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>308.74173442134</v>
+        <v>308.439888440756</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>308.219671270315</v>
+        <v>308.112367933425</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>308.219671270315</v>
+        <v>308.112367933425</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.0101770283601846</v>
+        <v>0.0122165152394656</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.0467578388351884</v>
+        <v>0.0481487872818938</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0102289904368866</v>
+        <v>0.0122914416641622</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.998928789306028</v>
+        <v>0.998957639927932</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.987785798314902</v>
+        <v>0.986751541460311</v>
       </c>
     </row>
     <row r="32">
@@ -3236,46 +3294,46 @@
         <v>301.481</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.97933362179314</v>
+        <v>-7.80572574895645</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>309.994903706861</v>
+        <v>310.920357773198</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>314.409227429112</v>
+        <v>314.601615090302</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>309.51097860819</v>
+        <v>309.98851350279</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>307.842999863514</v>
+        <v>309.286725748956</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>307.842999863514</v>
+        <v>309.286725748956</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>309.904422667002</v>
+        <v>310.563948134311</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>309.904422667002</v>
+        <v>310.563948134311</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.005451188798946</v>
+        <v>0.00792528490006887</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.040446331177864</v>
+        <v>0.0408348605030682</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.00546607356286888</v>
+        <v>0.00795677309979315</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.999708120879481</v>
+        <v>0.998853694748586</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.985672161090991</v>
+        <v>0.987165778043347</v>
       </c>
     </row>
     <row r="33">
@@ -3295,46 +3353,46 @@
         <v>309.323</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.981385966150626</v>
+        <v>-5.91945259857477</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>312.720460545564</v>
+        <v>312.801611826814</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>316.731396518823</v>
+        <v>316.88335609677</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>312.354334321249</v>
+        <v>312.937865296468</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>315.189956519639</v>
+        <v>315.242452598575</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>315.189956519639</v>
+        <v>315.242452598575</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>312.508145049101</v>
+        <v>312.562289794078</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>312.508145049101</v>
+        <v>312.562289794078</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.00836659703066343</v>
+        <v>0.00641394436276098</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.0403304858982592</v>
+        <v>0.0403538847777061</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.00840169481833186</v>
+        <v>0.00643455775138202</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.999321069379047</v>
+        <v>0.99923490792986</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.986666141986115</v>
+        <v>0.986363858437007</v>
       </c>
     </row>
     <row r="34">
@@ -3354,46 +3412,46 @@
         <v>319.058</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.02324601661424</v>
+        <v>8.58047176979215</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>312.441422960406</v>
+        <v>311.565134878655</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>318.983882638728</v>
+        <v>319.079029377387</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>315.269286086763</v>
+        <v>315.950113202651</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>311.809667293612</v>
+        <v>310.477528230208</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>311.809667293612</v>
+        <v>310.477528230208</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>312.792667365545</v>
+        <v>312.150461911142</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>312.792667365545</v>
+        <v>312.150461911142</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>0.000910033476466561</v>
+        <v>-0.00131845537479329</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0.0252175640393297</v>
+        <v>0.0255584455228397</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>0.000910447682568316</v>
+        <v>-0.00131758659436365</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.00112419282248</v>
+        <v>1.00187866666376</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.980590821009614</v>
+        <v>0.978285732284682</v>
       </c>
     </row>
     <row r="35">
@@ -3413,46 +3471,46 @@
         <v>317.946</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1.01787872007125</v>
+        <v>5.54166141442177</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>313.415887002719</v>
+        <v>313.261955035842</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>321.152218395595</v>
+        <v>321.172227365987</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>318.244841544397</v>
+        <v>319.006623176094</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>312.361378355316</v>
+        <v>312.404338585578</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>312.361378355316</v>
+        <v>312.404338585578</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>314.858212342303</v>
+        <v>314.727327067944</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>314.858212342303</v>
+        <v>314.727327067944</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.00658185147279335</v>
+        <v>0.00822131431766572</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.021538343236263</v>
+        <v>0.0214693073792753</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.00660355945730773</v>
+        <v>0.00825520212600273</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.00460195350458</v>
+        <v>1.00467778486517</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.980401797986215</v>
+        <v>0.979933195497944</v>
       </c>
     </row>
     <row r="36">
@@ -3472,46 +3530,46 @@
         <v>314.546</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.974126929825112</v>
+        <v>-9.0771028704106</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>324.023106998321</v>
+        <v>324.145928201912</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>323.217452511599</v>
+        <v>323.141166558191</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>321.252710239851</v>
+        <v>322.061398246689</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>322.900425364969</v>
+        <v>323.623102870411</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>322.900425364969</v>
+        <v>323.623102870411</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>323.320742396091</v>
+        <v>323.676166335452</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>323.320742396091</v>
+        <v>323.676166335452</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0265224230849036</v>
+        <v>0.0280368937562089</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0.0432917982054919</v>
+        <v>0.042220670750458</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.0268772727598026</v>
+        <v>0.028433626501001</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>0.997832362609146</v>
+        <v>0.998550770422859</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>1.00031956778228</v>
+        <v>1.00165562247286</v>
       </c>
     </row>
     <row r="37">
@@ -3531,46 +3589,46 @@
         <v>329.818</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.984176626933885</v>
+        <v>-5.23612101540865</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>331.261162973048</v>
+        <v>332.695203530941</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>325.155139433889</v>
+        <v>324.958583519132</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>324.235184402879</v>
+        <v>325.035430021376</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>335.12074049911</v>
+        <v>335.054121015409</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>335.12074049911</v>
+        <v>335.054121015409</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>329.750992031251</v>
+        <v>331.057163691587</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>329.750992031251</v>
+        <v>331.057163691587</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0196929589992414</v>
+        <v>0.0225475310871875</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.0551756722354877</v>
+        <v>0.0591718019140854</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0198881444707377</v>
+        <v>0.0228036479784708</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>0.995441147014507</v>
+        <v>0.99507645489935</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>1.01413433785904</v>
+        <v>1.01876725368018</v>
       </c>
     </row>
     <row r="38">
@@ -3590,46 +3648,46 @@
         <v>340.482</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.06476658330554</v>
+        <v>9.98469013488154</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0.277844632718093</v>
+        <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>328.205368933383</v>
+        <v>331.831451100039</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>326.94063546765</v>
+        <v>326.597516024135</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>327.142794838863</v>
+        <v>327.857518630212</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>319.771492962319</v>
+        <v>330.497309865118</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>325.862061761813</v>
+        <v>330.497309865118</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>327.054537534975</v>
+        <v>330.481884140027</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>327.054537534975</v>
+        <v>330.481884140027</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>-0.00821086158402366</v>
+        <v>-0.00173921614591897</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.0455952829378936</v>
+        <v>0.058726237714499</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>-0.00817724453129109</v>
+        <v>-0.00173770458595468</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>0.996493563154839</v>
+        <v>0.995932974540121</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.00034838761221</v>
+        <v>1.01189344047431</v>
       </c>
     </row>
     <row r="39">
@@ -3649,46 +3707,46 @@
         <v>329.749</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.97785181496953</v>
+        <v>3.87020418553917</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>321.373286117165</v>
+        <v>324.775047981382</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>328.55552541873</v>
+        <v>328.037311559465</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>329.980500133663</v>
+        <v>330.506557658228</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>337.217761374483</v>
+        <v>325.878795814461</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>321.373286117165</v>
+        <v>325.878795814461</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>321.731723051898</v>
+        <v>325.302468435872</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>321.731723051898</v>
+        <v>325.302468435872</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>-0.0164088983920216</v>
+        <v>-0.0157964226614658</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.0218304952520092</v>
+        <v>0.0336009633051177</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>-0.0162750057626343</v>
+        <v>-0.0156723135297805</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00111532896546</v>
+        <v>1.00162395620528</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.979230900596983</v>
+        <v>0.991663012019601</v>
       </c>
     </row>
     <row r="40">
@@ -3708,46 +3766,46 @@
         <v>309.118</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.971097296576256</v>
+        <v>-9.83697224944584</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>318.53922070791</v>
+        <v>319.557874665353</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>329.980719984413</v>
+        <v>329.259754982534</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>332.746855207757</v>
+        <v>332.974639646626</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>318.318258211448</v>
+        <v>318.954972249446</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>318.318258211448</v>
+        <v>318.954972249446</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>320.096461271903</v>
+        <v>321.575741791891</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>320.096461271903</v>
+        <v>321.575741791891</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>-0.00509564820716026</v>
+        <v>-0.0115223169250758</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>-0.00997239181220966</v>
+        <v>-0.00648927774739094</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>-0.00508268741572426</v>
+        <v>-0.011456189256417</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.00488869333118</v>
+        <v>1.00631455922859</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.970045950827136</v>
+        <v>0.97666276222841</v>
       </c>
     </row>
     <row r="41">
@@ -3767,46 +3825,46 @@
         <v>319.451</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.990926613142733</v>
+        <v>-3.06322685420975</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>324.513408581025</v>
+        <v>324.101874467195</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>331.192640962418</v>
+        <v>330.245282078413</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>335.397378911537</v>
+        <v>335.23071832739</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>322.376042547549</v>
+        <v>322.51422685421</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>322.376042547549</v>
+        <v>322.51422685421</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>326.342571500786</v>
+        <v>326.279354139719</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>326.342571500786</v>
+        <v>326.279354139719</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0193252706087662</v>
+        <v>0.0145208242558093</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>-0.010336346554923</v>
+        <v>-0.0144319775430642</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0195132123737463</v>
+        <v>0.0146267635786796</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>1.00563663279049</v>
+        <v>1.00671850379176</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.985355745080752</v>
+        <v>0.987990962615017</v>
       </c>
     </row>
     <row r="42">
@@ -3826,46 +3884,46 @@
         <v>351.422</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.02664931005112</v>
+        <v>10.2880093989892</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>341.917367642725</v>
+        <v>341.704893750777</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>332.160421111858</v>
+        <v>330.967888142968</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>337.815447110417</v>
+        <v>337.173649095518</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>342.299942696598</v>
+        <v>341.133990601011</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>342.299942696598</v>
+        <v>341.133990601011</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>340.824582759282</v>
+        <v>340.637913518707</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>340.824582759282</v>
+        <v>340.637913518707</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0434202624104853</v>
+        <v>0.0430661469824062</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.0421032080095638</v>
+        <v>0.030730971548133</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0443767149100287</v>
+        <v>0.0440069504760618</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.996803950349241</v>
+        <v>0.996877480388537</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.02608426861461</v>
+        <v>1.0292174126922</v>
       </c>
     </row>
     <row r="43">
@@ -3885,46 +3943,46 @@
         <v>358.827</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1.00702901889371</v>
+        <v>1.05755398140277</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>353.618628542323</v>
+        <v>353.985456007373</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>332.847682817834</v>
+        <v>331.396736562547</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>339.819328987987</v>
+        <v>338.638704888644</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>356.322403096383</v>
+        <v>357.769446018597</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>356.322403096383</v>
+        <v>357.769446018597</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>350.707731237655</v>
+        <v>351.068375272849</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>350.707731237655</v>
+        <v>351.068375272849</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0285852771998991</v>
+        <v>0.0301609298952182</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.0900626394901185</v>
+        <v>0.0792059985307381</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0289977571405224</v>
+        <v>0.0306203782379868</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.991768258033615</v>
+        <v>0.991759320375966</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.0536583228359</v>
+        <v>1.0593597840291</v>
       </c>
     </row>
     <row r="44">
@@ -3944,46 +4002,46 @@
         <v>338.369</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.972642844941382</v>
+        <v>-9.23161845318892</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>347.389522846085</v>
+        <v>347.893518244916</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>333.22438566644</v>
+        <v>331.507344537537</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>341.249716205773</v>
+        <v>339.480960351927</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>347.886176061258</v>
+        <v>347.600618453189</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>347.886176061258</v>
+        <v>347.600618453189</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>347.337900881847</v>
+        <v>347.57813908221</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>347.337900881847</v>
+        <v>347.57813908221</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.00965511817291523</v>
+        <v>-0.00999150544598695</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0851038449525507</v>
+        <v>0.0808593246039913</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.00960865716851045</v>
+        <v>-0.00994175618332371</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>0.999851400342142</v>
+        <v>0.99909346065343</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.04235438888178</v>
+        <v>1.04847794418278</v>
       </c>
     </row>
     <row r="45">
@@ -4003,46 +4061,46 @@
         <v>336.904</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.998953769774407</v>
+        <v>-0.437873403866151</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>341.224341355698</v>
+        <v>340.901677677989</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>333.275160943942</v>
+        <v>331.291712211732</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>342.029815795838</v>
+        <v>339.651143836176</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>337.256848308489</v>
+        <v>337.341873403866</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>337.256848308489</v>
+        <v>337.341873403866</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>343.465955755292</v>
+        <v>343.000731354872</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>343.465955755292</v>
+        <v>343.000731354872</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.0112100870223569</v>
+        <v>-0.0132569210020942</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0524705807635177</v>
+        <v>0.0512486524292679</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.0111474881282014</v>
+        <v>-0.0131694350497</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.00656932735422</v>
+        <v>1.00615735801355</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.03057772077129</v>
+        <v>1.03534353173211</v>
       </c>
     </row>
     <row r="46">
@@ -4062,46 +4120,46 @@
         <v>359.582</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.02309781600402</v>
+        <v>9.8634398414351</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>351.404715017016</v>
+        <v>349.688827415465</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>332.993803555603</v>
+        <v>330.751898025125</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>342.116017089525</v>
+        <v>339.140581982709</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>351.463950342933</v>
+        <v>349.718560158565</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>351.463950342933</v>
+        <v>349.718560158565</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>350.922071231404</v>
+        <v>348.92246935314</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>350.922071231404</v>
+        <v>348.92246935314</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0214761826641925</v>
+        <v>0.0171171672790584</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.0296266436838959</v>
+        <v>0.0243207097790608</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0217084556742035</v>
+        <v>0.0172645054571099</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.998626530137511</v>
+        <v>0.997808457113175</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.05383964351399</v>
+        <v>1.05493716419017</v>
       </c>
     </row>
     <row r="47">
@@ -4121,46 +4179,46 @@
         <v>362.479</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.997181496656875</v>
+        <v>-2.99736941779334</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>1</v>
+        <v>0.427867455506185</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>358.512887985223</v>
+        <v>354.000906626149</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>332.37659696129</v>
+        <v>329.893741768453</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>341.44084458074</v>
+        <v>337.929055080679</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>363.50353593126</v>
+        <v>365.476369417793</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>363.50353593126</v>
+        <v>358.910883691566</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>356.412352442498</v>
+        <v>351.665071371901</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>356.412352442498</v>
+        <v>351.665071371901</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.01552417439343</v>
+        <v>0.00782947417587652</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.0162660263710495</v>
+        <v>0.00169965779056191</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0156453003706174</v>
+        <v>0.00786020465762793</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.994140976201638</v>
+        <v>0.993401612226053</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.0723148251139</v>
+        <v>1.06599497609969</v>
       </c>
     </row>
     <row r="48">
@@ -4168,58 +4226,58 @@
         <v>98</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>340.80650444183</v>
+        <v>327.6245</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>340.80650444183</v>
+        <v>327.6245</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>340.80650444183</v>
+        <v>327.6245</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>340.80650444183</v>
+        <v>327.6245</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.981646659610903</v>
+        <v>-6.45748901546646</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1</v>
+        <v>0.485930338159144</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>351.105260215624</v>
+        <v>343.882156783392</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>331.431368462612</v>
+        <v>328.734937396288</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>339.983562429656</v>
+        <v>336.049233310119</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>347.17838756454</v>
+        <v>334.081989015466</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>347.17838756454</v>
+        <v>339.119957945908</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>350.52986770529</v>
+        <v>342.903656717028</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>350.52986770529</v>
+        <v>342.903656717028</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.0166424365157913</v>
+        <v>-0.0252296973448796</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.00918980282698545</v>
+        <v>-0.0134487237244698</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.0165047162279743</v>
+        <v>-0.024914088341765</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.998361196554046</v>
+        <v>0.99715454830365</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.05762429588747</v>
+        <v>1.04310074077602</v>
       </c>
     </row>
     <row r="49">
@@ -4227,58 +4285,58 @@
         <v>99</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>345.764859332108</v>
+        <v>336.2245</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>345.764859332108</v>
+        <v>336.2245</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>345.764859332108</v>
+        <v>336.2245</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>345.764859332108</v>
+        <v>336.2245</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.00437373858791</v>
+        <v>1.76067271526747</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>345.243528334748</v>
+        <v>334.905390714633</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>330.185399698032</v>
+        <v>327.311314576903</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>337.833748253199</v>
+        <v>333.63869599412</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>344.25915976082</v>
+        <v>334.463827284733</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>344.25915976082</v>
+        <v>334.463827284733</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>344.378852440894</v>
+        <v>334.345978132513</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>344.378852440894</v>
+        <v>334.345978132513</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.0177035508039987</v>
+        <v>-0.0252732039902997</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.00265789569622732</v>
+        <v>-0.0252324628818469</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.0175477636318482</v>
+        <v>-0.024956510135956</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.997495460963384</v>
+        <v>0.998329639959136</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.04298631240461</v>
+        <v>1.02149227124856</v>
       </c>
     </row>
     <row r="50">
@@ -4286,58 +4344,58 @@
         <v>100</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>374.704344280682</v>
+        <v>337.3735</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>374.704344280682</v>
+        <v>337.3735</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>374.704344280682</v>
+        <v>337.3735</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>374.704344280682</v>
+        <v>337.3735</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.05336295567031</v>
+        <v>8.03719998531895</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.23310225507827</v>
+        <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>337.592738173428</v>
+        <v>323.476875700457</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>328.675814192956</v>
+        <v>325.665193616415</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>335.116953793968</v>
+        <v>330.850376078946</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>355.721968637333</v>
+        <v>329.336300014681</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>341.818702677398</v>
+        <v>329.336300014681</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>336.230622674401</v>
+        <v>324.437508731889</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>336.230622674401</v>
+        <v>324.437508731889</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0239450650844428</v>
+        <v>-0.0300833790119875</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.0418652736929593</v>
+        <v>-0.0701730692971514</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.023660656595899</v>
+        <v>-0.0296353778680629</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.995965210903537</v>
+        <v>1.00296971160412</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>1.02298559296185</v>
+        <v>0.996230223835429</v>
       </c>
     </row>
     <row r="51">
@@ -4357,46 +4415,46 @@
         <v>298.598</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.95465148042799</v>
+        <v>-6.01560761346261</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0.58293419514245</v>
+        <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>322.957380027263</v>
+        <v>312.288104321328</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>326.948531572826</v>
+        <v>323.843365141382</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>331.990857852102</v>
+        <v>327.84133216732</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>312.78221018013</v>
+        <v>304.613607613463</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>317.025925581987</v>
+        <v>304.613607613463</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>323.805530576949</v>
+        <v>314.723812830278</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>323.805530576949</v>
+        <v>314.723812830278</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>-0.0376541801984223</v>
+        <v>-0.0303974709420299</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.0914862283590731</v>
+        <v>-0.105046709351909</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.0369540763379058</v>
+        <v>-0.0299401137050344</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00262619962304</v>
+        <v>1.00779955584361</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.990386863092009</v>
+        <v>0.97183961972751</v>
       </c>
     </row>
     <row r="52">
@@ -4416,46 +4474,46 @@
         <v>316.88</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.992260665954157</v>
+        <v>-3.45173607950766</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>321.742621226203</v>
+        <v>319.30536695217</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>325.057685768386</v>
+        <v>321.894914219864</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>328.646647972156</v>
+        <v>324.761052481638</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>319.351568466426</v>
+        <v>320.331736079508</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>319.351568466426</v>
+        <v>320.331736079508</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>322.12679435753</v>
+        <v>319.321103766771</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>322.12679435753</v>
+        <v>319.321103766771</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>-0.00519788198944505</v>
+        <v>0.0145017218287427</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>-0.081028967755865</v>
+        <v>-0.0687731159709332</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.00518439637651591</v>
+        <v>0.0146073819300474</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00119403866937</v>
+        <v>1.00004928452895</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.99098347296749</v>
+        <v>0.992004190375824</v>
       </c>
     </row>
     <row r="53">
@@ -4475,46 +4533,46 @@
         <v>335.545</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.00831450435201</v>
+        <v>3.53766470539346</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>326.653862573589</v>
+        <v>326.072380209225</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>323.051209081639</v>
+        <v>319.856907321462</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>325.200687037333</v>
+        <v>321.642886621533</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>332.778114915283</v>
+        <v>332.007335294607</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>332.778114915283</v>
+        <v>332.007335294607</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>324.471545004176</v>
+        <v>323.370407957302</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>324.471545004176</v>
+        <v>323.370407957302</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.00725260422669096</v>
+        <v>0.0126012486533053</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.0578064166705324</v>
+        <v>-0.0328269843008597</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.00727896805766348</v>
+        <v>0.0126809789355116</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.993319174148994</v>
+        <v>0.991713581352124</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.0043966277872</v>
+        <v>1.01098460141212</v>
       </c>
     </row>
     <row r="54">
@@ -4534,46 +4592,46 @@
         <v>315.165</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.00698648343784</v>
+        <v>6.02977483951333</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>313.743474297087</v>
+        <v>312.51276189796</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>320.973467491271</v>
+        <v>317.765433929441</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>321.722862533311</v>
+        <v>318.498037604621</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>312.978381719713</v>
+        <v>309.135225160487</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>312.978381719713</v>
+        <v>309.135225160487</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>314.099653741208</v>
+        <v>313.079111779795</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>314.099653741208</v>
+        <v>313.079111779795</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0324875394001422</v>
+        <v>-0.0323425281478983</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.0658208010833802</v>
+        <v>-0.0350095061341411</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0319654879531421</v>
+        <v>-0.0318251018778006</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.0011352569003</v>
+        <v>1.00181224561325</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.978584479883059</v>
+        <v>0.985252259530887</v>
       </c>
     </row>
     <row r="55">
@@ -4593,46 +4651,46 @@
         <v>293.215</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.985054489133324</v>
+        <v>-8.82366150359906</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>302.443308257692</v>
+        <v>304.192042871136</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>318.874906292117</v>
+        <v>315.664177544551</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>318.320949085155</v>
+        <v>315.389530691887</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>297.663736610122</v>
+        <v>302.038661503599</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>297.663736610122</v>
+        <v>302.038661503599</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>305.607892503161</v>
+        <v>307.063653663838</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>305.607892503161</v>
+        <v>307.063653663838</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.0274074209473925</v>
+        <v>-0.0194008448739088</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0561992812209365</v>
+        <v>-0.0243393059379698</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0270352454608042</v>
+        <v>-0.0192138596591771</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>1.01046339647486</v>
+        <v>1.00944012461864</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.958394299685649</v>
+        <v>0.97275419736375</v>
       </c>
     </row>
     <row r="56">
@@ -4652,46 +4710,46 @@
         <v>315.244</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>1.00355999166466</v>
+        <v>0.20193351233295</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>312.514744131066</v>
+        <v>313.616061127637</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>316.800973850403</v>
+        <v>313.591427787059</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>315.058998913862</v>
+        <v>312.333577082096</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>314.125715072686</v>
+        <v>315.042066487667</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>314.125715072686</v>
+        <v>315.042066487667</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>312.619451370543</v>
+        <v>313.816413342223</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>312.619451370543</v>
+        <v>313.816413342223</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.0226837573127472</v>
+        <v>0.0217530770173475</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0295142880180137</v>
+        <v>-0.0172387304177964</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0229429901497371</v>
+        <v>0.0219914001472061</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00033504735838</v>
+        <v>1.0006388455166</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.986800790322588</v>
+        <v>1.0007174480398</v>
       </c>
     </row>
     <row r="57">
@@ -4711,46 +4769,46 @@
         <v>327.515</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.0090964298445</v>
+        <v>4.37214111004313</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>320.438863242232</v>
+        <v>322.328796389658</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>314.783861551303</v>
+        <v>311.576958329708</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>311.897778178056</v>
+        <v>309.279633628069</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>324.562638726677</v>
+        <v>323.142858889957</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>324.562638726677</v>
+        <v>323.142858889957</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>319.090927921055</v>
+        <v>320.521769164646</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>319.090927921055</v>
+        <v>320.521769164646</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0204894621479735</v>
+        <v>0.0211420525277533</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.0165827086102482</v>
+        <v>-0.00880921297236181</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0207008121923986</v>
+        <v>0.0213671291154285</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>0.995793471155345</v>
+        <v>0.994393838697468</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.01368261494896</v>
+        <v>1.02870819101287</v>
       </c>
     </row>
     <row r="58">
@@ -4770,46 +4828,46 @@
         <v>324.057</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.03495316597564</v>
+        <v>3.29770760899512</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>317.730168326777</v>
+        <v>320.421098684744</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>312.854088743256</v>
+        <v>309.651449494427</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>308.793386617152</v>
+        <v>306.190699629656</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>313.11271915818</v>
+        <v>320.759292391005</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>313.11271915818</v>
+        <v>320.759292391005</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>317.716034922309</v>
+        <v>319.514455074943</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>317.716034922309</v>
+        <v>319.514455074943</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>-0.00431809077259593</v>
+        <v>-0.00314768096945434</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.0115134835012607</v>
+        <v>0.0205550068753058</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>-0.00430878122328249</v>
+        <v>-0.00314273221543959</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.999955517587321</v>
+        <v>0.997170462202637</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.01554061894663</v>
+        <v>1.03185195999121</v>
       </c>
     </row>
     <row r="59">
@@ -4829,46 +4887,46 @@
         <v>304.316</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.950761508011865</v>
+        <v>-9.0803766278055</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>321.117719385175</v>
+        <v>316.443061865074</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>311.048286510437</v>
+        <v>307.852810290997</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>305.765248273311</v>
+        <v>303.099090513017</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>320.076062646199</v>
+        <v>313.396376627805</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>320.076062646199</v>
+        <v>313.396376627805</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>319.033089953666</v>
+        <v>313.836808923318</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>319.033089953666</v>
+        <v>313.836808923318</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.00413681576671295</v>
+        <v>-0.0179293815912942</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.0439294853956256</v>
+        <v>0.0220578214929179</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.00414538420032629</v>
+        <v>-0.0177696065434449</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.993508208031933</v>
+        <v>0.991763911882299</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.02567062346753</v>
+        <v>1.01943785611918</v>
       </c>
     </row>
     <row r="60">
@@ -4888,46 +4946,46 @@
         <v>326.08</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1.00994985398977</v>
+        <v>2.26038344880587</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>1</v>
+        <v>0.160783439951754</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>314.122630069422</v>
+        <v>304.725109522381</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>309.403247581028</v>
+        <v>306.225892131009</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>302.854383851398</v>
+        <v>300.109964668118</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>322.867515364087</v>
+        <v>323.819616551194</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>322.867515364087</v>
+        <v>307.795190046657</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>312.631661032187</v>
+        <v>302.91746150282</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>312.631661032187</v>
+        <v>302.91746150282</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>-0.0202691319164252</v>
+        <v>-0.0354127698844817</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.0000390559883305386</v>
+        <v>-0.0347303435257758</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.0200650939449841</v>
+        <v>-0.0347930743304422</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.995253544652593</v>
+        <v>0.994067938732079</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.0104343230926</v>
+        <v>0.989196110736535</v>
       </c>
     </row>
     <row r="61">
@@ -4947,46 +5005,46 @@
         <v>287.232</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.00883846786365</v>
+        <v>4.54891070983732</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>293.353571500036</v>
+        <v>287.815167761869</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>307.961407043297</v>
+        <v>304.819011155014</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>300.173368128141</v>
+        <v>297.379966915499</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>284.715550754376</v>
+        <v>282.683089290163</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>284.715550754376</v>
+        <v>282.683089290163</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>295.061067095897</v>
+        <v>289.35877384578</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>295.061067095897</v>
+        <v>289.35877384578</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0578433537295417</v>
+        <v>-0.0457930139542547</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>-0.075307251703197</v>
+        <v>-0.0972258308697228</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0562022217400461</v>
+        <v>-0.0447603369900611</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1.00582060612772</v>
+        <v>1.00536318532451</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.958110530565327</v>
+        <v>0.949280600148093</v>
       </c>
     </row>
     <row r="62">
@@ -5006,46 +5064,46 @@
         <v>285.117</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.990176439561045</v>
+        <v>0.84327324386113</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>287.035695654253</v>
+        <v>286.71175945127</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>306.773615152875</v>
+        <v>303.68146431476</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>297.934841537834</v>
+        <v>295.104168202593</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>287.94565151075</v>
+        <v>284.273726756139</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>287.94565151075</v>
+        <v>284.273726756139</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>289.462134558327</v>
+        <v>288.399126519224</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>289.462134558327</v>
+        <v>288.399126519224</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.0191578495619073</v>
+        <v>-0.00332197347181772</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.088928153629046</v>
+        <v>-0.0973831639273451</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0189755042665496</v>
+        <v>-0.00331646182281709</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.00845343955755</v>
+        <v>1.00588523844011</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.94356919976341</v>
+        <v>0.94967642220107</v>
       </c>
     </row>
     <row r="63">
@@ -5065,46 +5123,46 @@
         <v>294.649</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.991277520640611</v>
+        <v>-7.71696327445338</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>293.633560542913</v>
+        <v>295.902590564063</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>305.876193505215</v>
+        <v>302.848713610831</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>296.2741554279</v>
+        <v>293.404155088706</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>297.24168445743</v>
+        <v>302.365963274453</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>297.24168445743</v>
+        <v>302.365963274453</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>293.027317246278</v>
+        <v>294.797705556877</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>293.027317246278</v>
+        <v>294.797705556877</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.0122413451339646</v>
+        <v>0.0219440005415596</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.081514342951588</v>
+        <v>-0.0606656160944252</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.0123165770659144</v>
+        <v>0.0221865409749311</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.997935374636626</v>
+        <v>0.996266051591234</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.95799321250963</v>
+        <v>0.973415742936587</v>
       </c>
     </row>
     <row r="64">
@@ -5124,46 +5182,46 @@
         <v>293.701</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.01387996406552</v>
+        <v>3.5158310775394</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>292.962147455923</v>
+        <v>294.470022216639</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>305.293696218493</v>
+        <v>302.344091207835</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>295.276715195628</v>
+        <v>292.347361925913</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>289.680248559503</v>
+        <v>290.185168922461</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>289.680248559503</v>
+        <v>290.185168922461</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>292.019833941432</v>
+        <v>292.929498904837</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>292.019833941432</v>
+        <v>292.929498904837</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.0034441131751216</v>
+        <v>-0.00635741524328224</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0659300693432757</v>
+        <v>-0.0329725547957221</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.00343818902044468</v>
+        <v>-0.00633724963533899</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.996783497381234</v>
+        <v>0.994768488485839</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.956521007667446</v>
+        <v>0.968861331916933</v>
       </c>
     </row>
     <row r="65">
@@ -5183,46 +5241,46 @@
         <v>292.276</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00274068069908</v>
+        <v>3.29430550002477</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>289.47863915054</v>
+        <v>288.224475733174</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>305.045280842727</v>
+        <v>302.19062755142</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>295.032763883455</v>
+        <v>292.046032107216</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>291.477154189291</v>
+        <v>288.981694499975</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>291.477154189291</v>
+        <v>288.981694499975</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>289.19660782649</v>
+        <v>287.449706918795</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>289.19660782649</v>
+        <v>287.449706918795</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>-0.0097149637099555</v>
+        <v>-0.0188840495130942</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>-0.0198754085963544</v>
+        <v>-0.00659757746970091</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>-0.0096679258968001</v>
+        <v>-0.0187068629364046</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.999025726648165</v>
+        <v>0.997311925670406</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.948044851005552</v>
+        <v>0.951219795424936</v>
       </c>
     </row>
     <row r="66">
@@ -5242,46 +5300,46 @@
         <v>280.81</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.98823912608245</v>
+        <v>-0.840269752768981</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>283.861814476793</v>
+        <v>277.326890024735</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>305.140346523153</v>
+        <v>302.403753760807</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>295.604562200635</v>
+        <v>292.6015980606</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>284.151874367876</v>
+        <v>281.650269752769</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>284.151874367876</v>
+        <v>281.650269752769</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>284.49244495056</v>
+        <v>278.420114218808</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>284.49244495056</v>
+        <v>278.420114218808</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.0164000630288025</v>
+        <v>-0.0319167372790006</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>-0.0171687036556605</v>
+        <v>-0.0346013957145268</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.0162663141566058</v>
+        <v>-0.031412774070206</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.00222161080358</v>
+        <v>1.00394200574627</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.932333099153028</v>
+        <v>0.92069000717177</v>
       </c>
     </row>
     <row r="67">
@@ -5301,46 +5359,46 @@
         <v>256.914</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.999498898262362</v>
+        <v>-4.48422286971858</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>278.188876877196</v>
+        <v>269.202474170592</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>305.579812325844</v>
+        <v>302.990645372059</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>297.036592807954</v>
+        <v>294.100170526014</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>257.04280459603</v>
+        <v>261.398222869719</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>278.188876877196</v>
+        <v>261.398222869719</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>280.008591390031</v>
+        <v>269.680553919714</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>280.008591390031</v>
+        <v>269.680553919714</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>-0.015886411445375</v>
+        <v>-0.0318930502870241</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.0444283692680615</v>
+        <v>-0.0852013131842942</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>-0.0157608879958401</v>
+        <v>-0.0313898308806304</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00654129141777</v>
+        <v>1.00177591142353</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.916319010928164</v>
+        <v>0.890062310631926</v>
       </c>
     </row>
     <row r="68">
@@ -5360,46 +5418,46 @@
         <v>306.755</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1.00963239554368</v>
+        <v>2.1088515515591</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>279.504737437857</v>
+        <v>274.275500186649</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>306.351479521779</v>
+        <v>303.945506993734</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>299.316074927033</v>
+        <v>296.57310360187</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>303.828404629206</v>
+        <v>304.646148448441</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>279.504737437857</v>
+        <v>274.275500186649</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>281.005480420285</v>
+        <v>273.536396540575</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>281.005480420285</v>
+        <v>273.536396540575</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.00355388618424828</v>
+        <v>0.0141965650263426</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.0377178268081483</v>
+        <v>-0.0662039925537259</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.00356020872539875</v>
+        <v>0.0142978148213428</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00536929354466</v>
+        <v>0.997305250940857</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.91726496917508</v>
+        <v>0.89995209748639</v>
       </c>
     </row>
     <row r="69">
@@ -5419,46 +5477,46 @@
         <v>287.002</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.00062208999008</v>
+        <v>2.80563708071669</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>288.570867925533</v>
+        <v>286.923953437277</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>307.426030047281</v>
+        <v>305.236547970325</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>302.335989199839</v>
+        <v>299.888241648294</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>286.823569928229</v>
+        <v>284.196362919283</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>286.823569928229</v>
+        <v>284.196362919283</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>289.172005542355</v>
+        <v>285.93619837595</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>289.172005542355</v>
+        <v>285.93619837595</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0286475135345528</v>
+        <v>0.0443340133927624</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.0000850711366221502</v>
+        <v>-0.00526529861195124</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0290618001821752</v>
+        <v>0.0453314512883678</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00208315420452</v>
+        <v>0.996557432554883</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.940623035394504</v>
+        <v>0.936769204989659</v>
       </c>
     </row>
     <row r="70">
@@ -5478,46 +5536,46 @@
         <v>300.125</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>0.988761981290533</v>
+        <v>-0.951567478583008</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>302.614508525676</v>
+        <v>301.878795274569</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>308.75736662487</v>
+        <v>306.813433892074</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>305.890259580892</v>
+        <v>303.80194100834</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>303.536144875106</v>
+        <v>301.076567478583</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>303.536144875106</v>
+        <v>301.076567478583</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>302.749658691107</v>
+        <v>302.04624199491</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>302.749658691107</v>
+        <v>302.04624199491</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0458845691172645</v>
+        <v>0.0548114215101153</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.0641746874639169</v>
+        <v>0.084857833789749</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0469535532088832</v>
+        <v>0.0563413926269638</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.000446608347</v>
+        <v>1.00055468195502</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.980542300903022</v>
+        <v>0.984462245226067</v>
       </c>
     </row>
     <row r="71">
@@ -5537,46 +5595,46 @@
         <v>318.876</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1.00559195646752</v>
+        <v>-2.95947010319263</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>315.703405108225</v>
+        <v>318.161759835911</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>310.286515439491</v>
+        <v>308.612680233562</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>309.695247928357</v>
+        <v>307.992098631415</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>317.102775085989</v>
+        <v>321.835470103193</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>317.102775085989</v>
+        <v>321.835470103193</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>315.936884834576</v>
+        <v>317.794164979375</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>315.936884834576</v>
+        <v>317.794164979375</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.04263620703135</v>
+        <v>0.0508237684232335</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.12831139668318</v>
+        <v>0.178409641927629</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.043558186656532</v>
+        <v>0.0521374571007884</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>1.00073955403259</v>
+        <v>0.998844629044276</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.01821016742246</v>
+        <v>1.02975083440792</v>
       </c>
     </row>
     <row r="72">
@@ -5596,46 +5654,46 @@
         <v>327.007</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1.00307097472733</v>
+        <v>0.577847767470317</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>330.65845435057</v>
+        <v>331.77472719949</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>311.951239412498</v>
+        <v>310.567216927863</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>313.455545526867</v>
+        <v>312.122984599278</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>326.00584429122</v>
+        <v>326.42915223253</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>326.00584429122</v>
+        <v>326.42915223253</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>329.22507156335</v>
+        <v>329.884976235739</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>329.22507156335</v>
+        <v>329.884976235739</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0411991628636232</v>
+        <v>0.037340143574065</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.171596621784549</v>
+        <v>0.206000299805827</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0420596244586364</v>
+        <v>0.0380460454871765</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.995665065361672</v>
+        <v>0.994304114181022</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.05537350062588</v>
+        <v>1.06220154045545</v>
       </c>
     </row>
     <row r="73">
@@ -5655,46 +5713,46 @@
         <v>348.079</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.00084298265194</v>
+        <v>3.23286962529582</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>340.982825597814</v>
+        <v>338.014967241356</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>313.693561627521</v>
+        <v>312.618238151721</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>316.912781296846</v>
+        <v>315.928085851046</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>347.78582258497</v>
+        <v>344.846130374704</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>347.78582258497</v>
+        <v>344.846130374704</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>339.549137892855</v>
+        <v>337.598673498386</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>339.549137892855</v>
+        <v>337.598673498386</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.030877047621541</v>
+        <v>0.0231137966640749</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.174211650453559</v>
+        <v>0.180678331095774</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0313586880867858</v>
+        <v>0.0233829904916163</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.995795425466236</v>
+        <v>0.998768416243911</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.08242303772888</v>
+        <v>1.0799071592699</v>
       </c>
     </row>
     <row r="74">
@@ -5714,46 +5772,46 @@
         <v>333.69</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.991298585136873</v>
+        <v>-0.58328101160761</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>341.862815384477</v>
+        <v>341.319341638227</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>315.464289296242</v>
+        <v>314.716851791444</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>319.871335652536</v>
+        <v>319.212420164002</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>336.619062110258</v>
+        <v>334.273281011608</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>336.619062110258</v>
+        <v>334.273281011608</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>340.089050433978</v>
+        <v>339.581027257402</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>340.089050433978</v>
+        <v>339.581027257402</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.00158882377116101</v>
+        <v>0.00585475146231344</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.123334215814815</v>
+        <v>0.12426834055139</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.0015900866203753</v>
+        <v>0.00587192401697845</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.994811471529876</v>
+        <v>0.99490707332177</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.07805879135376</v>
+        <v>1.07900490655148</v>
       </c>
     </row>
     <row r="75">
@@ -5773,46 +5831,46 @@
         <v>342.148</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1.00829789985674</v>
+        <v>-2.78341663168722</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>338.082808090575</v>
+        <v>340.425995675969</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>317.235537293437</v>
+        <v>316.834308165979</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>322.289954214624</v>
+        <v>321.92559553805</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>339.332254930426</v>
+        <v>344.931416631687</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>339.332254930426</v>
+        <v>344.931416631687</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>336.655184883951</v>
+        <v>338.804207199435</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>336.655184883951</v>
+        <v>338.804207199435</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0101482800775512</v>
+        <v>-0.00229020432063452</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0655773385251397</v>
+        <v>0.0661121081987903</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0100969600333941</v>
+        <v>-0.00228758380360761</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.995777297240617</v>
+        <v>0.995236002840166</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.06121523381711</v>
+        <v>1.06934191931622</v>
       </c>
     </row>
     <row r="76">
@@ -5832,46 +5890,46 @@
         <v>329.742</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.995185666683821</v>
+        <v>-1.3387145227587</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>325.855104336792</v>
+        <v>328.660166219001</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>318.992642226897</v>
+        <v>318.954080362537</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>324.211121236082</v>
+        <v>324.092524277328</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>331.337167564695</v>
+        <v>331.080714522759</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>331.337167564695</v>
+        <v>331.080714522759</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>326.779729310392</v>
+        <v>329.443819987654</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>326.779729310392</v>
+        <v>329.443819987654</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0297728830324682</v>
+        <v>-0.0280165420353657</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>-0.00742756996405403</v>
+        <v>-0.00133730324162928</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0293340367740451</v>
+        <v>-0.027627718348465</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00283753411039</v>
+        <v>1.00238438925431</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.02441149435026</v>
+        <v>1.03288793049205</v>
       </c>
     </row>
     <row r="77">
@@ -5891,46 +5949,46 @@
         <v>305.407</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.00638839188027</v>
+        <v>5.61751864238813</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>0.864448057580595</v>
+        <v>0.31700241722258</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>315.596530575838</v>
+        <v>315.73822435536</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>320.73475115293</v>
+        <v>321.077202161118</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>325.762532473463</v>
+        <v>325.853147791446</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>303.468325414006</v>
+        <v>299.789481357612</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>305.112327181753</v>
+        <v>310.682434273412</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>317.289156117427</v>
+        <v>319.435705527734</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>317.289156117427</v>
+        <v>319.435705527734</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.029472810731639</v>
+        <v>-0.0308498196972538</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.0655574680989232</v>
+        <v>-0.0538004719699787</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0290427230997269</v>
+        <v>-0.0303788198555213</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00536325775984</v>
+        <v>1.01171059088561</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.989257182069864</v>
+        <v>0.994887532897587</v>
       </c>
     </row>
     <row r="78">
@@ -5950,46 +6008,46 @@
         <v>324.625</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.990934524850621</v>
+        <v>-0.672239041354865</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>319.495517531184</v>
+        <v>321.393057225463</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>322.468726456185</v>
+        <v>323.212286488075</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>327.107513914963</v>
+        <v>327.382348441239</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>327.594802541506</v>
+        <v>325.297239041355</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>327.594802541506</v>
+        <v>325.297239041355</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>320.713521130043</v>
+        <v>322.766838880395</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>320.713521130043</v>
+        <v>322.766838880395</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.0107347445974525</v>
+        <v>0.0103741825919073</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.0569719292026902</v>
+        <v>-0.0495145106097499</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0107925686919756</v>
+        <v>0.0104281809923454</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.00381227132159</v>
+        <v>1.0042744596501</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>0.994556975042415</v>
+        <v>0.99862181103163</v>
       </c>
     </row>
     <row r="79">
@@ -6009,46 +6067,46 @@
         <v>325.422</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1.00889731389025</v>
+        <v>-4.36844316545902</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>324.696407277653</v>
+        <v>327.890345560494</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>324.191666506325</v>
+        <v>325.361449539828</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>328.306140522318</v>
+        <v>328.779155019952</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>322.552152255408</v>
+        <v>329.790443165459</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>322.552152255408</v>
+        <v>329.790443165459</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>324.138412915706</v>
+        <v>326.927641344239</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>324.138412915706</v>
+        <v>326.927641344239</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.010622357811473</v>
+        <v>0.0128086646142012</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>-0.037179798589943</v>
+        <v>-0.0350543635610909</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0106789753472034</v>
+        <v>0.0128910469188117</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.998281488955712</v>
+        <v>0.997063944610478</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>0.999835734239583</v>
+        <v>1.00481369813979</v>
       </c>
     </row>
     <row r="80">
@@ -6068,46 +6126,46 @@
         <v>321.243</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.991936056930613</v>
+        <v>-1.58944000468285</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>326.705821841906</v>
+        <v>326.238089334794</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>325.90387347057</v>
+        <v>327.528110608146</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>329.420923700399</v>
+        <v>330.13217077383</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>323.854544610501</v>
+        <v>322.832440004683</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>323.854544610501</v>
+        <v>322.832440004683</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>326.620290688741</v>
+        <v>326.692001404164</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>326.620290688741</v>
+        <v>326.692001404164</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>0.00762768071348227</v>
+        <v>-0.00072103081019092</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.000487908543127302</v>
+        <v>-0.00835292215708683</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>0.00765684557627733</v>
+        <v>-0.000720770929940606</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.999738201319209</v>
+        <v>1.00139135215724</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>1.00219824701849</v>
+        <v>0.997447213912632</v>
       </c>
     </row>
     <row r="81">
@@ -6127,46 +6185,46 @@
         <v>338.9</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.00797120739085</v>
+        <v>7.58731755816885</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>330.761107764557</v>
+        <v>330.391207912455</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>327.60462481973</v>
+        <v>329.718457105812</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>330.485604912739</v>
+        <v>331.535055389848</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>336.219921278553</v>
+        <v>331.312682441831</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>336.219921278553</v>
+        <v>331.312682441831</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>330.457232677339</v>
+        <v>330.299181961874</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>330.457232677339</v>
+        <v>330.299181961874</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>0.0116789433957613</v>
+        <v>0.010981020433649</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.041501817210035</v>
+        <v>0.0340083348421949</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>0.0117474085290499</v>
+        <v>0.011041533132756</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.999081285314129</v>
+        <v>0.999721463681912</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>1.00870747126717</v>
+        <v>1.00176127494093</v>
       </c>
     </row>
     <row r="82">
@@ -6186,46 +6244,46 @@
         <v>335.07</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.02929168853944</v>
+        <v>-0.668922959152526</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>330.449526493662</v>
+        <v>334.089674774269</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>329.29191719408</v>
+        <v>331.935741651481</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>331.506093727426</v>
+        <v>333.044969901133</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>325.534543541746</v>
+        <v>335.738922959153</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>325.534543541746</v>
+        <v>335.738922959153</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>329.829380558735</v>
+        <v>332.989761973585</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>329.829380558735</v>
+        <v>332.989761973585</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.00190175688934399</v>
+        <v>0.0081128889419738</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>0.028423682907325</v>
+        <v>0.031672780043484</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.00189994969550689</v>
+        <v>0.00814588760326007</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.99812332630188</v>
+        <v>0.996707731834492</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>1.00163217903809</v>
+        <v>1.00317537459768</v>
       </c>
     </row>
     <row r="83">
@@ -6245,46 +6303,46 @@
         <v>322.848</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.972350224485813</v>
+        <v>-6.32051953420218</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>328.257920254098</v>
+        <v>329.920178034673</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>330.96913179418</v>
+        <v>334.184213254646</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>332.516971294374</v>
+        <v>334.717963476072</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>332.028513872895</v>
+        <v>329.168519534202</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>332.028513872895</v>
+        <v>329.168519534202</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>329.646529790851</v>
+        <v>330.298995434413</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>329.646529790851</v>
+        <v>330.298995434413</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>-0.000554533591599671</v>
+        <v>-0.00811345366488196</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>0.0169931012668274</v>
+        <v>0.0103122332400878</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>-0.000554379866264165</v>
+        <v>-0.00808062843501345</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00423023924504</v>
+        <v>1.00114820924866</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.996003850884343</v>
+        <v>0.988374023469287</v>
       </c>
     </row>
     <row r="84">
@@ -6304,46 +6362,46 @@
         <v>325.352</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.988928242430197</v>
+        <v>-1.7680197100931</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>333.264805505063</v>
+        <v>328.92440723791</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>332.637301462058</v>
+        <v>336.470497913114</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>333.522961012568</v>
+        <v>336.623555048343</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>328.994547875869</v>
+        <v>327.120019710093</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>328.994547875869</v>
+        <v>327.120019710093</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>332.773716206409</v>
+        <v>329.570914268288</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>332.773716206409</v>
+        <v>329.570914268288</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.00944176952932836</v>
+        <v>-0.0022067424226523</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0.0188396915105677</v>
+        <v>0.00881231512173652</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.0094864836512667</v>
+        <v>-0.00220430935663807</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.998526429162209</v>
+        <v>1.00196551856947</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>1.00041010056224</v>
+        <v>0.979494238907664</v>
       </c>
     </row>
     <row r="85">
@@ -6363,46 +6421,46 @@
         <v>344.852</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1.01106712553076</v>
+        <v>9.97690188123514</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>336.869839318612</v>
+        <v>332.570326518898</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>334.298121153541</v>
+        <v>338.798086816119</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>334.526343993889</v>
+        <v>338.803516331914</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>341.077255201003</v>
+        <v>334.875098118765</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>341.077255201003</v>
+        <v>334.875098118765</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>336.478365444727</v>
+        <v>332.502901418805</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>336.478365444727</v>
+        <v>332.502901418805</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.0110711260514993</v>
+        <v>0.00885703753322363</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.0182206112379681</v>
+        <v>0.00667188893366699</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.0111326377592289</v>
+        <v>0.00889637714853087</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.998837907618335</v>
+        <v>0.999797260625148</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>1.00652185625113</v>
+        <v>0.981419064503954</v>
       </c>
     </row>
     <row r="86">
@@ -6422,46 +6480,46 @@
         <v>332.281</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>0.992581638086184</v>
+        <v>-0.860389727597691</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>336.423556496238</v>
+        <v>332.594091178879</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>335.951009103465</v>
+        <v>341.164627104018</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>335.506759284531</v>
+        <v>341.252101364063</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>334.764403501033</v>
+        <v>333.141389727598</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>334.764403501033</v>
+        <v>333.141389727598</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>336.431187763475</v>
+        <v>333.860931295625</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>336.431187763475</v>
+        <v>333.860931295625</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>-0.000140219977870711</v>
+        <v>0.00407594677341715</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.020015825132242</v>
+        <v>0.0026162045249587</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>-0.00014021014750909</v>
+        <v>0.00408426474182622</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00002268351038</v>
+        <v>1.00380896759848</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>1.00142931155733</v>
+        <v>0.97859187257955</v>
       </c>
     </row>
     <row r="87">
@@ -6481,46 +6539,46 @@
         <v>317.285</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1.00750944292085</v>
+        <v>-8.64462072117948</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0</v>
+        <v>0.328782963460522</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>335.118688850828</v>
+        <v>338.378987218849</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>337.599620505446</v>
+        <v>343.56531404923</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>336.476600486725</v>
+        <v>343.943922091001</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>314.920125294474</v>
+        <v>325.92962072118</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>335.118688850828</v>
+        <v>334.285847608539</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>335.516969399917</v>
+        <v>339.690024758805</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>335.516969399917</v>
+        <v>339.690024758805</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>-0.00272109959053658</v>
+        <v>0.017308976977678</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0178082857805004</v>
+        <v>0.0284319039845751</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>-0.00271740075477322</v>
+        <v>0.0174596453695837</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00118847609023</v>
+        <v>1.00387446499185</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.993831002823964</v>
+        <v>0.988720370968911</v>
       </c>
     </row>
     <row r="88">
@@ -6540,80 +6598,106 @@
         <v>355.915</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.987629225089268</v>
+        <v>-1.13201409054553</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>337.066096396978</v>
+        <v>354.333528101584</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>339.246868924596</v>
+        <v>345.990328400817</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>337.444549423785</v>
+        <v>346.813036900756</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>360.373094435141</v>
+        <v>357.047014090546</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>337.066096396978</v>
+        <v>357.047014090546</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>336.416960548261</v>
+        <v>352.684377321363</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>336.416960548261</v>
+        <v>352.684377321363</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.00267881006279969</v>
+        <v>0.0375400318563866</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0.0109481132806557</v>
+        <v>0.0701319869333477</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.00268240128049002</v>
+        <v>0.0382535594672953</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.998074158582974</v>
+        <v>0.995345767054401</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.991658262358306</v>
+        <v>1.0193475030111</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
         <v>139</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="n">
+        <v>373.783</v>
+      </c>
       <c r="C89" s="3" t="n">
-        <v>339.945234078288</v>
+        <v>373.783</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>378.003507086034</v>
+        <v>373.783</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>305.718756588784</v>
+        <v>373.783</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1.01292930858347</v>
-      </c>
-      <c r="G89" s="7"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="12"/>
-      <c r="M89" s="13"/>
+        <v>11.4253665041768</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>359.241423657568</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>348.424051241313</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>349.745213808946</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>362.357633495823</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>362.357633495823</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>360.587427027397</v>
+      </c>
       <c r="N89" s="14" t="n">
-        <v>335.606079513766</v>
-      </c>
-      <c r="O89" s="15"/>
-      <c r="P89" s="16"/>
-      <c r="Q89" s="17"/>
-      <c r="R89" s="18"/>
-      <c r="S89" s="19"/>
+        <v>360.587427027397</v>
+      </c>
+      <c r="O89" s="15" t="n">
+        <v>0.0221609016119005</v>
+      </c>
+      <c r="P89" s="16" t="n">
+        <v>0.0844640016335325</v>
+      </c>
+      <c r="Q89" s="17" t="n">
+        <v>0.0224082783764272</v>
+      </c>
+      <c r="R89" s="18" t="n">
+        <v>1.00374679332947</v>
+      </c>
+      <c r="S89" s="19" t="n">
+        <v>1.0349096904842</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
@@ -6621,16 +6705,16 @@
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3" t="n">
-        <v>336.679700552532</v>
+        <v>346.122717639737</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>379.177450186792</v>
+        <v>376.710118416795</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>298.945047255057</v>
+        <v>315.535316862679</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>0.992364505303043</v>
+        <v>-0.90073166429486</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -6640,7 +6724,7 @@
       <c r="L90" s="12"/>
       <c r="M90" s="13"/>
       <c r="N90" s="14" t="n">
-        <v>339.270196337503</v>
+        <v>347.023449304032</v>
       </c>
       <c r="O90" s="15"/>
       <c r="P90" s="16"/>
@@ -6654,16 +6738,16 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
-        <v>343.242440761618</v>
+        <v>340.448046464769</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>390.849556552598</v>
+        <v>376.705212001354</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>301.43407140885</v>
+        <v>304.190880928184</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>1.0073298729474</v>
+        <v>-10.1124926431591</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -6673,7 +6757,7 @@
       <c r="L91" s="12"/>
       <c r="M91" s="13"/>
       <c r="N91" s="14" t="n">
-        <v>340.744824490618</v>
+        <v>350.560539107928</v>
       </c>
       <c r="O91" s="15"/>
       <c r="P91" s="16"/>
@@ -6687,16 +6771,16 @@
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3" t="n">
-        <v>339.945234078288</v>
+        <v>348.859693415875</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>391.000874925807</v>
+        <v>385.766141601964</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>295.556275147645</v>
+        <v>311.953245229787</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.986443389410891</v>
+        <v>-0.858378722624383</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
@@ -6706,7 +6790,7 @@
       <c r="L92" s="12"/>
       <c r="M92" s="13"/>
       <c r="N92" s="14" t="n">
-        <v>344.617073546719</v>
+        <v>349.718072138499</v>
       </c>
       <c r="O92" s="15"/>
       <c r="P92" s="16"/>
@@ -6719,10 +6803,18 @@
         <v>143</v>
       </c>
       <c r="B93" s="2"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
+      <c r="C93" s="3" t="n">
+        <v>344.503677947775</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>383.593116372733</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>305.414239522817</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>12.77042660226</v>
+      </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
       <c r="I93" s="9"/>
@@ -6730,7 +6822,9 @@
       <c r="K93" s="11"/>
       <c r="L93" s="12"/>
       <c r="M93" s="13"/>
-      <c r="N93" s="14"/>
+      <c r="N93" s="14" t="n">
+        <v>331.733251345515</v>
+      </c>
       <c r="O93" s="15"/>
       <c r="P93" s="16"/>
       <c r="Q93" s="17"/>
@@ -7118,6 +7212,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -7126,7 +7326,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -7136,80 +7336,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.18166587788623</v>
+        <v>0.125165183071812</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.104693170072222</v>
+        <v>0.0782920477791863</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.181158701800193</v>
+        <v>0.206452701639453</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.328873486551596</v>
+        <v>0.405104710087746</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.468243527587803</v>
+        <v>0.510384249257591</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.49620024218763</v>
+        <v>0.450811009210763</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.389986909824501</v>
+        <v>0.321801190288771</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.273040971195524</v>
+        <v>0.22270322477442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.168171626210785</v>
+        <v>0.161007966463821</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/GR-EPRIV-FOR_out.xlsx
+++ b/indicadores/GR-EPRIV-FOR_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocupados en el sector privado formal del Gran Rosario</t>
+    <t xml:space="preserve">Ocupados en el sector privado formal</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -74,6 +74,12 @@
     <t xml:space="preserve">const</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglomerado Gran Rosario</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -107,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/05/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">vcorvalan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1086,9 +1092,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1099,7 +1109,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1113,12 +1123,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.510384249257591</v>
+        <v>0.50185533493928</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1129,7 +1139,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1157,7 +1167,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1171,12 +1181,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.260492081890234</v>
+        <v>0.251858777207017</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1199,7 +1209,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1213,7 +1223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1227,7 +1237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1241,12 +1251,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.317906197644644</v>
+        <v>0.276373862774229</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1257,7 +1267,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1271,12 +1281,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.307296559920668</v>
+        <v>0.21976401017304</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1419,10 +1429,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1435,10 +1445,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1462,66 +1472,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>187.428</v>
@@ -1574,7 +1584,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>193.778</v>
@@ -1631,7 +1641,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>202.718</v>
@@ -1688,7 +1698,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>196.406</v>
@@ -1745,7 +1755,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>206.403</v>
@@ -1804,7 +1814,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>221.58</v>
@@ -1863,7 +1873,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>220.366</v>
@@ -1922,7 +1932,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>229.158</v>
@@ -1981,7 +1991,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>234.538</v>
@@ -2040,7 +2050,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>241.824</v>
@@ -2099,7 +2109,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>247.933</v>
@@ -2158,7 +2168,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>265.114</v>
@@ -2217,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>274.574</v>
@@ -2276,7 +2286,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>270.671</v>
@@ -2335,7 +2345,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>264.265</v>
@@ -2394,7 +2404,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>282.778</v>
@@ -2453,7 +2463,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>292.243</v>
@@ -2512,7 +2522,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>306.237</v>
@@ -2571,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>280.597</v>
@@ -2630,7 +2640,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>290.531</v>
@@ -2689,7 +2699,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>288.02</v>
@@ -2748,7 +2758,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>293.355</v>
@@ -2807,7 +2817,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>280.514</v>
@@ -2866,7 +2876,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>273.279</v>
@@ -2925,7 +2935,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>294.75</v>
@@ -2984,7 +2994,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>298.139</v>
@@ -3043,7 +3053,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>296.237</v>
@@ -3102,7 +3112,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>291.018</v>
@@ -3161,7 +3171,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>313.284</v>
@@ -3220,7 +3230,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>314.394</v>
@@ -3279,7 +3289,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>301.481</v>
@@ -3338,7 +3348,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>309.323</v>
@@ -3397,7 +3407,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>319.058</v>
@@ -3456,7 +3466,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>317.946</v>
@@ -3515,7 +3525,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>314.546</v>
@@ -3574,7 +3584,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>329.818</v>
@@ -3633,7 +3643,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>340.482</v>
@@ -3692,7 +3702,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>329.749</v>
@@ -3751,7 +3761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>309.118</v>
@@ -3810,7 +3820,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>319.451</v>
@@ -3869,7 +3879,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>351.422</v>
@@ -3928,7 +3938,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>358.827</v>
@@ -3987,7 +3997,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>338.369</v>
@@ -4046,7 +4056,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>336.904</v>
@@ -4105,7 +4115,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>359.582</v>
@@ -4164,7 +4174,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>362.479</v>
@@ -4223,7 +4233,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>327.6245</v>
@@ -4282,7 +4292,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>336.2245</v>
@@ -4341,7 +4351,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>337.3735</v>
@@ -4400,7 +4410,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>298.598</v>
@@ -4459,7 +4469,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>316.88</v>
@@ -4518,7 +4528,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>335.545</v>
@@ -4577,7 +4587,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>315.165</v>
@@ -4636,7 +4646,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>293.215</v>
@@ -4695,7 +4705,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>315.244</v>
@@ -4754,7 +4764,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>327.515</v>
@@ -4813,7 +4823,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>324.057</v>
@@ -4872,7 +4882,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>304.316</v>
@@ -4931,7 +4941,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>326.08</v>
@@ -4990,7 +5000,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>287.232</v>
@@ -5049,7 +5059,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>285.117</v>
@@ -5108,7 +5118,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>294.649</v>
@@ -5167,7 +5177,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>293.701</v>
@@ -5226,7 +5236,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>292.276</v>
@@ -5285,7 +5295,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>280.81</v>
@@ -5344,7 +5354,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>256.914</v>
@@ -5403,7 +5413,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>306.755</v>
@@ -5462,7 +5472,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>287.002</v>
@@ -5521,7 +5531,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>300.125</v>
@@ -5580,7 +5590,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>318.876</v>
@@ -5639,7 +5649,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>327.007</v>
@@ -5698,7 +5708,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>348.079</v>
@@ -5757,7 +5767,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>333.69</v>
@@ -5816,7 +5826,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>342.148</v>
@@ -5875,7 +5885,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>329.742</v>
@@ -5934,7 +5944,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>305.407</v>
@@ -5993,7 +6003,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>324.625</v>
@@ -6052,7 +6062,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>325.422</v>
@@ -6111,7 +6121,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>321.243</v>
@@ -6170,7 +6180,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>338.9</v>
@@ -6229,7 +6239,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>335.07</v>
@@ -6288,7 +6298,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>322.848</v>
@@ -6347,7 +6357,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>325.352</v>
@@ -6406,7 +6416,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>344.852</v>
@@ -6465,7 +6475,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>332.281</v>
@@ -6524,7 +6534,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>317.285</v>
@@ -6583,7 +6593,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>355.915</v>
@@ -6642,7 +6652,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>373.783</v>
@@ -6701,7 +6711,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3" t="n">
@@ -6734,7 +6744,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
@@ -6767,7 +6777,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3" t="n">
@@ -6800,7 +6810,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3" t="n">
@@ -6833,7 +6843,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
@@ -6856,7 +6866,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
@@ -6879,7 +6889,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -6902,7 +6912,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
@@ -6925,7 +6935,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="3"/>
@@ -6948,7 +6958,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="3"/>
@@ -6971,7 +6981,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="3"/>
@@ -6994,7 +7004,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="3"/>
@@ -7017,7 +7027,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="3"/>
@@ -7040,7 +7050,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="3"/>
@@ -7063,7 +7073,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="3"/>
@@ -7086,7 +7096,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="3"/>
@@ -7109,7 +7119,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="3"/>
@@ -7132,7 +7142,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="3"/>
@@ -7155,7 +7165,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="3"/>
@@ -7178,7 +7188,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="3"/>
@@ -7212,97 +7222,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7326,7 +7336,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -7336,80 +7346,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.125165183071812</v>
+        <v>0.129884158777597</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0782920477791863</v>
+        <v>0.0788479318001665</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.206452701639453</v>
+        <v>0.212296402428649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.405104710087746</v>
+        <v>0.405559896985056</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.510384249257591</v>
+        <v>0.50185533493928</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.450811009210763</v>
+        <v>0.454695013463935</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.321801190288771</v>
+        <v>0.332154177242986</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.22270322477442</v>
+        <v>0.223528962663784</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.161007966463821</v>
+        <v>0.160930672559236</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/GR-EPRIV-FOR_out.xlsx
+++ b/indicadores/GR-EPRIV-FOR_out.xlsx
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">04/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1108,9 +1108,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1122,14 +1120,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>0.50185533493928</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1139,13 +1133,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1154,10 +1146,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.500863481293228</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1167,11 +1163,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1180,14 +1178,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.251858777207017</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1196,7 +1190,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1209,11 +1205,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.250864226893172</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1222,9 +1220,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1237,7 +1233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1251,13 +1247,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.276373862774229</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1267,7 +1261,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1286,7 +1280,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.21976401017304</v>
+        <v>0.33952589362822</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1296,7 +1290,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1308,10 +1304,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.324474764939864</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1546,40 +1546,40 @@
         <v>187.428</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.66220156240624</v>
+        <v>1.66220156127063</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>185.763616817716</v>
+        <v>185.763616818725</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>189.989588472999</v>
+        <v>189.989657765462</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>182.652459219421</v>
+        <v>182.652459272038</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>185.765798437594</v>
+        <v>185.765798438729</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>185.765798437594</v>
+        <v>185.765798438729</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>187.510579325657</v>
+        <v>187.510579326284</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>187.510579325657</v>
+        <v>187.510579326284</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>1.00940422316204</v>
+        <v>1.00940422315993</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.986951868429916</v>
+        <v>0.986951508475064</v>
       </c>
     </row>
     <row r="3">
@@ -1599,44 +1599,44 @@
         <v>193.778</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2.77785889821579</v>
+        <v>2.77785889860556</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>191.187053591071</v>
+        <v>191.187053590747</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>195.947833238304</v>
+        <v>195.947906770797</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>189.551624022892</v>
+        <v>189.551624117038</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>191.000141101784</v>
+        <v>191.000141101394</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>191.000141101784</v>
+        <v>191.000141101394</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>190.671485998139</v>
+        <v>190.671485998005</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>190.671485998139</v>
+        <v>190.671485998005</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.0167167117173488</v>
+        <v>0.0167167117133015</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.0168572177839197</v>
+        <v>0.0168572177798041</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>0.997303334178501</v>
+        <v>0.99730333417949</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.97307269413003</v>
+        <v>0.97307232896872</v>
       </c>
     </row>
     <row r="4">
@@ -1656,44 +1656,44 @@
         <v>202.718</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-4.48183521396759</v>
+        <v>-4.48183521274575</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>194.919863351393</v>
+        <v>194.919863350501</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>201.903438134838</v>
+        <v>201.903515864052</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>196.466355522453</v>
+        <v>196.466355657871</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>207.199835213968</v>
+        <v>207.199835212746</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>194.919863351393</v>
+        <v>194.919863350501</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>194.328165278306</v>
+        <v>194.328165277837</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>194.328165278306</v>
+        <v>194.328165277837</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.0189963249573456</v>
+        <v>0.018996324955638</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0191779030882593</v>
+        <v>0.0191779030865189</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.996964403407052</v>
+        <v>0.996964403409211</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.96248071391695</v>
+        <v>0.962480343376905</v>
       </c>
     </row>
     <row r="5">
@@ -1713,44 +1713,44 @@
         <v>196.406</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.0667933086518215</v>
+        <v>-0.0667933089519626</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>197.623552074322</v>
+        <v>197.623552074522</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>207.850670986242</v>
+        <v>207.850752779605</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>203.41946299959</v>
+        <v>203.419463175293</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>196.472793308652</v>
+        <v>196.472793308952</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>196.472793308652</v>
+        <v>196.472793308952</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>198.144736388585</v>
+        <v>198.144736388846</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>198.144736388585</v>
+        <v>198.144736388846</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0194494519480447</v>
+        <v>0.0194494519517718</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.0196398247511556</v>
+        <v>0.0196398247549558</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>1.00263725810407</v>
+        <v>1.00263725810437</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.95330332804988</v>
+        <v>0.953302952907507</v>
       </c>
     </row>
     <row r="6">
@@ -1770,46 +1770,46 @@
         <v>206.403</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.68950441435661</v>
+        <v>1.68950441302129</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>205.393981656429</v>
+        <v>205.393981657721</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>213.779434881919</v>
+        <v>213.779520469013</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>210.426023274934</v>
+        <v>210.426023488523</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>204.713495585643</v>
+        <v>204.713495586979</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>204.713495585643</v>
+        <v>204.713495586979</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>206.057529375965</v>
+        <v>206.057529376809</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>206.057529375965</v>
+        <v>206.057529376809</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.0391576431050139</v>
+        <v>0.0391576431077916</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>0.0989114860452578</v>
+        <v>0.0989114860460814</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.0399344092182305</v>
+        <v>0.0399344092211191</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>1.00323060935956</v>
+        <v>1.00323060935736</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.963879100390461</v>
+        <v>0.963878714503321</v>
       </c>
     </row>
     <row r="7">
@@ -1829,46 +1829,46 @@
         <v>221.58</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>3.24966697607774</v>
+        <v>3.24966697567398</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>217.217005977974</v>
+        <v>217.217005977423</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>219.672521737724</v>
+        <v>219.672610659163</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>217.466379820659</v>
+        <v>217.466380067446</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>218.330333023922</v>
+        <v>218.330333024326</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>218.330333023922</v>
+        <v>218.330333024326</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>216.697937183028</v>
+        <v>216.697937182717</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>216.697937183028</v>
+        <v>216.697937182717</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0503489906511149</v>
+        <v>0.0503489906455864</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.136498916178495</v>
+        <v>0.136498916177663</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0516380441874</v>
+        <v>0.051638044181586</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.997610367601702</v>
+        <v>0.997610367602802</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.986459004835173</v>
+        <v>0.986458605524284</v>
       </c>
     </row>
     <row r="8">
@@ -1888,46 +1888,46 @@
         <v>220.366</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-5.05158709862313</v>
+        <v>-5.0515870952369</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>225.431290800054</v>
+        <v>225.431290798689</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>225.50705725745</v>
+        <v>225.507148811391</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>224.492313470494</v>
+        <v>224.492313742442</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>225.417587098623</v>
+        <v>225.417587095237</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>225.417587098623</v>
+        <v>225.417587095237</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>224.599375140099</v>
+        <v>224.599375139025</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>224.599375140099</v>
+        <v>224.599375139025</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.0358138709316139</v>
+        <v>0.0358138709282663</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.155773661622547</v>
+        <v>0.155773661619806</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0364629126598335</v>
+        <v>0.0364629126563638</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.996309670866884</v>
+        <v>0.996309670868152</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.995974928109165</v>
+        <v>0.995974523747248</v>
       </c>
     </row>
     <row r="9">
@@ -1947,46 +1947,46 @@
         <v>229.158</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.0739933392257658</v>
+        <v>-0.073993341298438</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>229.346096096511</v>
+        <v>229.346096096992</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>231.259328276947</v>
+        <v>231.259421463511</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>231.459924824185</v>
+        <v>231.459925108673</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>229.231993339226</v>
+        <v>229.231993341298</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>229.231993339226</v>
+        <v>229.231993341298</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>229.181307422484</v>
+        <v>229.181307423017</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>229.181307422484</v>
+        <v>229.181307423017</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0201951655670093</v>
+        <v>0.020195165574117</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.156635859218749</v>
+        <v>0.156635859219916</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0204004676305396</v>
+        <v>0.0204004676377922</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.999281484721859</v>
+        <v>0.999281484722087</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.991014326341141</v>
+        <v>0.991013927011739</v>
       </c>
     </row>
     <row r="10">
@@ -2006,46 +2006,46 @@
         <v>234.538</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.69434408714024</v>
+        <v>1.69434408576735</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>232.250964936114</v>
+        <v>232.25096493851</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>236.905565713213</v>
+        <v>236.905659177265</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>238.329940849618</v>
+        <v>238.329941128069</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>232.84365591286</v>
+        <v>232.843655914233</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>232.84365591286</v>
+        <v>232.843655914233</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>233.172003316667</v>
+        <v>233.172003318069</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>233.172003316667</v>
+        <v>233.172003318069</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.0172629671146029</v>
+        <v>0.0172629671182923</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.131586911785345</v>
+        <v>0.131586911787519</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0174128332675332</v>
+        <v>0.0174128332712868</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>1.00396570313844</v>
+        <v>1.00396570313412</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.984240292602218</v>
+        <v>0.984239904305529</v>
       </c>
     </row>
     <row r="11">
@@ -2065,46 +2065,46 @@
         <v>241.824</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4.05529189827914</v>
+        <v>4.05529189748718</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>239.543029279208</v>
+        <v>239.543029277179</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>242.42073339891</v>
+        <v>242.420825371818</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>245.051948857253</v>
+        <v>245.051949103718</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>237.768708101721</v>
+        <v>237.768708102513</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>237.768708101721</v>
+        <v>237.768708102513</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>240.494060484996</v>
+        <v>240.494060483905</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>240.494060484996</v>
+        <v>240.494060483905</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0309189998317598</v>
+        <v>0.0309189998212076</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.109812412666715</v>
+        <v>0.109812412663272</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.0314019567708814</v>
+        <v>0.0314019567599979</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.00397018944216</v>
+        <v>1.00397018944611</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.992052359190154</v>
+        <v>0.992051982807347</v>
       </c>
     </row>
     <row r="12">
@@ -2124,46 +2124,46 @@
         <v>247.933</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>-5.66216982368374</v>
+        <v>-5.66216981636264</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>252.649315478455</v>
+        <v>252.64931547684</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>247.777256473077</v>
+        <v>247.777344714296</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>251.548104732868</v>
+        <v>251.548104912642</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>253.595169823684</v>
+        <v>253.595169816363</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>253.595169823684</v>
+        <v>253.595169816363</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>252.676386034507</v>
+        <v>252.676386032994</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>252.676386034507</v>
+        <v>252.676386032994</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>0.04941417067669</v>
+        <v>0.0494141706752404</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0.125009301013836</v>
+        <v>0.125009301012481</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>0.0506554113018123</v>
+        <v>0.0506554113002893</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>1.00010714676191</v>
+        <v>1.00010714676231</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.01977231337196</v>
+        <v>1.01977195019322</v>
       </c>
     </row>
     <row r="13">
@@ -2183,46 +2183,46 @@
         <v>265.114</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.632496388938652</v>
+        <v>-0.632496396738306</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>266.220590618631</v>
+        <v>266.220590620653</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>252.94465255894</v>
+        <v>252.944734298531</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>257.704148158463</v>
+        <v>257.704148226857</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>265.746496388939</v>
+        <v>265.746496396738</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>265.746496388939</v>
+        <v>265.746496396738</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>264.403985269398</v>
+        <v>264.40398527127</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>264.403985269398</v>
+        <v>264.40398527127</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.0453686173541965</v>
+        <v>0.0453686173672646</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.153689139149482</v>
+        <v>0.153689139154969</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.0464135150060663</v>
+        <v>0.0464135150197409</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0.993176315381873</v>
+        <v>0.993176315381363</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.0453037160285</v>
+        <v>1.04530337824394</v>
       </c>
     </row>
     <row r="14">
@@ -2242,46 +2242,46 @@
         <v>274.574</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>2.04622152396949</v>
+        <v>2.04622152475794</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>270.117247426982</v>
+        <v>270.117247429472</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>257.89607547557</v>
+        <v>257.896147359046</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>263.41605414149</v>
+        <v>263.416054042897</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>272.527778476031</v>
+        <v>272.527778475242</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>272.527778476031</v>
+        <v>272.527778475242</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>269.147362053601</v>
+        <v>269.147362054823</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>269.147362053601</v>
+        <v>269.147362054823</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>0.0177808631883466</v>
+        <v>0.0177808631858067</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.154286784970822</v>
+        <v>0.154286784969121</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.0179398838461913</v>
+        <v>0.0179398838436058</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>0.996409391171353</v>
+        <v>0.996409391166694</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.04362721129929</v>
+        <v>1.04362692041349</v>
       </c>
     </row>
     <row r="15">
@@ -2301,46 +2301,46 @@
         <v>270.671</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4.88360512659586</v>
+        <v>4.88360512792905</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>267.676103274893</v>
+        <v>267.676103270519</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>262.612680194431</v>
+        <v>262.612738231672</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>268.620009430557</v>
+        <v>268.620009098143</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>265.787394873404</v>
+        <v>265.787394872071</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>265.787394873404</v>
+        <v>265.787394872071</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>268.576357434132</v>
+        <v>268.576357431586</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>268.576357434132</v>
+        <v>268.576357431586</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.00212378518335524</v>
+        <v>-0.00212378519737757</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.116769191274426</v>
+        <v>0.116769191268905</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.00212153154729799</v>
+        <v>-0.00212153156129058</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>1.00336322199937</v>
+        <v>1.00336322200625</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.02270902241006</v>
+        <v>1.02270879638235</v>
       </c>
     </row>
     <row r="16">
@@ -2360,46 +2360,46 @@
         <v>264.265</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-5.93786151369005</v>
+        <v>-5.93786150695996</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>271.60354860161</v>
+        <v>271.603548601132</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>267.084766501364</v>
+        <v>267.08480602169</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>273.297759395941</v>
+        <v>273.297758752143</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>270.20286151369</v>
+        <v>270.20286150696</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>270.20286151369</v>
+        <v>270.20286150696</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>272.730600642982</v>
+        <v>272.730600642167</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>272.730600642982</v>
+        <v>272.730600642167</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0153492383863812</v>
+        <v>0.0153492383928749</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.0793671894837715</v>
+        <v>0.0793671894870092</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0154676429769833</v>
+        <v>0.0154676429835774</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1.00414962192937</v>
+        <v>1.00414962192814</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.0211387351498</v>
+        <v>1.02113858404966</v>
       </c>
     </row>
     <row r="17">
@@ -2419,46 +2419,46 @@
         <v>282.778</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-1.95128467114375</v>
+        <v>-1.95128468267884</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>282.005527549452</v>
+        <v>282.005527553449</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>271.304618378883</v>
+        <v>271.304633994781</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>277.416886335137</v>
+        <v>277.41688529331</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>284.729284671144</v>
+        <v>284.729284682679</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>284.729284671144</v>
+        <v>284.729284682679</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>282.226794331557</v>
+        <v>282.226794334849</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>282.226794331557</v>
+        <v>282.226794334849</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.0342264857975161</v>
+        <v>0.0342264858121663</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.0674074902615396</v>
+        <v>0.0674074902664301</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.034818951984805</v>
+        <v>0.0348189519999653</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>1.0007846185996</v>
+        <v>1.00078461859709</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.04025798019192</v>
+        <v>1.04025792032833</v>
       </c>
     </row>
     <row r="18">
@@ -2478,46 +2478,46 @@
         <v>292.243</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>2.9972535297494</v>
+        <v>2.9972535329226</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>292.540135013894</v>
+        <v>292.540135010114</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>275.266468618885</v>
+        <v>275.266454201303</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>280.929498056225</v>
+        <v>280.929496523832</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>289.245746470251</v>
+        <v>289.245746467077</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>289.245746470251</v>
+        <v>289.245746467077</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>290.986771147545</v>
+        <v>290.986771147634</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>290.986771147545</v>
+        <v>290.986771147634</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.030566823231538</v>
+        <v>0.0305668232201817</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0811429431346025</v>
+        <v>0.0811429431300239</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.0310387850903213</v>
+        <v>0.0310387850786125</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.994690082896572</v>
+        <v>0.99469008290973</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.0571093987856</v>
+        <v>1.05710945415395</v>
       </c>
     </row>
     <row r="19">
@@ -2537,46 +2537,46 @@
         <v>306.237</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>5.51069302146658</v>
+        <v>5.51069302629821</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>296.25316002415</v>
+        <v>296.253160035679</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>278.972940429699</v>
+        <v>278.972889098296</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>283.824264358967</v>
+        <v>283.824262242846</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>300.726306978533</v>
+        <v>300.726306973702</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>300.726306978533</v>
+        <v>300.726306973702</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>295.678991885777</v>
+        <v>295.678991906972</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>295.678991885777</v>
+        <v>295.678991906972</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.0159965728062094</v>
+        <v>0.0159965728775846</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.100912212491719</v>
+        <v>0.100912212581072</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0161252029421413</v>
+        <v>0.0161252030146675</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.998061900374915</v>
+        <v>0.998061900407618</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.05988412865544</v>
+        <v>1.05988432375158</v>
       </c>
     </row>
     <row r="20">
@@ -2596,46 +2596,46 @@
         <v>280.597</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-6.16061833467602</v>
+        <v>-6.16061833096774</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.400192782926635</v>
+        <v>0.400192774354102</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>295.527083975286</v>
+        <v>295.527084015172</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>282.435394068312</v>
+        <v>282.435298200464</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>286.131436285195</v>
+        <v>286.131433499204</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>286.757618334676</v>
+        <v>286.757618330968</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>292.017607115791</v>
+        <v>292.017607213407</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>294.672937293866</v>
+        <v>294.672937347808</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>294.672937293866</v>
+        <v>294.672937347808</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.00340832481813555</v>
+        <v>-0.00340832470676194</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0804542526550132</v>
+        <v>0.0804542528560239</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.00340252307238564</v>
+        <v>-0.00340252296139099</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.997109751600664</v>
+        <v>0.997109751648615</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.04332864606408</v>
+        <v>1.04332900039519</v>
       </c>
     </row>
     <row r="21">
@@ -2655,46 +2655,46 @@
         <v>290.531</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-3.3992279653489</v>
+        <v>-3.3992279907145</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>290.169536376359</v>
+        <v>290.169536419852</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>285.678785645805</v>
+        <v>285.678636908684</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>287.96577508984</v>
+        <v>287.96577156541</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>293.930227965349</v>
+        <v>293.930227990715</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>293.930227965349</v>
+        <v>293.930227990715</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>290.931622099677</v>
+        <v>290.931622138208</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>290.931622099677</v>
+        <v>290.931622138208</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0127777901942392</v>
+        <v>-0.0127777902448555</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0308433782438604</v>
+        <v>0.0308433783683619</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.0126965008342705</v>
+        <v>-0.0126965008842442</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.00262634642091</v>
+        <v>1.00262634640341</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.01838721220408</v>
+        <v>1.01838774255705</v>
       </c>
     </row>
     <row r="22">
@@ -2714,46 +2714,46 @@
         <v>288.02</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4.1715746477788</v>
+        <v>4.17157464200265</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>287.079906873757</v>
+        <v>287.079906843319</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>288.734060156412</v>
+        <v>288.733849566967</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>289.471472881983</v>
+        <v>289.471468582544</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>283.848425352221</v>
+        <v>283.848425357997</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>283.848425352221</v>
+        <v>283.848425357997</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>287.261127596749</v>
+        <v>287.261127574051</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>287.261127596749</v>
+        <v>287.261127574051</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0126966096094819</v>
+        <v>-0.0126966098209345</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0128034808458938</v>
+        <v>-0.012803480924198</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0126163477054805</v>
+        <v>-0.0126163479142652</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>1.00063125533572</v>
+        <v>1.00063125536275</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>0.994898653249065</v>
+        <v>0.994899378804653</v>
       </c>
     </row>
     <row r="23">
@@ -2773,46 +2773,46 @@
         <v>293.355</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5.93756828279724</v>
+        <v>5.93756841050462</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>286.462316524264</v>
+        <v>286.462316414046</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>291.637319745816</v>
+        <v>291.637037763748</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>290.822544035086</v>
+        <v>290.822538973807</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>287.417431717203</v>
+        <v>287.417431589495</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>287.417431717203</v>
+        <v>287.417431589495</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>286.423770717413</v>
+        <v>286.423770652083</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>286.423770717413</v>
+        <v>286.423770652083</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.00291922439112635</v>
+        <v>-0.00291922454020134</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0313015852405906</v>
+        <v>-0.0313015855309774</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.00291496759878829</v>
+        <v>-0.00291496774742872</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.99986544196347</v>
+        <v>0.999865442120117</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.982123176029229</v>
+        <v>0.98212412541411</v>
       </c>
     </row>
     <row r="24">
@@ -2832,46 +2832,46 @@
         <v>280.514</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-6.49779408302356</v>
+        <v>-6.49779407134297</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>284.552908889156</v>
+        <v>284.552909014209</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>294.42161303795</v>
+        <v>294.421249697334</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>292.164887684958</v>
+        <v>292.164881946281</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>287.011794083024</v>
+        <v>287.011794071343</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>287.011794083024</v>
+        <v>287.011794071343</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>284.854624940801</v>
+        <v>284.854625025573</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>284.854624940801</v>
+        <v>284.854625025573</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.00549346775477592</v>
+        <v>-0.00549346722909031</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0333193554970864</v>
+        <v>-0.0333193553863611</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.00547840625336815</v>
+        <v>-0.00547840573056246</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.00106031617397</v>
+        <v>1.00106031603194</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.967505822692725</v>
+        <v>0.967507016964314</v>
       </c>
     </row>
     <row r="25">
@@ -2891,46 +2891,46 @@
         <v>273.279</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-4.55980255150752</v>
+        <v>-4.55980312981232</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.968569708328098</v>
+        <v>0.968569725805573</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>282.251021499218</v>
+        <v>282.251021726471</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>297.117351226727</v>
+        <v>297.116896312172</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>293.627377405823</v>
+        <v>293.627371170126</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>277.838802551508</v>
+        <v>277.838803129812</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>277.977479879954</v>
+        <v>277.977480370111</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>283.065060118325</v>
+        <v>283.065060262392</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>283.065060118325</v>
+        <v>283.065060262392</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.00630219656992552</v>
+        <v>-0.00630219635856959</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.0270392125977208</v>
+        <v>-0.0270392122313875</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.00628237938158249</v>
+        <v>-0.00628237917155439</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.00288409450135</v>
+        <v>1.00288409420431</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.952704575985267</v>
+        <v>0.95270603515252</v>
       </c>
     </row>
     <row r="26">
@@ -2950,46 +2950,46 @@
         <v>294.75</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>5.45651336963402</v>
+        <v>5.4565137619991</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>285.985302508958</v>
+        <v>285.985302132484</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>299.750314369214</v>
+        <v>299.749757642942</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>295.313121303893</v>
+        <v>295.313114876125</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>289.293486630366</v>
+        <v>289.293486238001</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>289.293486630366</v>
+        <v>289.293486238001</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>287.144641472812</v>
+        <v>287.144641165845</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>287.144641472812</v>
+        <v>287.144641165845</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.014309300430313</v>
+        <v>0.0143092988523253</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>-0.000405506045704995</v>
+        <v>-0.000405507035324715</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0144121685409784</v>
+        <v>0.0144121669402484</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.00405384106695</v>
+        <v>1.00405384131533</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.957946089488084</v>
+        <v>0.957947867660623</v>
       </c>
     </row>
     <row r="27">
@@ -3009,46 +3009,46 @@
         <v>298.139</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>6.12488724943837</v>
+        <v>6.12488818273474</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>294.963641100303</v>
+        <v>294.963640335132</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>302.334320102886</v>
+        <v>302.333651589361</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>297.24697799775</v>
+        <v>297.246971841064</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>292.014112750562</v>
+        <v>292.014111817265</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>292.014112750562</v>
+        <v>292.014111817265</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>293.958617013178</v>
+        <v>293.958616553995</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>293.958617013178</v>
+        <v>293.958616553995</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.0234529329097797</v>
+        <v>0.02345293241675</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.026306637458519</v>
+        <v>0.0263066360894508</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0237301156149583</v>
+        <v>0.0237301151102289</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.996592718738566</v>
+        <v>0.996592719767105</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.972296552085593</v>
+        <v>0.972298700487565</v>
       </c>
     </row>
     <row r="28">
@@ -3068,46 +3068,46 @@
         <v>296.237</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>-7.05790466586625</v>
+        <v>-7.05790511485652</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.843907981255756</v>
+        <v>0.843907963062701</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>298.284086361782</v>
+        <v>298.284087223356</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>304.876650547881</v>
+        <v>304.875860881518</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>299.423707932611</v>
+        <v>299.423702698536</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>303.294904665866</v>
+        <v>303.294905114857</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>302.512755921221</v>
+        <v>302.51275634345</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>298.379656484801</v>
+        <v>298.379657110581</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>298.379656484801</v>
+        <v>298.379657110581</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>0.0149276917138305</v>
+        <v>0.0149276953731543</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0474804702462195</v>
+        <v>0.0474804721313309</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.0150396661834378</v>
+        <v>0.0150396698977966</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00032039967061</v>
+        <v>1.00032039887918</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.978689761740018</v>
+        <v>0.978692298720685</v>
       </c>
     </row>
     <row r="29">
@@ -3127,46 +3127,46 @@
         <v>291.018</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-5.46100134619909</v>
+        <v>-5.46100393815635</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>300.545158234486</v>
+        <v>300.545159416898</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>307.378137694744</v>
+        <v>307.377218537144</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>301.811907227455</v>
+        <v>301.811903782016</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>296.479001346199</v>
+        <v>296.479003938156</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>296.479001346199</v>
+        <v>296.479003938156</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>300.438431929212</v>
+        <v>300.438432787582</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>300.438431929212</v>
+        <v>300.438432787582</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.006876156869931</v>
+        <v>0.00687615762972788</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0613758964233364</v>
+        <v>0.0613758989155568</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.00689985191573017</v>
+        <v>0.00689985268076954</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.999644890951161</v>
+        <v>0.999644889874377</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.977422903861747</v>
+        <v>0.977425829465876</v>
       </c>
     </row>
     <row r="30">
@@ -3186,46 +3186,46 @@
         <v>313.284</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>7.00103089677007</v>
+        <v>7.00103306943461</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>304.10203021989</v>
+        <v>304.102028815738</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>309.838136099874</v>
+        <v>309.837080633635</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>304.395617241203</v>
+        <v>304.395616693204</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>306.28296910323</v>
+        <v>306.282966930565</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>306.28296910323</v>
+        <v>306.282966930565</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>304.371206998354</v>
+        <v>304.371205864504</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>304.371206998354</v>
+        <v>304.371205864504</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0130051845956948</v>
+        <v>0.013005178013418</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0599926414687173</v>
+        <v>0.0599926386531802</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0130901198088669</v>
+        <v>0.0130901131404273</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>1.00088515284909</v>
+        <v>1.00088515374203</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.982355531922777</v>
+        <v>0.982358874677129</v>
       </c>
     </row>
     <row r="31">
@@ -3245,46 +3245,46 @@
         <v>314.394</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>5.95411155924372</v>
+        <v>5.95411434127027</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>308.433867081344</v>
+        <v>308.433864691615</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>312.249188359457</v>
+        <v>312.24799186426</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>307.132214803373</v>
+        <v>307.13221853458</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>308.439888440756</v>
+        <v>308.43988565873</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>308.439888440756</v>
+        <v>308.43988565873</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>308.112367933425</v>
+        <v>308.112366368421</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>308.112367933425</v>
+        <v>308.112366368421</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.0122165152394656</v>
+        <v>0.0122165138853575</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.0481487872818938</v>
+        <v>0.0481487835952779</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0122914416641622</v>
+        <v>0.0122914402934102</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.998957639927932</v>
+        <v>0.998957642593768</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.986751541460311</v>
+        <v>0.986755317556577</v>
       </c>
     </row>
     <row r="32">
@@ -3304,46 +3304,46 @@
         <v>301.481</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-7.80572574895645</v>
+        <v>-7.80572722565926</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>310.920357773198</v>
+        <v>310.920359646054</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>314.601615090302</v>
+        <v>314.600275601226</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>309.98851350279</v>
+        <v>309.988523159811</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>309.286725748956</v>
+        <v>309.286727225659</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>309.286725748956</v>
+        <v>309.286727225659</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>310.563948134311</v>
+        <v>310.563949670564</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>310.563948134311</v>
+        <v>310.563949670564</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.00792528490006887</v>
+        <v>0.00792529492605169</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.0408348605030682</v>
+        <v>0.0408348634688176</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.00795677309979315</v>
+        <v>0.00795678320555049</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.998853694748586</v>
+        <v>0.998853693672888</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.987165778043347</v>
+        <v>0.987169986030851</v>
       </c>
     </row>
     <row r="33">
@@ -3363,46 +3363,46 @@
         <v>309.323</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-5.91945259857477</v>
+        <v>-5.91945857220652</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>312.801611826814</v>
+        <v>312.801617550327</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>316.88335609677</v>
+        <v>316.88187515036</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>312.937865296468</v>
+        <v>312.937882758185</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>315.242452598575</v>
+        <v>315.242458572206</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>315.242452598575</v>
+        <v>315.242458572206</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>312.562289794078</v>
+        <v>312.562293320978</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>312.562289794078</v>
+        <v>312.562293320978</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.00641394436276098</v>
+        <v>0.00641395069993686</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.0403538847777061</v>
+        <v>0.0403538935445329</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.00643455775138202</v>
+        <v>0.00643456412933485</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.99923490792986</v>
+        <v>0.999234900921476</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.986363858437007</v>
+        <v>0.986368479335299</v>
       </c>
     </row>
     <row r="34">
@@ -3422,46 +3422,46 @@
         <v>319.058</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>8.58047176979215</v>
+        <v>8.58047108615819</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>311.565134878655</v>
+        <v>311.565129237765</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>319.079029377387</v>
+        <v>319.077412849756</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>315.950113202651</v>
+        <v>315.950140539319</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>310.477528230208</v>
+        <v>310.477528913842</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>310.477528230208</v>
+        <v>310.477528913842</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>312.150461911142</v>
+        <v>312.150458493357</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>312.150461911142</v>
+        <v>312.150458493357</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.00131845537479329</v>
+        <v>-0.00131847760778464</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0.0255584455228397</v>
+        <v>0.0255584381142662</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.00131758659436365</v>
+        <v>-0.00131760879806087</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.00187866666376</v>
+        <v>1.00187867383306</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.978285732284682</v>
+        <v>0.978290677818487</v>
       </c>
     </row>
     <row r="35">
@@ -3481,46 +3481,46 @@
         <v>317.946</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>5.54166141442177</v>
+        <v>5.54168242646352</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>313.261955035842</v>
+        <v>313.261948686947</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>321.172227365987</v>
+        <v>321.170486402144</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>319.006623176094</v>
+        <v>319.0066625919</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>312.404338585578</v>
+        <v>312.404317573537</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>312.404338585578</v>
+        <v>312.404317573537</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>314.727327067944</v>
+        <v>314.727321833293</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>314.727327067944</v>
+        <v>314.727321833293</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.00822131431766572</v>
+        <v>0.00822130863448886</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.0214693073792753</v>
+        <v>0.0214692955782305</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.00825520212600273</v>
+        <v>0.0082551963959101</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.00467778486517</v>
+        <v>1.00467778851689</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.979933195497944</v>
+        <v>0.979938491107853</v>
       </c>
     </row>
     <row r="36">
@@ -3540,46 +3540,46 @@
         <v>314.546</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>-9.0771028704106</v>
+        <v>-9.07712327225594</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>324.145928201912</v>
+        <v>324.14593497092</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>323.141166558191</v>
+        <v>323.139318582798</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>322.061398246689</v>
+        <v>322.061451946487</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>323.623102870411</v>
+        <v>323.623123272256</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>323.623102870411</v>
+        <v>323.623123272256</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>323.676166335452</v>
+        <v>323.676172468975</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>323.676166335452</v>
+        <v>323.676172468975</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0280368937562089</v>
+        <v>0.0280369293381134</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0.042220670750458</v>
+        <v>0.0422206853445823</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.028433626501001</v>
+        <v>0.0284336630946287</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>0.998550770422859</v>
+        <v>0.998550768492633</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>1.00165562247286</v>
+        <v>1.00166136974148</v>
       </c>
     </row>
     <row r="37">
@@ -3599,46 +3599,46 @@
         <v>329.818</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-5.23612101540865</v>
+        <v>-5.23612575785286</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>332.695203530941</v>
+        <v>332.695215887347</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>324.958583519132</v>
+        <v>324.95665331147</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>325.035430021376</v>
+        <v>325.035499908549</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>335.054121015409</v>
+        <v>335.054125757853</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>335.054121015409</v>
+        <v>335.054125757853</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>331.057163691587</v>
+        <v>331.057170536559</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>331.057163691587</v>
+        <v>331.057170536559</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0225475310871875</v>
+        <v>0.0225475328137242</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.0591718019140854</v>
+        <v>0.0591718118621163</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0228036479784708</v>
+        <v>0.0228036497443789</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>0.99507645489935</v>
+        <v>0.995076438516198</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>1.01876725368018</v>
+        <v>1.01877332611264</v>
       </c>
     </row>
     <row r="38">
@@ -3658,46 +3658,46 @@
         <v>340.482</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>9.98469013488154</v>
+        <v>9.98469264172566</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>331.831451100039</v>
+        <v>331.831434468006</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>326.597516024135</v>
+        <v>326.595536885845</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>327.857518630212</v>
+        <v>327.857606140183</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>330.497309865118</v>
+        <v>330.497307358274</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>330.497309865118</v>
+        <v>330.497307358274</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>330.481884140027</v>
+        <v>330.481874182834</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>330.481884140027</v>
+        <v>330.481874182834</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>-0.00173921614591897</v>
+        <v>-0.00173926695133711</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.058726237714499</v>
+        <v>0.0587262174079672</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>-0.00173770458595468</v>
+        <v>-0.00173775530308673</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>0.995932974540121</v>
+        <v>0.995932994451428</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.01189344047431</v>
+        <v>1.01189954196572</v>
       </c>
     </row>
     <row r="39">
@@ -3717,46 +3717,46 @@
         <v>329.749</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>3.87020418553917</v>
+        <v>3.8702437430648</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>324.775047981382</v>
+        <v>324.77503834185</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>328.037311559465</v>
+        <v>328.035326523887</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>330.506557658228</v>
+        <v>330.506663432731</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>325.878795814461</v>
+        <v>325.878756256935</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>325.878795814461</v>
+        <v>325.878756256935</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>325.302468435872</v>
+        <v>325.302459968025</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>325.302468435872</v>
+        <v>325.302459968025</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>-0.0157964226614658</v>
+        <v>-0.0157964185628385</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.0336009633051177</v>
+        <v>0.0336009535909745</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>-0.0156723135297805</v>
+        <v>-0.0156723094953881</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00162395620528</v>
+        <v>1.00162395986116</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.991663012019601</v>
+        <v>0.991668987042274</v>
       </c>
     </row>
     <row r="40">
@@ -3776,46 +3776,46 @@
         <v>309.118</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-9.83697224944584</v>
+        <v>-9.83701999995474</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>319.557874665353</v>
+        <v>319.557893275507</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>329.259754982534</v>
+        <v>329.257818050105</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>332.974639646626</v>
+        <v>332.974763083627</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>318.954972249446</v>
+        <v>318.955019999955</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>318.954972249446</v>
+        <v>318.955019999955</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>321.575741791891</v>
+        <v>321.575757308459</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>321.575741791891</v>
+        <v>321.575757308459</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>-0.0115223169250758</v>
+        <v>-0.0115222426427133</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>-0.00648927774739094</v>
+        <v>-0.00648924863543165</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>-0.011456189256417</v>
+        <v>-0.0114561158250446</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.00631455922859</v>
+        <v>1.00631454918002</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.97666276222841</v>
+        <v>0.976668554790468</v>
       </c>
     </row>
     <row r="41">
@@ -3835,46 +3835,46 @@
         <v>319.451</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>-3.06322685420975</v>
+        <v>-3.06323297699225</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>324.101874467195</v>
+        <v>324.101892889213</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>330.245282078413</v>
+        <v>330.243459432591</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>335.23071832739</v>
+        <v>335.230856854426</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>322.51422685421</v>
+        <v>322.514232976992</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>322.51422685421</v>
+        <v>322.514232976992</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>326.279354139719</v>
+        <v>326.279363920912</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>326.279354139719</v>
+        <v>326.279363920912</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0145208242558093</v>
+        <v>0.0145208059821031</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>-0.0144319775430642</v>
+        <v>-0.0144319683754431</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0146267635786796</v>
+        <v>0.0146267450376885</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>1.00671850379176</v>
+        <v>1.00671847674905</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.987990962615017</v>
+        <v>0.987996445051507</v>
       </c>
     </row>
     <row r="42">
@@ -3894,46 +3894,46 @@
         <v>351.422</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>10.2880093989892</v>
+        <v>10.2880302702926</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>341.704893750777</v>
+        <v>341.704856984496</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>330.967888142968</v>
+        <v>330.966259390656</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>337.173649095518</v>
+        <v>337.173797791265</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>341.133990601011</v>
+        <v>341.133969729707</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>341.133990601011</v>
+        <v>341.133969729707</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>340.637913518707</v>
+        <v>340.637890322196</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>340.637913518707</v>
+        <v>340.637890322196</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0430661469824062</v>
+        <v>0.0430660489071674</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.030730971548133</v>
+        <v>0.0307309324133864</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0440069504760618</v>
+        <v>0.0440068480848359</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.996877480388537</v>
+        <v>0.996877519764525</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.0292174126922</v>
+        <v>1.02922240759329</v>
       </c>
     </row>
     <row r="43">
@@ -3953,46 +3953,46 @@
         <v>358.827</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1.05755398140277</v>
+        <v>1.05761114762253</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>353.985456007373</v>
+        <v>353.985442686066</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>331.396736562547</v>
+        <v>331.395395877076</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>338.638704888644</v>
+        <v>338.638855820892</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>357.769446018597</v>
+        <v>357.769388852377</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>357.769446018597</v>
+        <v>357.769388852377</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>351.068375272849</v>
+        <v>351.068363916417</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>351.068375272849</v>
+        <v>351.068363916417</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0301609298952182</v>
+        <v>0.0301609656442824</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.0792059985307381</v>
+        <v>0.0792059917128343</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0306203782379868</v>
+        <v>0.0306204150817015</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.991759320375966</v>
+        <v>0.991759325616573</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.0593597840291</v>
+        <v>1.05936403548177</v>
       </c>
     </row>
     <row r="44">
@@ -4012,46 +4012,46 @@
         <v>338.369</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-9.23161845318892</v>
+        <v>-9.2317082312053</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>347.893518244916</v>
+        <v>347.893561916058</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>331.507344537537</v>
+        <v>331.506401663588</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>339.480960351927</v>
+        <v>339.48110172975</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>347.600618453189</v>
+        <v>347.600708231205</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>347.600618453189</v>
+        <v>347.600708231205</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>347.57813908221</v>
+        <v>347.578173523522</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>347.57813908221</v>
+        <v>347.578173523522</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.00999150544598695</v>
+        <v>-0.00999137400837845</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0808593246039913</v>
+        <v>0.0808593795524248</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.00994175618332371</v>
+        <v>-0.00994162605242732</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>0.99909346065343</v>
+        <v>0.999093434236614</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.04847794418278</v>
+        <v>1.04848103016799</v>
       </c>
     </row>
     <row r="45">
@@ -4071,46 +4071,46 @@
         <v>336.904</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-0.437873403866151</v>
+        <v>-0.437888779301532</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>340.901677677989</v>
+        <v>340.901689312571</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>331.291712211732</v>
+        <v>331.291293267541</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>339.651143836176</v>
+        <v>339.651258969436</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>337.341873403866</v>
+        <v>337.341888779302</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>337.341873403866</v>
+        <v>337.341888779302</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>343.000731354872</v>
+        <v>343.000747230041</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>343.000731354872</v>
+        <v>343.000747230041</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.0132569210020942</v>
+        <v>-0.0132569738083035</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0512486524292679</v>
+        <v>0.0512486695701133</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.0131694350497</v>
+        <v>-0.0131694871604801</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.00615735801355</v>
+        <v>1.00615737024273</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.03534353173211</v>
+        <v>1.03534488892542</v>
       </c>
     </row>
     <row r="46">
@@ -4130,46 +4130,46 @@
         <v>359.582</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>9.8634398414351</v>
+        <v>9.86349686964318</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>349.688827415465</v>
+        <v>349.688841017311</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>330.751898025125</v>
+        <v>330.752146147886</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>339.140581982709</v>
+        <v>339.140649024058</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>349.718560158565</v>
+        <v>349.718503130357</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>349.718560158565</v>
+        <v>349.718503130357</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>348.92246935314</v>
+        <v>348.922500345133</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>348.92246935314</v>
+        <v>348.922500345133</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0171171672790584</v>
+        <v>0.0171172098178627</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.0243207097790608</v>
+        <v>0.0243208705147289</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0172645054571099</v>
+        <v>0.0172645487303265</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.997808457113175</v>
+        <v>0.997808506928763</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.05493716419017</v>
+        <v>1.05493646650178</v>
       </c>
     </row>
     <row r="47">
@@ -4189,46 +4189,46 @@
         <v>362.479</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>-2.99736941779334</v>
+        <v>-2.99724335872378</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.427867455506185</v>
+        <v>0.427889102682699</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>354.000906626149</v>
+        <v>354.000955876886</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>329.893741768453</v>
+        <v>329.894817385771</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>337.929055080679</v>
+        <v>337.92904652677</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>365.476369417793</v>
+        <v>365.476243358724</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>358.910883691566</v>
+        <v>358.911106340516</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>351.665071371901</v>
+        <v>351.665139199029</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>351.665071371901</v>
+        <v>351.665139199029</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.00782947417587652</v>
+        <v>0.00782957822808404</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.00169965779056191</v>
+        <v>0.00169988339579907</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.00786020465762793</v>
+        <v>0.00786030952771255</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.993401612226053</v>
+        <v>0.993401665619599</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.06599497609969</v>
+        <v>1.06599170604066</v>
       </c>
     </row>
     <row r="48">
@@ -4248,46 +4248,46 @@
         <v>327.6245</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>-6.45748901546646</v>
+        <v>-6.45773395622567</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.485930338159144</v>
+        <v>0.485954956885541</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>343.882156783392</v>
+        <v>343.882167047653</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>328.734937396288</v>
+        <v>328.737018035457</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>336.049233310119</v>
+        <v>336.04911538126</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>334.081989015466</v>
+        <v>334.082233956226</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>339.119957945908</v>
+        <v>339.119840984727</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>342.903656717028</v>
+        <v>342.903644490082</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>342.903656717028</v>
+        <v>342.903644490082</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.0252296973448796</v>
+        <v>-0.025229925876174</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.0134487237244698</v>
+        <v>-0.0134488566587846</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.024914088341765</v>
+        <v>-0.024914311179385</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.99715454830365</v>
+        <v>0.997154482984763</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.04310074077602</v>
+        <v>1.04309410159916</v>
       </c>
     </row>
     <row r="49">
@@ -4307,46 +4307,46 @@
         <v>336.2245</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.76067271526747</v>
+        <v>1.76071034964034</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>334.905390714633</v>
+        <v>334.905323727477</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>327.311314576903</v>
+        <v>327.314594331801</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>333.63869599412</v>
+        <v>333.638429790283</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>334.463827284733</v>
+        <v>334.46378965036</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>334.463827284733</v>
+        <v>334.46378965036</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>334.345978132513</v>
+        <v>334.345903215258</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>334.345978132513</v>
+        <v>334.345903215258</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.0252732039902997</v>
+        <v>-0.0252733924042887</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>-0.0252324628818469</v>
+        <v>-0.0252327264143788</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.024956510135956</v>
+        <v>-0.024956693847772</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.998329639959136</v>
+        <v>0.998329615946404</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.02149227124856</v>
+        <v>1.02148180681589</v>
       </c>
     </row>
     <row r="50">
@@ -4366,46 +4366,46 @@
         <v>337.3735</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>8.03719998531895</v>
+        <v>8.03730742441393</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>323.476875700457</v>
+        <v>323.476723023448</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>325.665193616415</v>
+        <v>325.669881774004</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>330.850376078946</v>
+        <v>330.849917584612</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>329.336300014681</v>
+        <v>329.336192575586</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>329.336300014681</v>
+        <v>329.336192575586</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>324.437508731889</v>
+        <v>324.437397258255</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>324.437508731889</v>
+        <v>324.437397258255</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0300833790119875</v>
+        <v>-0.0300834985314343</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.0701730692971514</v>
+        <v>-0.0701734713658732</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0296353778680629</v>
+        <v>-0.0296354938454988</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00296971160412</v>
+        <v>1.00296984038242</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.996230223835429</v>
+        <v>0.996215540383913</v>
       </c>
     </row>
     <row r="51">
@@ -4425,46 +4425,46 @@
         <v>298.598</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>-6.01560761346261</v>
+        <v>-6.0154142314868</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>312.288104321328</v>
+        <v>312.288084892439</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>323.843365141382</v>
+        <v>323.849684108343</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>327.84133216732</v>
+        <v>327.840633394322</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>304.613607613463</v>
+        <v>304.613414231487</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>304.613607613463</v>
+        <v>304.613414231487</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>314.723812830278</v>
+        <v>314.723788591704</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>314.723812830278</v>
+        <v>314.723788591704</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>-0.0303974709420299</v>
+        <v>-0.0303972043668887</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.105046709351909</v>
+        <v>-0.105046950890452</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.0299401137050344</v>
+        <v>-0.0299398551111487</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00779955584361</v>
+        <v>1.00779954092742</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.97183961972751</v>
+        <v>0.971820582311929</v>
       </c>
     </row>
     <row r="52">
@@ -4484,46 +4484,46 @@
         <v>316.88</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>-3.45173607950766</v>
+        <v>-3.45213332825766</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>319.30536695217</v>
+        <v>319.305542125305</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>321.894914219864</v>
+        <v>321.903096525343</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>324.761052481638</v>
+        <v>324.760063224439</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>320.331736079508</v>
+        <v>320.332133328258</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>320.331736079508</v>
+        <v>320.332133328258</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>319.321103766771</v>
+        <v>319.32125106802</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>319.321103766771</v>
+        <v>319.32125106802</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0145017218287427</v>
+        <v>0.0145022601390836</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>-0.0687731159709332</v>
+        <v>-0.0687726531957124</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0146073819300474</v>
+        <v>0.01460792810384</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00004928452895</v>
+        <v>1.00004919721283</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.992004190375824</v>
+        <v>0.991979432676504</v>
       </c>
     </row>
     <row r="53">
@@ -4543,46 +4543,46 @@
         <v>335.545</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3.53766470539346</v>
+        <v>3.53767661592175</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>326.072380209225</v>
+        <v>326.072530421997</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>319.856907321462</v>
+        <v>319.867191546858</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>321.642886621533</v>
+        <v>321.641556984178</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>332.007335294607</v>
+        <v>332.007323384078</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>332.007335294607</v>
+        <v>332.007323384078</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>323.370407957302</v>
+        <v>323.370483122963</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>323.370407957302</v>
+        <v>323.370483122963</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0126012486533053</v>
+        <v>0.0126010198027849</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.0328269843008597</v>
+        <v>-0.0328265427712714</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0126809789355116</v>
+        <v>0.0126807471829691</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.991713581352124</v>
+        <v>0.991713355014797</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.01098460141212</v>
+        <v>1.01095233168229</v>
       </c>
     </row>
     <row r="54">
@@ -4602,46 +4602,46 @@
         <v>315.165</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>6.02977483951333</v>
+        <v>6.02984760456182</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>312.51276189796</v>
+        <v>312.512454770258</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>317.765433929441</v>
+        <v>317.778059842742</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>318.498037604621</v>
+        <v>318.496324933273</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>309.135225160487</v>
+        <v>309.135152395438</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>309.135225160487</v>
+        <v>309.135152395438</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>313.079111779795</v>
+        <v>313.078911123387</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>313.079111779795</v>
+        <v>313.078911123387</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0323425281478983</v>
+        <v>-0.0323434015053318</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.0350095061341411</v>
+        <v>-0.0350097930474573</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0318251018778006</v>
+        <v>-0.0318259474401756</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.00181224561325</v>
+        <v>1.00181258808884</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.985252259530887</v>
+        <v>0.98521248219062</v>
       </c>
     </row>
     <row r="55">
@@ -4661,46 +4661,46 @@
         <v>293.215</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>-8.82366150359906</v>
+        <v>-8.82301631859517</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>304.192042871136</v>
+        <v>304.191805155126</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>315.664177544551</v>
+        <v>315.679379665249</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>315.389530691887</v>
+        <v>315.387406163455</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>302.038661503599</v>
+        <v>302.038016318595</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>302.038661503599</v>
+        <v>302.038016318595</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>307.063653663838</v>
+        <v>307.063463568961</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>307.063653663838</v>
+        <v>307.063463568961</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.0194008448739088</v>
+        <v>-0.0194008230342986</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0243393059379698</v>
+        <v>-0.0243398348025137</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0192138596591771</v>
+        <v>-0.0192138382391899</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>1.00944012461864</v>
+        <v>1.00944028854548</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.97275419736375</v>
+        <v>0.972706750420555</v>
       </c>
     </row>
     <row r="56">
@@ -4720,46 +4720,46 @@
         <v>315.244</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.20193351233295</v>
+        <v>0.201330756784481</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>313.616061127637</v>
+        <v>313.616335918384</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>313.591427787059</v>
+        <v>313.609427449477</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>312.333577082096</v>
+        <v>312.331033903769</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>315.042066487667</v>
+        <v>315.042669243216</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>315.042066487667</v>
+        <v>315.042669243216</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>313.816413342223</v>
+        <v>313.816666834478</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>313.816413342223</v>
+        <v>313.816666834478</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.0217530770173475</v>
+        <v>0.0217545038628653</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0172387304177964</v>
+        <v>-0.0172383899133901</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0219914001472061</v>
+        <v>0.021992858372095</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.0006388455166</v>
+        <v>1.00063877704427</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.0007174480398</v>
+        <v>1.00066082001006</v>
       </c>
     </row>
     <row r="57">
@@ -4779,46 +4779,46 @@
         <v>327.515</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>4.37214111004313</v>
+        <v>4.37168746711408</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>322.328796389658</v>
+        <v>322.32946765842</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>311.576958329708</v>
+        <v>311.597953778435</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>309.279633628069</v>
+        <v>309.276694434034</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>323.142858889957</v>
+        <v>323.143312532886</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>323.142858889957</v>
+        <v>323.143312532886</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>320.521769164646</v>
+        <v>320.522185832923</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>320.521769164646</v>
+        <v>320.522185832923</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0211420525277533</v>
+        <v>0.0211425447235034</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.00880921297236181</v>
+        <v>-0.00880815485239383</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0213671291154285</v>
+        <v>0.0213676318281124</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>0.994393838697468</v>
+        <v>0.994393060496062</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.02870819101287</v>
+        <v>1.02864021392398</v>
       </c>
     </row>
     <row r="58">
@@ -4838,46 +4838,46 @@
         <v>324.057</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>3.29770760899512</v>
+        <v>3.29755097729681</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>320.421098684744</v>
+        <v>320.420881663244</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>309.651449494427</v>
+        <v>309.675605011248</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>306.190699629656</v>
+        <v>306.187432210766</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>320.759292391005</v>
+        <v>320.759449022703</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>320.759292391005</v>
+        <v>320.759449022703</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>319.514455074943</v>
+        <v>319.514146056482</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>319.514455074943</v>
+        <v>319.514146056482</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>-0.00314768096945434</v>
+        <v>-0.00314994808797926</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.0205550068753058</v>
+        <v>0.020554673931896</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>-0.00314273221543959</v>
+        <v>-0.00314499220645625</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.997170462202637</v>
+        <v>0.99717017317331</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.03185195999121</v>
+        <v>1.03177047492933</v>
       </c>
     </row>
     <row r="59">
@@ -4897,46 +4897,46 @@
         <v>304.316</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>-9.0803766278055</v>
+        <v>-9.0783736476348</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>316.443061865074</v>
+        <v>316.441040828066</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>307.852810290997</v>
+        <v>307.880243356269</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>303.099090513017</v>
+        <v>303.095624780977</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>313.396376627805</v>
+        <v>313.394373647635</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>313.396376627805</v>
+        <v>313.394373647635</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>313.836808923318</v>
+        <v>313.834837525264</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>313.836808923318</v>
+        <v>313.834837525264</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>-0.0179293815912942</v>
+        <v>-0.0179346960627876</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.0220578214929179</v>
+        <v>0.022052034057064</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>-0.0177696065434449</v>
+        <v>-0.0177748265650001</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.991763911882299</v>
+        <v>0.991764016146634</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.01943785611918</v>
+        <v>1.01934061797562</v>
       </c>
     </row>
     <row r="60">
@@ -4956,46 +4956,46 @@
         <v>326.08</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>2.26038344880587</v>
+        <v>2.2596699892815</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.160783439951754</v>
+        <v>0.160636739196756</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>304.725109522381</v>
+        <v>304.723501526354</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>306.225892131009</v>
+        <v>306.256658424352</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>300.109964668118</v>
+        <v>300.106509775735</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>323.819616551194</v>
+        <v>323.820330010718</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>307.795190046657</v>
+        <v>307.791153783082</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>302.91746150282</v>
+        <v>302.915400702435</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>302.91746150282</v>
+        <v>302.915400702435</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>-0.0354127698844817</v>
+        <v>-0.0354132914601044</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>-0.0347303435257758</v>
+        <v>-0.0347376901361102</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.0347930743304422</v>
+        <v>-0.0347935777587142</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.994067938732079</v>
+        <v>0.994066421477627</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>0.989196110736535</v>
+        <v>0.989090007906742</v>
       </c>
     </row>
     <row r="61">
@@ -5015,46 +5015,46 @@
         <v>287.232</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>4.54891070983732</v>
+        <v>4.54707840405869</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>287.815167761869</v>
+        <v>287.81607705145</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>304.819011155014</v>
+        <v>304.853086157788</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>297.379966915499</v>
+        <v>297.376818570445</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>282.683089290163</v>
+        <v>282.684921595941</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>282.683089290163</v>
+        <v>282.684921595941</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>289.35877384578</v>
+        <v>289.358896241198</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>289.35877384578</v>
+        <v>289.358896241198</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0457930139542547</v>
+        <v>-0.0457857877681384</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>-0.0972258308697228</v>
+        <v>-0.0972266225838374</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0447603369900611</v>
+        <v>-0.0447534342255302</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1.00536318532451</v>
+        <v>1.00536043436334</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.949280600148093</v>
+        <v>0.949174895646062</v>
       </c>
     </row>
     <row r="62">
@@ -5074,46 +5074,46 @@
         <v>285.117</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.84327324386113</v>
+        <v>0.842412010170969</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>286.71175945127</v>
+        <v>286.71216672343</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>303.68146431476</v>
+        <v>303.718721558464</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>295.104168202593</v>
+        <v>295.101705760548</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>284.273726756139</v>
+        <v>284.274587989829</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>284.273726756139</v>
+        <v>284.274587989829</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>288.399126519224</v>
+        <v>288.399120288957</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>288.399126519224</v>
+        <v>288.399120288957</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.00332197347181772</v>
+        <v>-0.00332241806310791</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0973831639273451</v>
+        <v>-0.0973823104596592</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.00331646182281709</v>
+        <v>-0.00331690493953873</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.00588523844011</v>
+        <v>1.00588378785876</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.94967642220107</v>
+        <v>0.949559904668047</v>
       </c>
     </row>
     <row r="63">
@@ -5133,46 +5133,46 @@
         <v>294.649</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>-7.71696327445338</v>
+        <v>-7.71338358022686</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>295.902590564063</v>
+        <v>295.899001818053</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>302.848713610831</v>
+        <v>302.888904525418</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>293.404155088706</v>
+        <v>293.402866456612</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>302.365963274453</v>
+        <v>302.362383580227</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>302.365963274453</v>
+        <v>302.362383580227</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>294.797705556877</v>
+        <v>294.795300183629</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>294.797705556877</v>
+        <v>294.795300183629</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.0219440005415596</v>
+        <v>0.0219358627083241</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.0606656160944252</v>
+        <v>-0.0606673799880557</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.0221865409749311</v>
+        <v>0.0221782226251719</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.996266051591234</v>
+        <v>0.996270005550398</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.973415742936587</v>
+        <v>0.973278637081571</v>
       </c>
     </row>
     <row r="64">
@@ -5192,46 +5192,46 @@
         <v>293.701</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>3.5158310775394</v>
+        <v>3.51915441576767</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>294.470022216639</v>
+        <v>294.470182350635</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>302.344091207835</v>
+        <v>302.386822374206</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>292.347361925913</v>
+        <v>292.34786018035</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>290.185168922461</v>
+        <v>290.181845584232</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>290.185168922461</v>
+        <v>290.181845584232</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>292.929498904837</v>
+        <v>292.929422491691</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>292.929498904837</v>
+        <v>292.929422491691</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.00635741524328224</v>
+        <v>-0.00634951666563545</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0329725547957221</v>
+        <v>-0.0329662281534281</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.00633724963533899</v>
+        <v>-0.00632940108195434</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.994768488485839</v>
+        <v>0.99476768803332</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.968861331916933</v>
+        <v>0.968724166588151</v>
       </c>
     </row>
     <row r="65">
@@ -5251,46 +5251,46 @@
         <v>292.276</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>3.29430550002477</v>
+        <v>3.28438478192574</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>288.224475733174</v>
+        <v>288.228644220463</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>302.19062755142</v>
+        <v>302.235333344793</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>292.046032107216</v>
+        <v>292.049044039094</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>288.981694499975</v>
+        <v>288.991615218074</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>288.981694499975</v>
+        <v>288.991615218074</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>287.449706918795</v>
+        <v>287.453086772551</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>287.449706918795</v>
+        <v>287.453086772551</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>-0.0188840495130942</v>
+        <v>-0.0188720306537646</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>-0.00659757746970091</v>
+        <v>-0.00658631717705505</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>-0.0187068629364046</v>
+        <v>-0.0186950688413534</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.997311925670406</v>
+        <v>0.997309228407852</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.951219795424936</v>
+        <v>0.951090276544939</v>
       </c>
     </row>
     <row r="66">
@@ -5310,46 +5310,46 @@
         <v>280.81</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>-0.840269752768981</v>
+        <v>-0.837271069824571</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>277.326890024735</v>
+        <v>277.328400563343</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>302.403753760807</v>
+        <v>302.449667566653</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>292.6015980606</v>
+        <v>292.607945067198</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>281.650269752769</v>
+        <v>281.647271069825</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>281.650269752769</v>
+        <v>281.647271069825</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>278.420114218808</v>
+        <v>278.420371858424</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>278.420114218808</v>
+        <v>278.420371858424</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.0319167372790006</v>
+        <v>-0.03192756991744</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>-0.0346013957145268</v>
+        <v>-0.0346004815151134</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.031412774070206</v>
+        <v>-0.0314232663685918</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.00394200574627</v>
+        <v>1.00393746653016</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.92069000717177</v>
+        <v>0.920551092346848</v>
       </c>
     </row>
     <row r="67">
@@ -5369,46 +5369,46 @@
         <v>256.914</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>-4.48422286971858</v>
+        <v>-4.4813300759709</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>269.202474170592</v>
+        <v>269.194794529557</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>302.990645372059</v>
+        <v>303.036777845428</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>294.100170526014</v>
+        <v>294.110803154907</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>261.398222869719</v>
+        <v>261.395330075971</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>261.398222869719</v>
+        <v>261.395330075971</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>269.680553919714</v>
+        <v>269.677372980632</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>269.680553919714</v>
+        <v>269.677372980632</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>-0.0318930502870241</v>
+        <v>-0.0319057709301278</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.0852013131842942</v>
+        <v>-0.0852046392440827</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>-0.0313898308806304</v>
+        <v>-0.031402152146531</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00177591142353</v>
+        <v>1.00179267378449</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.890062310631926</v>
+        <v>0.889916316092129</v>
       </c>
     </row>
     <row r="68">
@@ -5428,46 +5428,46 @@
         <v>306.755</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>2.1088515515591</v>
+        <v>2.11753228361437</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>274.275500186649</v>
+        <v>274.27156070076</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>303.945506993734</v>
+        <v>303.990615488949</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>296.57310360187</v>
+        <v>296.589054822482</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>304.646148448441</v>
+        <v>304.637467716386</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>274.275500186649</v>
+        <v>274.27156070076</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>273.536396540575</v>
+        <v>273.536877832876</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>273.536396540575</v>
+        <v>273.536877832876</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0141965650263426</v>
+        <v>0.014210119823848</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.0662039925537259</v>
+        <v>-0.0662021059334386</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0142978148213428</v>
+        <v>0.0143115635160131</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>0.997305250940857</v>
+        <v>0.997321330487173</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.89995209748639</v>
+        <v>0.899820138831948</v>
       </c>
     </row>
     <row r="69">
@@ -5487,46 +5487,46 @@
         <v>287.002</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>2.80563708071669</v>
+        <v>2.79294014598878</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>286.923953437277</v>
+        <v>286.928976407316</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>305.236547970325</v>
+        <v>305.279105900195</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>299.888241648294</v>
+        <v>299.910559224788</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>284.196362919283</v>
+        <v>284.209059854011</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>284.196362919283</v>
+        <v>284.209059854011</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>285.93619837595</v>
+        <v>285.942701805028</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>285.93619837595</v>
+        <v>285.942701805028</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0443340133927624</v>
+        <v>0.0443549979537198</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.00526529861195124</v>
+        <v>-0.00525437031997733</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0453314512883678</v>
+        <v>0.0453533873400864</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.996557432554883</v>
+        <v>0.996562652491089</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.936769204989659</v>
+        <v>0.936659916379968</v>
       </c>
     </row>
     <row r="70">
@@ -5546,46 +5546,46 @@
         <v>300.125</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>-0.951567478583008</v>
+        <v>-0.956126811328854</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>301.878795274569</v>
+        <v>301.888740028745</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>306.813433892074</v>
+        <v>306.851600072898</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>303.80194100834</v>
+        <v>303.83158804608</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>301.076567478583</v>
+        <v>301.081126811329</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>301.076567478583</v>
+        <v>301.081126811329</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>302.04624199491</v>
+        <v>302.052076876934</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>302.04624199491</v>
+        <v>302.052076876934</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0548114215101153</v>
+        <v>0.0548079950892685</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.084857833789749</v>
+        <v>0.0848777869980244</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0563413926269638</v>
+        <v>0.0563377731629957</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00055468195502</v>
+        <v>1.00054104981913</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.984462245226067</v>
+        <v>0.984358813202134</v>
       </c>
     </row>
     <row r="71">
@@ -5605,46 +5605,46 @@
         <v>318.876</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>-2.95947010319263</v>
+        <v>-2.96099403106549</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>318.161759835911</v>
+        <v>318.15322537574</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>308.612680233562</v>
+        <v>308.644280222014</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>307.992098631415</v>
+        <v>308.029905473762</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>321.835470103193</v>
+        <v>321.836994031065</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>321.835470103193</v>
+        <v>321.836994031065</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>317.794164979375</v>
+        <v>317.78810860469</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>317.794164979375</v>
+        <v>317.78810860469</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0508237684232335</v>
+        <v>0.0507853930457829</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.178409641927629</v>
+        <v>0.178401083829581</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0521374571007884</v>
+        <v>0.0520970817034578</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.998844629044276</v>
+        <v>0.998852387020064</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.02975083440792</v>
+        <v>1.02962578271692</v>
       </c>
     </row>
     <row r="72">
@@ -5664,46 +5664,46 @@
         <v>327.007</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.577847767470317</v>
+        <v>0.609680454698292</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>331.77472719949</v>
+        <v>331.755980115464</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>310.567216927863</v>
+        <v>310.589722016709</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>312.122984599278</v>
+        <v>312.169523389063</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>326.42915223253</v>
+        <v>326.397319545302</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>326.42915223253</v>
+        <v>326.397319545302</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>329.884976235739</v>
+        <v>329.870953810556</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>329.884976235739</v>
+        <v>329.870953810556</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.037340143574065</v>
+        <v>0.0373166933775498</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.206000299805827</v>
+        <v>0.205946914448951</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0380460454871765</v>
+        <v>0.0380217033888326</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.994304114181022</v>
+        <v>0.994318033681708</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.06220154045545</v>
+        <v>1.06207942641711</v>
       </c>
     </row>
     <row r="73">
@@ -5723,46 +5723,46 @@
         <v>348.079</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>3.23286962529582</v>
+        <v>3.22681787944508</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>338.014967241356</v>
+        <v>338.017394629155</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>312.618238151721</v>
+        <v>312.628746572282</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>315.928085851046</v>
+        <v>315.983489115998</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>344.846130374704</v>
+        <v>344.852182120555</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>344.846130374704</v>
+        <v>344.852182120555</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>337.598673498386</v>
+        <v>337.6033727076</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>337.598673498386</v>
+        <v>337.6033727076</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0231137966640749</v>
+        <v>0.0231702239975486</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.180678331095774</v>
+        <v>0.180667912055324</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0233829904916163</v>
+        <v>0.0234407388941709</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.998768416243911</v>
+        <v>0.998775146107469</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.0799071592699</v>
+        <v>1.07988589152196</v>
       </c>
     </row>
     <row r="74">
@@ -5782,46 +5782,46 @@
         <v>333.69</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>-0.58328101160761</v>
+        <v>-0.621807043989665</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>341.319341638227</v>
+        <v>341.365074028721</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>314.716851791444</v>
+        <v>314.712054752483</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>319.212420164002</v>
+        <v>319.275988959364</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>334.273281011608</v>
+        <v>334.31180704399</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>334.273281011608</v>
+        <v>334.31180704399</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>339.581027257402</v>
+        <v>339.611378030688</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>339.581027257402</v>
+        <v>339.611378030688</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.00585475146231344</v>
+        <v>0.00593020516926873</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.12426834055139</v>
+        <v>0.124347104453306</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.00587192401697845</v>
+        <v>0.00594782364578594</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.99490707332177</v>
+        <v>0.994862696475253</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.07900490655148</v>
+        <v>1.07911779324052</v>
       </c>
     </row>
     <row r="75">
@@ -5841,46 +5841,46 @@
         <v>342.148</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>-2.78341663168722</v>
+        <v>-2.82171591421633</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>340.425995675969</v>
+        <v>340.441403594382</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>316.834308165979</v>
+        <v>316.810487068284</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>321.92559553805</v>
+        <v>321.995552688979</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>344.931416631687</v>
+        <v>344.969715914216</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>344.931416631687</v>
+        <v>344.969715914216</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>338.804207199435</v>
+        <v>338.802972566838</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>338.804207199435</v>
+        <v>338.802972566838</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.00229020432063452</v>
+        <v>-0.00238322153936141</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0661121081987903</v>
+        <v>0.0661285409778773</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.00228758380360761</v>
+        <v>-0.00238038392158013</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.995236002840166</v>
+        <v>0.995187333237833</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.06934191931622</v>
+        <v>1.06941842646078</v>
       </c>
     </row>
     <row r="76">
@@ -5900,46 +5900,46 @@
         <v>329.742</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>-1.3387145227587</v>
+        <v>-1.21865139492869</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>328.660166219001</v>
+        <v>328.513196087339</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>318.954080362537</v>
+        <v>318.907133875836</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>324.092524277328</v>
+        <v>324.165889165087</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>331.080714522759</v>
+        <v>330.960651394929</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>331.080714522759</v>
+        <v>330.960651394929</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>329.443819987654</v>
+        <v>329.2926544204</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>329.443819987654</v>
+        <v>329.2926544204</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0280165420353657</v>
+        <v>-0.0284718540651731</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>-0.00133730324162928</v>
+        <v>-0.00175310794562467</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.027627718348465</v>
+        <v>-0.0280703503702633</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00238438925431</v>
+        <v>1.00237268500122</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.03288793049205</v>
+        <v>1.03256597122286</v>
       </c>
     </row>
     <row r="77">
@@ -5959,46 +5959,46 @@
         <v>305.407</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>5.61751864238813</v>
+        <v>5.64435902513885</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>0.31700241722258</v>
+        <v>0.33660804816285</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>315.73822435536</v>
+        <v>315.615950580954</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>321.077202161118</v>
+        <v>321.002685049321</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>325.853147791446</v>
+        <v>325.925578064056</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>299.789481357612</v>
+        <v>299.762640974861</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>310.682434273412</v>
+        <v>310.279598977526</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>319.435705527734</v>
+        <v>319.254409260774</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>319.435705527734</v>
+        <v>319.254409260774</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0308498196972538</v>
+        <v>-0.0309585763568165</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.0538004719699787</v>
+        <v>-0.0543506520674452</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0303788198555213</v>
+        <v>-0.0304842668819779</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.01171059088561</v>
+        <v>1.01152812040431</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.994887532897587</v>
+        <v>0.994553703535909</v>
       </c>
     </row>
     <row r="78">
@@ -6018,46 +6018,46 @@
         <v>324.625</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>-0.672239041354865</v>
+        <v>-0.872787693113639</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>321.393057225463</v>
+        <v>321.483812255409</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>323.212286488075</v>
+        <v>323.10536391137</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>327.382348441239</v>
+        <v>327.447172873405</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>325.297239041355</v>
+        <v>325.497787693114</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>325.297239041355</v>
+        <v>325.497787693114</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>322.766838880395</v>
+        <v>322.776985803487</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>322.766838880395</v>
+        <v>322.776985803487</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.0103741825919073</v>
+        <v>0.0109733321984667</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.0495145106097499</v>
+        <v>-0.0495695766284941</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0104281809923454</v>
+        <v>0.011033760037551</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.0042744596501</v>
+        <v>1.00402251528314</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>0.99862181103163</v>
+        <v>0.998983681038569</v>
       </c>
     </row>
     <row r="79">
@@ -6077,46 +6077,46 @@
         <v>325.422</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>-4.36844316545902</v>
+        <v>-4.41076885019474</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>327.890345560494</v>
+        <v>327.852011352083</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>325.361449539828</v>
+        <v>325.216691855818</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>328.779155019952</v>
+        <v>328.824997185218</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>329.790443165459</v>
+        <v>329.832768850195</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>329.790443165459</v>
+        <v>329.832768850195</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>326.927641344239</v>
+        <v>326.894043734677</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>326.927641344239</v>
+        <v>326.894043734677</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0128086646142012</v>
+        <v>0.0126744547875876</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>-0.0350543635610909</v>
+        <v>-0.0351500128288028</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0128910469188117</v>
+        <v>0.0127551161088555</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.997063944610478</v>
+        <v>0.997078048679783</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.00481369813979</v>
+        <v>1.00515764387519</v>
       </c>
     </row>
     <row r="80">
@@ -6136,46 +6136,46 @@
         <v>321.243</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>-1.58944000468285</v>
+        <v>-1.16984954520424</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>326.238089334794</v>
+        <v>326.047100093495</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>327.528110608146</v>
+        <v>327.339685541365</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>330.13217077383</v>
+        <v>330.143627665679</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>322.832440004683</v>
+        <v>322.412849545204</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>322.832440004683</v>
+        <v>322.412849545204</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>326.692001404164</v>
+        <v>326.54744430343</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>326.692001404164</v>
+        <v>326.54744430343</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.00072103081019092</v>
+        <v>-0.00106084315152032</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.00835292215708683</v>
+        <v>-0.00833668798899367</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.000720770929940606</v>
+        <v>-0.00106028065634822</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>1.00139135215724</v>
+        <v>1.00153457647619</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.997447213912632</v>
+        <v>0.997579758052785</v>
       </c>
     </row>
     <row r="81">
@@ -6195,46 +6195,46 @@
         <v>338.9</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>7.58731755816885</v>
+        <v>7.36869072688515</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>330.391207912455</v>
+        <v>330.456413416887</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>329.718457105812</v>
+        <v>329.48024667483</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>331.535055389848</v>
+        <v>331.492679839297</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>331.312682441831</v>
+        <v>331.531309273115</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>331.312682441831</v>
+        <v>331.531309273115</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>330.299181961874</v>
+        <v>330.365466085903</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>330.299181961874</v>
+        <v>330.365466085903</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>0.010981020433649</v>
+        <v>0.0116242646903132</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.0340083348421949</v>
+        <v>0.0348031428942728</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>0.011041533132756</v>
+        <v>0.0116920890029248</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.999721463681912</v>
+        <v>0.999724782672414</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>1.00176127494093</v>
+        <v>1.00268671466653</v>
       </c>
     </row>
     <row r="82">
@@ -6254,46 +6254,46 @@
         <v>335.07</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>-0.668922959152526</v>
+        <v>-0.916396252177701</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>334.089674774269</v>
+        <v>334.393018013883</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>331.935741651481</v>
+        <v>331.641197690539</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>333.044969901133</v>
+        <v>332.923115339978</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>335.738922959153</v>
+        <v>335.986396252178</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>335.738922959153</v>
+        <v>335.986396252178</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>332.989761973585</v>
+        <v>333.179879582399</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>332.989761973585</v>
+        <v>333.179879582399</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>0.0081128889419738</v>
+        <v>0.00848300841015244</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>0.031672780043484</v>
+        <v>0.0322293541251577</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>0.00814588760326007</v>
+        <v>0.00851909108370275</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.996707731834492</v>
+        <v>0.996372117938676</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>1.00317537459768</v>
+        <v>1.00463959816384</v>
       </c>
     </row>
     <row r="83">
@@ -6313,46 +6313,46 @@
         <v>322.848</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>-6.32051953420218</v>
+        <v>-6.36741655212425</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>329.920178034673</v>
+        <v>329.741285370309</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>334.184213254646</v>
+        <v>333.826642936936</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>334.717963476072</v>
+        <v>334.486088948798</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>329.168519534202</v>
+        <v>329.215416552124</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>329.168519534202</v>
+        <v>329.215416552124</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>330.298995434413</v>
+        <v>330.193299925401</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>330.298995434413</v>
+        <v>330.193299925401</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>-0.00811345366488196</v>
+        <v>-0.00900428274109415</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>0.0103122332400878</v>
+        <v>0.0100927387756329</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>-0.00808062843501345</v>
+        <v>-0.00896386558738371</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00114820924866</v>
+        <v>1.0013708157733</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.988374023469287</v>
+        <v>0.989116078394553</v>
       </c>
     </row>
     <row r="84">
@@ -6372,46 +6372,46 @@
         <v>325.352</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>-1.7680197100931</v>
+        <v>-1.00397034517881</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>328.92440723791</v>
+        <v>328.617277186381</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>336.470497913114</v>
+        <v>336.043402511572</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>336.623555048343</v>
+        <v>336.248071851392</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>327.120019710093</v>
+        <v>326.355970345179</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>327.120019710093</v>
+        <v>326.355970345179</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>329.570914268288</v>
+        <v>329.327795642454</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>329.570914268288</v>
+        <v>329.327795642454</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>-0.0022067424226523</v>
+        <v>-0.00262464623381593</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0.00881231512173652</v>
+        <v>0.00851438707461094</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>-0.00220430935663807</v>
+        <v>-0.0026212048613431</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>1.00196551856947</v>
+        <v>1.00216214577078</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.979494238907664</v>
+        <v>0.980015656254741</v>
       </c>
     </row>
     <row r="85">
@@ -6431,46 +6431,46 @@
         <v>344.852</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>9.97690188123514</v>
+        <v>9.46817467266621</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>332.570326518898</v>
+        <v>332.79248912976</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>338.798086816119</v>
+        <v>338.295414495502</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>338.803516331914</v>
+        <v>338.249181871415</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>334.875098118765</v>
+        <v>335.383825327334</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>334.875098118765</v>
+        <v>335.383825327334</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>332.502901418805</v>
+        <v>332.650381160704</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>332.502901418805</v>
+        <v>332.650381160704</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.00885703753322363</v>
+        <v>0.0100384379307665</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.00667188893366699</v>
+        <v>0.0069163254315654</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.00889637714853087</v>
+        <v>0.0100889920687324</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.999797260625148</v>
+        <v>0.99957298324422</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.981419064503954</v>
+        <v>0.983313302241424</v>
       </c>
     </row>
     <row r="86">
@@ -6490,46 +6490,46 @@
         <v>332.281</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>-0.860389727597691</v>
+        <v>-1.19690364296874</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>332.594091178879</v>
+        <v>332.805532964547</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>341.164627104018</v>
+        <v>340.580562324682</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>341.252101364063</v>
+        <v>340.480076324988</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>333.141389727598</v>
+        <v>333.477903642969</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>333.141389727598</v>
+        <v>333.477903642969</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>333.860931295625</v>
+        <v>333.801680726403</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>333.860931295625</v>
+        <v>333.801680726403</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0.00407594677341715</v>
+        <v>0.00345501432677999</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.0026162045249587</v>
+        <v>0.0018662625869954</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>0.00408426474182622</v>
+        <v>0.00346098976854292</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00380896759848</v>
+        <v>1.00299318269436</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.97859187257955</v>
+        <v>0.980096099577707</v>
       </c>
     </row>
     <row r="87">
@@ -6549,46 +6549,46 @@
         <v>317.285</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>-8.64462072117948</v>
+        <v>-8.64429803841837</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0.328782963460522</v>
+        <v>0.402268949458976</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>338.378987218849</v>
+        <v>337.536177499745</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>343.56531404923</v>
+        <v>342.894909691834</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>343.943922091001</v>
+        <v>342.917085745513</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>325.92962072118</v>
+        <v>325.929298038418</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>334.285847608539</v>
+        <v>332.86709029234</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>339.690024758805</v>
+        <v>338.778918913452</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>339.690024758805</v>
+        <v>338.778918913452</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>0.017308976977678</v>
+        <v>0.0148006916912644</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0284319039845751</v>
+        <v>0.0260017964931172</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>0.0174596453695837</v>
+        <v>0.0149107643083708</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00387446499185</v>
+        <v>1.00368180211944</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.988720370968911</v>
+        <v>0.987996349137756</v>
       </c>
     </row>
     <row r="88">
@@ -6608,46 +6608,46 @@
         <v>355.915</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>-1.13201409054553</v>
+        <v>0.0114085738396887</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>354.333528101584</v>
+        <v>353.646146679814</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>345.990328400817</v>
+        <v>345.230081128006</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>346.813036900756</v>
+        <v>345.501529802981</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>357.047014090546</v>
+        <v>355.90359142616</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>357.047014090546</v>
+        <v>355.90359142616</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>352.684377321363</v>
+        <v>351.966471266111</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>352.684377321363</v>
+        <v>351.966471266111</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.0375400318563866</v>
+        <v>0.0381881809400666</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0.0701319869333477</v>
+        <v>0.0687420737733149</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.0382535594672953</v>
+        <v>0.0389267206913406</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.995345767054401</v>
+        <v>0.995250406573144</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>1.0193475030111</v>
+        <v>1.01951275542414</v>
       </c>
     </row>
     <row r="89">
@@ -6667,80 +6667,106 @@
         <v>373.783</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>11.4253665041768</v>
+        <v>10.5913880802184</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>359.241423657568</v>
+        <v>359.470520836992</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>348.424051241313</v>
+        <v>347.57143377712</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>349.745213808946</v>
+        <v>348.124478190117</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>362.357633495823</v>
+        <v>363.191611919782</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>362.357633495823</v>
+        <v>363.191611919782</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>360.587427027397</v>
+        <v>357.333173068881</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>360.587427027397</v>
+        <v>357.333173068881</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>0.0221609016119005</v>
+        <v>0.015132685484854</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>0.0844640016335325</v>
+        <v>0.0742004017011859</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>0.0224082783764272</v>
+        <v>0.0152477643210294</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>1.00374679332947</v>
+        <v>0.994054177897162</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>1.0349096904842</v>
+        <v>1.02808556268758</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
         <v>142</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90" s="2" t="n">
+        <v>345.704</v>
+      </c>
       <c r="C90" s="3" t="n">
-        <v>346.122717639737</v>
+        <v>345.704</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>376.710118416795</v>
+        <v>345.704</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>315.535316862679</v>
+        <v>345.704</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>-0.90073166429486</v>
-      </c>
-      <c r="G90" s="7"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="11"/>
-      <c r="L90" s="12"/>
-      <c r="M90" s="13"/>
+        <v>-1.34187700979898</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>351.965419976212</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>349.910995727036</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>350.729010907763</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>347.045877009799</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>347.045877009799</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>352.42778864646</v>
+      </c>
       <c r="N90" s="14" t="n">
-        <v>347.023449304032</v>
-      </c>
-      <c r="O90" s="15"/>
-      <c r="P90" s="16"/>
-      <c r="Q90" s="17"/>
-      <c r="R90" s="18"/>
-      <c r="S90" s="19"/>
+        <v>352.42778864646</v>
+      </c>
+      <c r="O90" s="15" t="n">
+        <v>-0.0138228580982386</v>
+      </c>
+      <c r="P90" s="16" t="n">
+        <v>0.0557999225154402</v>
+      </c>
+      <c r="Q90" s="17" t="n">
+        <v>-0.0137277610704092</v>
+      </c>
+      <c r="R90" s="18" t="n">
+        <v>1.00131367641253</v>
+      </c>
+      <c r="S90" s="19" t="n">
+        <v>1.00719266599266</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
@@ -6748,16 +6774,16 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
-        <v>340.448046464769</v>
+        <v>340.17705618569</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>376.705212001354</v>
+        <v>370.525776074181</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>304.190880928184</v>
+        <v>309.828336297198</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>-10.1124926431591</v>
+        <v>-10.040204182597</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -6767,7 +6793,7 @@
       <c r="L91" s="12"/>
       <c r="M91" s="13"/>
       <c r="N91" s="14" t="n">
-        <v>350.560539107928</v>
+        <v>350.217260368287</v>
       </c>
       <c r="O91" s="15"/>
       <c r="P91" s="16"/>
@@ -6781,16 +6807,16 @@
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3" t="n">
-        <v>348.859693415875</v>
+        <v>348.792918935116</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>385.766141601964</v>
+        <v>384.756109910764</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>311.953245229787</v>
+        <v>312.829727959468</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>-0.858378722624383</v>
+        <v>0.335773191330656</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
@@ -6800,7 +6826,7 @@
       <c r="L92" s="12"/>
       <c r="M92" s="13"/>
       <c r="N92" s="14" t="n">
-        <v>349.718072138499</v>
+        <v>348.457145743785</v>
       </c>
       <c r="O92" s="15"/>
       <c r="P92" s="16"/>
@@ -6814,16 +6840,16 @@
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3" t="n">
-        <v>344.503677947775</v>
+        <v>344.346073701541</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>383.593116372733</v>
+        <v>380.945736335171</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>305.414239522817</v>
+        <v>307.746411067912</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>12.77042660226</v>
+        <v>11.7107462334567</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
@@ -6833,7 +6859,7 @@
       <c r="L93" s="12"/>
       <c r="M93" s="13"/>
       <c r="N93" s="14" t="n">
-        <v>331.733251345515</v>
+        <v>332.635327468084</v>
       </c>
       <c r="O93" s="15"/>
       <c r="P93" s="16"/>
@@ -6846,10 +6872,18 @@
         <v>146</v>
       </c>
       <c r="B94" s="2"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
+      <c r="C94" s="3" t="n">
+        <v>337.853795527083</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>376.617121570834</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>299.090469483333</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>-2.19155355634066</v>
+      </c>
       <c r="G94" s="7"/>
       <c r="H94" s="8"/>
       <c r="I94" s="9"/>
@@ -6857,7 +6891,9 @@
       <c r="K94" s="11"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13"/>
-      <c r="N94" s="14"/>
+      <c r="N94" s="14" t="n">
+        <v>340.045349083424</v>
+      </c>
       <c r="O94" s="15"/>
       <c r="P94" s="16"/>
       <c r="Q94" s="17"/>
@@ -7355,7 +7391,7 @@
         <v>183</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.129884158777597</v>
+        <v>0.126986813483656</v>
       </c>
     </row>
     <row r="6">
@@ -7363,7 +7399,7 @@
         <v>184</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0788479318001665</v>
+        <v>0.0719636967881625</v>
       </c>
     </row>
     <row r="7">
@@ -7371,7 +7407,7 @@
         <v>185</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.212296402428649</v>
+        <v>0.191701015438339</v>
       </c>
     </row>
     <row r="8">
@@ -7379,7 +7415,7 @@
         <v>186</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.405559896985056</v>
+        <v>0.392292035066246</v>
       </c>
     </row>
     <row r="9">
@@ -7387,7 +7423,7 @@
         <v>187</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.50185533493928</v>
+        <v>0.500863481293228</v>
       </c>
     </row>
     <row r="10">
@@ -7395,7 +7431,7 @@
         <v>188</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.454695013463935</v>
+        <v>0.439197086435172</v>
       </c>
     </row>
     <row r="11">
@@ -7403,7 +7439,7 @@
         <v>189</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.332154177242986</v>
+        <v>0.318663890118563</v>
       </c>
     </row>
     <row r="12">
@@ -7411,7 +7447,7 @@
         <v>190</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.223528962663784</v>
+        <v>0.226435782234767</v>
       </c>
     </row>
     <row r="13">
@@ -7419,7 +7455,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.160930672559236</v>
+        <v>0.145109285330823</v>
       </c>
     </row>
     <row r="14">
